--- a/metadata.xlsx
+++ b/metadata.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2987BBC7-4FFD-4D99-A282-3D00D6414A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF63D811-BB00-4ADE-A082-A9CCE4313B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6164,96 +6164,96 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -7011,446 +7011,446 @@
     </row>
     <row r="3" spans="1:180" s="69" customFormat="1" ht="25.5" customHeight="1">
       <c r="A3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(A237), LOWER(A2))</f>
-        <v>0iy field index</v>
+        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(A1), LOWER(A2))</f>
+        <v>vjdbv1.1 field index</v>
       </c>
       <c r="B3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(B237), LOWER(B2))</f>
-        <v>sequence_url field id</v>
+        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(B1), LOWER(B2))</f>
+        <v>vjdbv1.1 field id</v>
       </c>
       <c r="C3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(C237), LOWER(C2))</f>
-        <v>genbank url name</v>
-      </c>
-      <c r="D3" s="70" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(D237), LOWER(D2))</f>
-        <v>url to the genbank record from the ictv vmr description</v>
-      </c>
-      <c r="E3" s="45" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(E237), LOWER(E2))</f>
-        <v>keyword fields_type</v>
+        <f t="shared" ref="C3:BC3" si="0">_xlfn.TEXTJOIN(" ", TRUE, LOWER(C1), LOWER(C2))</f>
+        <v>vjdbv1.1 name</v>
+      </c>
+      <c r="D3" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>vjdbv1.1 description</v>
+      </c>
+      <c r="E3" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>vjdbv1.1 fields_type</v>
       </c>
       <c r="F3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(F237), LOWER(F2))</f>
-        <v>private privacy</v>
+        <f t="shared" si="0"/>
+        <v>vjdbv1.1 privacy</v>
       </c>
       <c r="G3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(G237), LOWER(G2))</f>
-        <v>field id</v>
+        <f t="shared" si="0"/>
+        <v>ena field id</v>
       </c>
       <c r="H3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(H237), LOWER(H2))</f>
-        <v>field id</v>
+        <f t="shared" si="0"/>
+        <v>rki field id</v>
       </c>
       <c r="I3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(I237), LOWER(I2))</f>
-        <v>field id</v>
+        <f t="shared" si="0"/>
+        <v>migs-vi field id</v>
       </c>
       <c r="J3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(J237), LOWER(J2))</f>
-        <v>field id</v>
+        <f t="shared" si="0"/>
+        <v>migs-uvig field id</v>
       </c>
       <c r="K3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(K237), LOWER(K2))</f>
-        <v>field id</v>
+        <f t="shared" si="0"/>
+        <v>env-o field id</v>
       </c>
       <c r="L3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(L237), LOWER(L2))</f>
-        <v>n nucleotide field id</v>
+        <f t="shared" si="0"/>
+        <v>ncbi virus n nucleotide field id</v>
       </c>
       <c r="M3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(M237), LOWER(M2))</f>
-        <v>b field name</v>
+        <f t="shared" si="0"/>
+        <v>bv-brc b field name</v>
       </c>
       <c r="N3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(N237), LOWER(N2))</f>
-        <v>field name</v>
+        <f t="shared" si="0"/>
+        <v>ena erc32 field name</v>
       </c>
       <c r="O3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(O237), LOWER(O2))</f>
-        <v>field name</v>
+        <f t="shared" si="0"/>
+        <v>ena erc33 field name</v>
       </c>
       <c r="P3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(P237), LOWER(P2))</f>
-        <v>field name</v>
+        <f t="shared" si="0"/>
+        <v>img/vr field name</v>
       </c>
       <c r="Q3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(Q237), LOWER(Q2))</f>
-        <v>field name</v>
+        <f t="shared" si="0"/>
+        <v>phd field name</v>
       </c>
       <c r="R3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(R237), LOWER(R2))</f>
-        <v>field name</v>
+        <f t="shared" si="0"/>
+        <v>phispy field name</v>
       </c>
       <c r="S3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(S237), LOWER(S2))</f>
-        <v>field name</v>
+        <f t="shared" si="0"/>
+        <v>gtdb field name</v>
       </c>
       <c r="T3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(T237), LOWER(T2))</f>
-        <v>object name</v>
+        <f t="shared" si="0"/>
+        <v>ena submission object object name</v>
       </c>
       <c r="U3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(U237), LOWER(U2))</f>
-        <v>object name</v>
+        <f t="shared" si="0"/>
+        <v>vjbd submission object object name</v>
       </c>
       <c r="V3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(V237), LOWER(V2))</f>
-        <v>group1</v>
+        <f t="shared" si="0"/>
+        <v>vjdbv1.1 group1</v>
       </c>
       <c r="W3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(W237), LOWER(W2))</f>
-        <v>group2</v>
+        <f t="shared" si="0"/>
+        <v>vjdbv1.1 group2</v>
       </c>
       <c r="X3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(X237), LOWER(X2))</f>
-        <v>group3</v>
+        <f t="shared" si="0"/>
+        <v>vjdbv1.1 group3</v>
       </c>
       <c r="Y3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(Y237), LOWER(Y2))</f>
-        <v>tags</v>
+        <f t="shared" si="0"/>
+        <v>vjdbv1.1 tags</v>
       </c>
       <c r="Z3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(Z237), LOWER(Z2))</f>
-        <v>input source</v>
+        <f t="shared" si="0"/>
+        <v>vjdbv1.1 input source</v>
       </c>
       <c r="AA3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(AA237), LOWER(AA2))</f>
-        <v>notes</v>
+        <f t="shared" si="0"/>
+        <v>vjdbv1.1 notes</v>
       </c>
       <c r="AB3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(AB237), LOWER(AB2))</f>
-        <v>changes</v>
+        <f t="shared" si="0"/>
+        <v>vjdbv1.1 changes</v>
       </c>
       <c r="AC3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(AC237), LOWER(AC2))</f>
-        <v>n field name</v>
+        <f t="shared" si="0"/>
+        <v>ncbi virus n field name</v>
       </c>
       <c r="AD3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(AD237), LOWER(AD2))</f>
-        <v>n field description</v>
+        <f t="shared" si="0"/>
+        <v>ncbi virus n field description</v>
       </c>
       <c r="AE3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(AE237), LOWER(AE2))</f>
-        <v>n type</v>
+        <f t="shared" si="0"/>
+        <v>ncbi virus n type</v>
       </c>
       <c r="AF3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(AF237), LOWER(AF2))</f>
-        <v>n curation notes</v>
+        <f t="shared" si="0"/>
+        <v>ncbi virus n curation notes</v>
       </c>
       <c r="AG3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(AG237), LOWER(AG2))</f>
-        <v>b category</v>
+        <f t="shared" si="0"/>
+        <v>bv-brc b category</v>
       </c>
       <c r="AH3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(AH237), LOWER(AH2))</f>
-        <v>b schema category</v>
+        <f t="shared" si="0"/>
+        <v>bv-brc b schema category</v>
       </c>
       <c r="AI3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(AI237), LOWER(AI2))</f>
-        <v>b field id</v>
+        <f t="shared" si="0"/>
+        <v>bv-brc b field id</v>
       </c>
       <c r="AJ3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(AJ237), LOWER(AJ2))</f>
-        <v>b field type</v>
+        <f t="shared" si="0"/>
+        <v>bv-brc b field type</v>
       </c>
       <c r="AK3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(AK237), LOWER(AK2))</f>
-        <v>b type</v>
+        <f t="shared" si="0"/>
+        <v>bv-brc b type</v>
       </c>
       <c r="AL3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(AL237), LOWER(AL2))</f>
-        <v>b curation notes</v>
+        <f t="shared" si="0"/>
+        <v>bv-brc b curation notes</v>
       </c>
       <c r="AM3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(AM237), LOWER(AM2))</f>
-        <v>field description</v>
+        <f t="shared" si="0"/>
+        <v>ena erc32 field description</v>
       </c>
       <c r="AN3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(AN237), LOWER(AN2))</f>
-        <v>controlled vocabulary</v>
+        <f t="shared" si="0"/>
+        <v>ena erc32 controlled vocabulary</v>
       </c>
       <c r="AO3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(AO237), LOWER(AO2))</f>
-        <v>field type</v>
+        <f t="shared" si="0"/>
+        <v>ena erc32 field type</v>
       </c>
       <c r="AP3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(AP237), LOWER(AP2))</f>
-        <v>field description</v>
+        <f t="shared" si="0"/>
+        <v>ena erc33 field description</v>
       </c>
       <c r="AQ3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(AQ237), LOWER(AQ2))</f>
-        <v>controlled vocabulary</v>
+        <f t="shared" si="0"/>
+        <v>ena erc33 controlled vocabulary</v>
       </c>
       <c r="AR3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(AR237), LOWER(AR2))</f>
-        <v>field type</v>
+        <f t="shared" si="0"/>
+        <v>ena erc33 field type</v>
       </c>
       <c r="AS3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(AS237), LOWER(AS2))</f>
-        <v>submission requiredness</v>
+        <f t="shared" si="0"/>
+        <v>ena submission requiredness</v>
       </c>
       <c r="AT3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(AT237), LOWER(AT2))</f>
-        <v>submission requiredness</v>
-      </c>
-      <c r="AU3" s="46" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(AU237), LOWER(AU2))</f>
-        <v>example</v>
+        <f t="shared" si="0"/>
+        <v>vjdb submission requiredness</v>
+      </c>
+      <c r="AU3" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>vjdb example</v>
       </c>
       <c r="AV3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(AV237), LOWER(AV2))</f>
-        <v>validation rules</v>
+        <f t="shared" si="0"/>
+        <v>vjdb validation rules</v>
       </c>
       <c r="AW3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(AW237), LOWER(AW2))</f>
-        <v>submission fieldtype</v>
+        <f t="shared" si="0"/>
+        <v>ena submission fieldtype</v>
       </c>
       <c r="AX3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(AX237), LOWER(AX2))</f>
-        <v>submission validation</v>
+        <f t="shared" si="0"/>
+        <v>ena submission validation</v>
       </c>
       <c r="AY3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(AY237), LOWER(AY2))</f>
-        <v>i field name</v>
+        <f t="shared" si="0"/>
+        <v>ictv40 i field name</v>
       </c>
       <c r="AZ3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(AZ237), LOWER(AZ2))</f>
-        <v>accessions link i field heading</v>
+        <f t="shared" si="0"/>
+        <v>ictv_msl41.v1 i field heading</v>
       </c>
       <c r="BA3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(BA237), LOWER(BA2))</f>
-        <v>link to the genbank record(s) in columns x. i field description</v>
+        <f t="shared" si="0"/>
+        <v>ictv_msl41.v1 i field description</v>
       </c>
       <c r="BB3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(BB237), LOWER(BB2))</f>
-        <v>facet fields</v>
+        <f t="shared" si="0"/>
+        <v>vjdbv1.1 facet fields</v>
       </c>
       <c r="BC3" s="44" t="str">
-        <f>_xlfn.TEXTJOIN(" ", TRUE, LOWER(BC237), LOWER(BC2))</f>
-        <v>default search</v>
+        <f t="shared" si="0"/>
+        <v>vjdbv1.1 default search</v>
       </c>
     </row>
     <row r="4" spans="1:180" s="69" customFormat="1" ht="25.5" customHeight="1">
       <c r="A4" s="44" t="str">
         <f>SUBSTITUTE(A3, " ", "_")</f>
-        <v>0iy_field_index</v>
+        <v>vjdbv1.1_field_index</v>
       </c>
       <c r="B4" s="44" t="str">
         <f>SUBSTITUTE(B3, " ", "_")</f>
-        <v>sequence_url_field_id</v>
+        <v>vjdbv1.1_field_id</v>
       </c>
       <c r="C4" s="44" t="str">
         <f>SUBSTITUTE(C3, " ", "_")</f>
-        <v>genbank_url_name</v>
+        <v>vjdbv1.1_name</v>
       </c>
       <c r="D4" s="70" t="str">
         <f>SUBSTITUTE(D3, " ", "_")</f>
-        <v>url_to_the_genbank_record_from_the_ictv_vmr_description</v>
+        <v>vjdbv1.1_description</v>
       </c>
       <c r="E4" s="45" t="str">
         <f>SUBSTITUTE(E3, " ", "_")</f>
-        <v>keyword_fields_type</v>
+        <v>vjdbv1.1_fields_type</v>
       </c>
       <c r="F4" s="44" t="str">
         <f>SUBSTITUTE(F3, " ", "_")</f>
-        <v>private_privacy</v>
+        <v>vjdbv1.1_privacy</v>
       </c>
       <c r="G4" s="44" t="str">
         <f>SUBSTITUTE(G3, " ", "_")</f>
-        <v>field_id</v>
+        <v>ena_field_id</v>
       </c>
       <c r="H4" s="44" t="str">
         <f>SUBSTITUTE(H3, " ", "_")</f>
-        <v>field_id</v>
+        <v>rki_field_id</v>
       </c>
       <c r="I4" s="44" t="str">
         <f>SUBSTITUTE(I3, " ", "_")</f>
-        <v>field_id</v>
+        <v>migs-vi_field_id</v>
       </c>
       <c r="J4" s="44" t="str">
         <f>SUBSTITUTE(J3, " ", "_")</f>
-        <v>field_id</v>
+        <v>migs-uvig_field_id</v>
       </c>
       <c r="K4" s="44" t="str">
         <f>SUBSTITUTE(K3, " ", "_")</f>
-        <v>field_id</v>
+        <v>env-o_field_id</v>
       </c>
       <c r="L4" s="44" t="str">
         <f>SUBSTITUTE(L3, " ", "_")</f>
-        <v>n_nucleotide_field_id</v>
+        <v>ncbi_virus_n_nucleotide_field_id</v>
       </c>
       <c r="M4" s="44" t="str">
         <f>SUBSTITUTE(M3, " ", "_")</f>
-        <v>b_field_name</v>
+        <v>bv-brc_b_field_name</v>
       </c>
       <c r="N4" s="44" t="str">
         <f>SUBSTITUTE(N3, " ", "_")</f>
-        <v>field_name</v>
+        <v>ena_erc32_field_name</v>
       </c>
       <c r="O4" s="44" t="str">
         <f>SUBSTITUTE(O3, " ", "_")</f>
-        <v>field_name</v>
+        <v>ena_erc33_field_name</v>
       </c>
       <c r="P4" s="44" t="str">
         <f>SUBSTITUTE(P3, " ", "_")</f>
-        <v>field_name</v>
+        <v>img/vr_field_name</v>
       </c>
       <c r="Q4" s="44" t="str">
         <f>SUBSTITUTE(Q3, " ", "_")</f>
-        <v>field_name</v>
+        <v>phd_field_name</v>
       </c>
       <c r="R4" s="44" t="str">
         <f>SUBSTITUTE(R3, " ", "_")</f>
-        <v>field_name</v>
+        <v>phispy_field_name</v>
       </c>
       <c r="S4" s="44" t="str">
         <f>SUBSTITUTE(S3, " ", "_")</f>
-        <v>field_name</v>
+        <v>gtdb_field_name</v>
       </c>
       <c r="T4" s="44" t="str">
         <f>SUBSTITUTE(T3, " ", "_")</f>
-        <v>object_name</v>
+        <v>ena_submission_object_object_name</v>
       </c>
       <c r="U4" s="44" t="str">
         <f>SUBSTITUTE(U3, " ", "_")</f>
-        <v>object_name</v>
+        <v>vjbd_submission_object_object_name</v>
       </c>
       <c r="V4" s="44" t="str">
         <f>SUBSTITUTE(V3, " ", "_")</f>
-        <v>group1</v>
+        <v>vjdbv1.1_group1</v>
       </c>
       <c r="W4" s="44" t="str">
         <f>SUBSTITUTE(W3, " ", "_")</f>
-        <v>group2</v>
+        <v>vjdbv1.1_group2</v>
       </c>
       <c r="X4" s="44" t="str">
         <f>SUBSTITUTE(X3, " ", "_")</f>
-        <v>group3</v>
+        <v>vjdbv1.1_group3</v>
       </c>
       <c r="Y4" s="44" t="str">
         <f>SUBSTITUTE(Y3, " ", "_")</f>
-        <v>tags</v>
+        <v>vjdbv1.1_tags</v>
       </c>
       <c r="Z4" s="44" t="str">
         <f>SUBSTITUTE(Z3, " ", "_")</f>
-        <v>input_source</v>
+        <v>vjdbv1.1_input_source</v>
       </c>
       <c r="AA4" s="44" t="str">
         <f>SUBSTITUTE(AA3, " ", "_")</f>
-        <v>notes</v>
+        <v>vjdbv1.1_notes</v>
       </c>
       <c r="AB4" s="44" t="str">
         <f>SUBSTITUTE(AB3, " ", "_")</f>
-        <v>changes</v>
+        <v>vjdbv1.1_changes</v>
       </c>
       <c r="AC4" s="44" t="str">
         <f>SUBSTITUTE(AC3, " ", "_")</f>
-        <v>n_field_name</v>
+        <v>ncbi_virus_n_field_name</v>
       </c>
       <c r="AD4" s="44" t="str">
         <f>SUBSTITUTE(AD3, " ", "_")</f>
-        <v>n_field_description</v>
+        <v>ncbi_virus_n_field_description</v>
       </c>
       <c r="AE4" s="44" t="str">
         <f>SUBSTITUTE(AE3, " ", "_")</f>
-        <v>n_type</v>
+        <v>ncbi_virus_n_type</v>
       </c>
       <c r="AF4" s="44" t="str">
         <f>SUBSTITUTE(AF3, " ", "_")</f>
-        <v>n_curation_notes</v>
+        <v>ncbi_virus_n_curation_notes</v>
       </c>
       <c r="AG4" s="44" t="str">
         <f>SUBSTITUTE(AG3, " ", "_")</f>
-        <v>b_category</v>
+        <v>bv-brc_b_category</v>
       </c>
       <c r="AH4" s="44" t="str">
         <f>SUBSTITUTE(AH3, " ", "_")</f>
-        <v>b_schema_category</v>
+        <v>bv-brc_b_schema_category</v>
       </c>
       <c r="AI4" s="44" t="str">
         <f>SUBSTITUTE(AI3, " ", "_")</f>
-        <v>b_field_id</v>
+        <v>bv-brc_b_field_id</v>
       </c>
       <c r="AJ4" s="44" t="str">
         <f>SUBSTITUTE(AJ3, " ", "_")</f>
-        <v>b_field_type</v>
+        <v>bv-brc_b_field_type</v>
       </c>
       <c r="AK4" s="44" t="str">
         <f>SUBSTITUTE(AK3, " ", "_")</f>
-        <v>b_type</v>
+        <v>bv-brc_b_type</v>
       </c>
       <c r="AL4" s="44" t="str">
         <f>SUBSTITUTE(AL3, " ", "_")</f>
-        <v>b_curation_notes</v>
+        <v>bv-brc_b_curation_notes</v>
       </c>
       <c r="AM4" s="44" t="str">
         <f>SUBSTITUTE(AM3, " ", "_")</f>
-        <v>field_description</v>
+        <v>ena_erc32_field_description</v>
       </c>
       <c r="AN4" s="44" t="str">
         <f>SUBSTITUTE(AN3, " ", "_")</f>
-        <v>controlled_vocabulary</v>
+        <v>ena_erc32_controlled_vocabulary</v>
       </c>
       <c r="AO4" s="44" t="str">
         <f>SUBSTITUTE(AO3, " ", "_")</f>
-        <v>field_type</v>
+        <v>ena_erc32_field_type</v>
       </c>
       <c r="AP4" s="44" t="str">
         <f>SUBSTITUTE(AP3, " ", "_")</f>
-        <v>field_description</v>
+        <v>ena_erc33_field_description</v>
       </c>
       <c r="AQ4" s="44" t="str">
         <f>SUBSTITUTE(AQ3, " ", "_")</f>
-        <v>controlled_vocabulary</v>
+        <v>ena_erc33_controlled_vocabulary</v>
       </c>
       <c r="AR4" s="44" t="str">
         <f>SUBSTITUTE(AR3, " ", "_")</f>
-        <v>field_type</v>
+        <v>ena_erc33_field_type</v>
       </c>
       <c r="AS4" s="44" t="str">
         <f>SUBSTITUTE(AS3, " ", "_")</f>
-        <v>submission_requiredness</v>
+        <v>ena_submission_requiredness</v>
       </c>
       <c r="AT4" s="44" t="str">
         <f>SUBSTITUTE(AT3, " ", "_")</f>
-        <v>submission_requiredness</v>
+        <v>vjdb_submission_requiredness</v>
       </c>
       <c r="AU4" s="46" t="str">
         <f>SUBSTITUTE(AU3, " ", "_")</f>
-        <v>example</v>
+        <v>vjdb_example</v>
       </c>
       <c r="AV4" s="44" t="str">
         <f>SUBSTITUTE(AV3, " ", "_")</f>
-        <v>validation_rules</v>
+        <v>vjdb_validation_rules</v>
       </c>
       <c r="AW4" s="44" t="str">
         <f>SUBSTITUTE(AW3, " ", "_")</f>
-        <v>submission_fieldtype</v>
+        <v>ena_submission_fieldtype</v>
       </c>
       <c r="AX4" s="44" t="str">
         <f>SUBSTITUTE(AX3, " ", "_")</f>
-        <v>submission_validation</v>
+        <v>ena_submission_validation</v>
       </c>
       <c r="AY4" s="44" t="str">
         <f>SUBSTITUTE(AY3, " ", "_")</f>
-        <v>i_field_name</v>
+        <v>ictv40_i_field_name</v>
       </c>
       <c r="AZ4" s="44" t="str">
         <f>SUBSTITUTE(AZ3, " ", "_")</f>
-        <v>accessions_link_i_field_heading</v>
+        <v>ictv_msl41.v1_i_field_heading</v>
       </c>
       <c r="BA4" s="44" t="str">
         <f>SUBSTITUTE(BA3, " ", "_")</f>
-        <v>link_to_the_genbank_record(s)_in_columns_x._i_field_description</v>
+        <v>ictv_msl41.v1_i_field_description</v>
       </c>
       <c r="BB4" s="44" t="str">
         <f>SUBSTITUTE(BB3, " ", "_")</f>
-        <v>facet_fields</v>
+        <v>vjdbv1.1_facet_fields</v>
       </c>
       <c r="BC4" s="44" t="str">
         <f>SUBSTITUTE(BC3, " ", "_")</f>
-        <v>default_search</v>
+        <v>vjdbv1.1_default_search</v>
       </c>
     </row>
     <row r="5" spans="1:180" s="49" customFormat="1" ht="25.5" customHeight="1">
@@ -46513,10 +46513,10 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:BC237">
     <sortCondition ref="A5:A237"/>
   </sortState>
-  <conditionalFormatting sqref="A8:B1048576 A2:B4 A5:A7 A1">
+  <conditionalFormatting sqref="A8:B1048576 A5:A7 A1 A2:B4 C3:BC3">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E1048576">
+  <conditionalFormatting sqref="E1:E2 E4:E1048576">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"boolean"</formula>
     </cfRule>

--- a/metadata.xlsx
+++ b/metadata.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30219"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A1A69F9-98B8-4B5B-9097-C46B2CEC129E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC7CB448-705B-4C79-91AC-B0DD7B347339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -237,7 +237,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5034" uniqueCount="1804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5034" uniqueCount="1805">
   <si>
     <t>VJDBv1.1</t>
   </si>
@@ -4483,13 +4483,16 @@
     <t>0he</t>
   </si>
   <si>
-    <t>updated_fields</t>
-  </si>
-  <si>
-    <t>Updated Fields</t>
+    <t>change_log</t>
+  </si>
+  <si>
+    <t>Change Log</t>
   </si>
   <si>
     <t>List of VirJenDB metadata fields and their content when they are updated in each release in compare to the previous version</t>
+  </si>
+  <si>
+    <t>nested</t>
   </si>
   <si>
     <t>0hf</t>
@@ -41926,7 +41929,7 @@
         <v>1402</v>
       </c>
       <c r="E191" s="54" t="s">
-        <v>76</v>
+        <v>1403</v>
       </c>
       <c r="F191" s="54" t="s">
         <v>154</v>
@@ -42009,16 +42012,16 @@
     </row>
     <row r="192" spans="1:55" ht="25.5" customHeight="1">
       <c r="A192" s="64" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="B192" s="64" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="C192" s="54" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="D192" s="71" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="E192" s="54" t="s">
         <v>76</v>
@@ -42106,16 +42109,16 @@
     </row>
     <row r="193" spans="1:55" ht="25.5" customHeight="1">
       <c r="A193" s="64" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="B193" s="64" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="C193" s="54" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="D193" s="73" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="E193" s="54" t="s">
         <v>76</v>
@@ -42133,16 +42136,16 @@
       <c r="N193" s="54"/>
       <c r="O193" s="54"/>
       <c r="P193" s="60" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="Q193" s="60" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="R193" s="60" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="S193" s="60" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="T193" s="54"/>
       <c r="U193" s="54"/>
@@ -42153,7 +42156,7 @@
         <v>205</v>
       </c>
       <c r="X193" s="52" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="Y193" s="54" t="str">
         <f>"[" &amp; _xlfn.TEXTJOIN(", ", TRUE,
@@ -42179,7 +42182,7 @@
         <v>["IMG/VR", "PHD", "PhiSpy", "GTDB", "Host", "Host Taxonomy", "GTDB Taxonomy"]</v>
       </c>
       <c r="Z193" s="54" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="AA193" s="54"/>
       <c r="AB193" s="54"/>
@@ -42211,16 +42214,16 @@
     </row>
     <row r="194" spans="1:55" ht="25.5" customHeight="1">
       <c r="A194" s="64" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="B194" s="64" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="C194" s="54" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="D194" s="71" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="E194" s="54" t="s">
         <v>63</v>
@@ -42274,7 +42277,7 @@
         <v>["Internal", "Workflows"]</v>
       </c>
       <c r="Z194" s="54" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="AA194" s="54"/>
       <c r="AB194" s="54"/>
@@ -42306,16 +42309,16 @@
     </row>
     <row r="195" spans="1:55" ht="25.5" customHeight="1">
       <c r="A195" s="64" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="B195" s="64" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="C195" s="54" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="D195" s="71" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="E195" s="54" t="s">
         <v>63</v>
@@ -42401,16 +42404,16 @@
     </row>
     <row r="196" spans="1:55" ht="25.5" customHeight="1">
       <c r="A196" s="64" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B196" s="64" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="C196" s="54" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="D196" s="71" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="E196" s="54" t="s">
         <v>162</v>
@@ -42499,16 +42502,16 @@
     </row>
     <row r="197" spans="1:55" ht="25.5" customHeight="1">
       <c r="A197" s="64" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B197" s="64" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="C197" s="54" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="D197" s="71" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="E197" s="54" t="s">
         <v>63</v>
@@ -42596,16 +42599,16 @@
     </row>
     <row r="198" spans="1:55" ht="25.5" customHeight="1">
       <c r="A198" s="64" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B198" s="64" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="C198" s="54" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="D198" s="71" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="E198" s="54" t="s">
         <v>162</v>
@@ -42694,16 +42697,16 @@
     </row>
     <row r="199" spans="1:55" ht="25.5" customHeight="1">
       <c r="A199" s="64" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B199" s="64" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="C199" s="54" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="D199" s="71" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="E199" s="54" t="s">
         <v>63</v>
@@ -42787,16 +42790,16 @@
     </row>
     <row r="200" spans="1:55" ht="25.5" customHeight="1">
       <c r="A200" s="64" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="B200" s="64" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="C200" s="54" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="D200" s="71" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="E200" s="54" t="s">
         <v>76</v>
@@ -42850,7 +42853,7 @@
         <v>["Analysis", "Workflows"]</v>
       </c>
       <c r="Z200" s="54" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="AA200" s="54"/>
       <c r="AB200" s="54"/>
@@ -42882,16 +42885,16 @@
     </row>
     <row r="201" spans="1:55" ht="25.5" customHeight="1">
       <c r="A201" s="64" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B201" s="64" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="C201" s="54" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="D201" s="71" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="E201" s="54" t="s">
         <v>63</v>
@@ -42909,11 +42912,11 @@
       <c r="N201" s="54"/>
       <c r="O201" s="54"/>
       <c r="P201" s="60" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="Q201" s="60"/>
       <c r="R201" s="60" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="S201" s="54"/>
       <c r="T201" s="54"/>
@@ -42984,16 +42987,16 @@
     </row>
     <row r="202" spans="1:55" ht="25.5" customHeight="1">
       <c r="A202" s="64" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="B202" s="64" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="C202" s="54" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="D202" s="71" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="E202" s="54" t="s">
         <v>76</v>
@@ -43011,11 +43014,11 @@
       <c r="N202" s="54"/>
       <c r="O202" s="54"/>
       <c r="P202" s="60" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="Q202" s="60"/>
       <c r="R202" s="60" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="S202" s="54"/>
       <c r="T202" s="53"/>
@@ -43051,7 +43054,7 @@
         <v>["IMG/VR", "PhiSpy", "Host", "Workflows"]</v>
       </c>
       <c r="Z202" s="54" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="AA202" s="54"/>
       <c r="AB202" s="54"/>
@@ -43085,16 +43088,16 @@
     </row>
     <row r="203" spans="1:55" ht="25.5" customHeight="1">
       <c r="A203" s="64" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="B203" s="64" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="C203" s="54" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="D203" s="71" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="E203" s="54" t="s">
         <v>63</v>
@@ -43112,11 +43115,11 @@
       <c r="N203" s="54"/>
       <c r="O203" s="54"/>
       <c r="P203" s="60" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="Q203" s="60"/>
       <c r="R203" s="60" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="S203" s="54"/>
       <c r="T203" s="53"/>
@@ -43152,7 +43155,7 @@
         <v>["IMG/VR", "PhiSpy", "Host", "Identifiers"]</v>
       </c>
       <c r="Z203" s="54" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="AA203" s="54"/>
       <c r="AB203" s="54"/>
@@ -43184,16 +43187,16 @@
     </row>
     <row r="204" spans="1:55" ht="25.5" customHeight="1">
       <c r="A204" s="64" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="B204" s="64" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="C204" s="54" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="D204" s="71" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="E204" s="54" t="s">
         <v>63</v>
@@ -43211,11 +43214,11 @@
       <c r="N204" s="54"/>
       <c r="O204" s="54"/>
       <c r="P204" s="60" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="Q204" s="60"/>
       <c r="R204" s="60" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="S204" s="54"/>
       <c r="T204" s="53"/>
@@ -43251,7 +43254,7 @@
         <v>["IMG/VR", "PhiSpy", "Host", "Identifiers"]</v>
       </c>
       <c r="Z204" s="54" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="AA204" s="54"/>
       <c r="AB204" s="54"/>
@@ -43283,16 +43286,16 @@
     </row>
     <row r="205" spans="1:55" ht="25.5" customHeight="1">
       <c r="A205" s="64" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="B205" s="64" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="C205" s="54" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="D205" s="71" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="E205" s="54" t="s">
         <v>76</v>
@@ -43310,11 +43313,11 @@
       <c r="N205" s="54"/>
       <c r="O205" s="54"/>
       <c r="P205" s="60" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="Q205" s="60"/>
       <c r="R205" s="60" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="S205" s="54"/>
       <c r="T205" s="53"/>
@@ -43350,7 +43353,7 @@
         <v>["IMG/VR", "PhiSpy", "Host", "Collection"]</v>
       </c>
       <c r="Z205" s="54" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="AA205" s="54"/>
       <c r="AB205" s="54"/>
@@ -43386,16 +43389,16 @@
     </row>
     <row r="206" spans="1:55" ht="25.5" customHeight="1">
       <c r="A206" s="64" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B206" s="64" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="C206" s="54" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="D206" s="71" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="E206" s="54" t="s">
         <v>117</v>
@@ -43413,11 +43416,11 @@
       <c r="N206" s="54"/>
       <c r="O206" s="54"/>
       <c r="P206" s="60" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="Q206" s="60"/>
       <c r="R206" s="60" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="S206" s="54"/>
       <c r="T206" s="53"/>
@@ -43453,7 +43456,7 @@
         <v>["IMG/VR", "PhiSpy", "Host", "Collection"]</v>
       </c>
       <c r="Z206" s="54" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="AA206" s="54"/>
       <c r="AB206" s="54"/>
@@ -43476,7 +43479,7 @@
       <c r="AS206" s="54"/>
       <c r="AT206" s="54"/>
       <c r="AU206" s="55" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="AV206" s="54" t="s">
         <v>131</v>
@@ -43489,16 +43492,16 @@
     </row>
     <row r="207" spans="1:55" ht="25.5" customHeight="1">
       <c r="A207" s="64" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B207" s="64" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="C207" s="54" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="D207" s="74" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="E207" s="54" t="s">
         <v>63</v>
@@ -43516,7 +43519,7 @@
       <c r="N207" s="54"/>
       <c r="O207" s="54"/>
       <c r="P207" s="54" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="Q207" s="54"/>
       <c r="R207" s="54"/>
@@ -43554,7 +43557,7 @@
         <v>["IMG/VR", "Host", "Identifiers"]</v>
       </c>
       <c r="Z207" s="54" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="AA207" s="54"/>
       <c r="AB207" s="54"/>
@@ -43586,16 +43589,16 @@
     </row>
     <row r="208" spans="1:55" ht="25.5" customHeight="1">
       <c r="A208" s="51" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B208" s="51" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="C208" s="52" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="D208" s="72" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="E208" s="54" t="s">
         <v>63</v>
@@ -43613,13 +43616,13 @@
       <c r="N208" s="52"/>
       <c r="O208" s="52"/>
       <c r="P208" s="60" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="Q208" s="60" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="R208" s="60" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="S208" s="52"/>
       <c r="T208" s="52"/>
@@ -43658,7 +43661,7 @@
         <v>16</v>
       </c>
       <c r="AA208" s="52" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="AB208" s="52"/>
       <c r="AC208" s="52"/>
@@ -43691,16 +43694,16 @@
     </row>
     <row r="209" spans="1:53" ht="25.5" customHeight="1">
       <c r="A209" s="64" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="B209" s="64" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="C209" s="54" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="D209" s="71" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="E209" s="54" t="s">
         <v>254</v>
@@ -43718,11 +43721,11 @@
       <c r="N209" s="54"/>
       <c r="O209" s="54"/>
       <c r="P209" s="60" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="Q209" s="60"/>
       <c r="R209" s="60" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="S209" s="54"/>
       <c r="T209" s="54"/>
@@ -43758,7 +43761,7 @@
         <v>["IMG/VR", "PhiSpy", "Host", "Workflows"]</v>
       </c>
       <c r="Z209" s="54" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="AA209" s="54"/>
       <c r="AB209" s="54"/>
@@ -43794,16 +43797,16 @@
     </row>
     <row r="210" spans="1:53" ht="25.5" customHeight="1">
       <c r="A210" s="64" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B210" s="64" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="C210" s="54" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="D210" s="71" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="E210" s="54" t="s">
         <v>76</v>
@@ -43821,11 +43824,11 @@
       <c r="N210" s="54"/>
       <c r="O210" s="54"/>
       <c r="P210" s="60" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="Q210" s="60"/>
       <c r="R210" s="60" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="S210" s="54"/>
       <c r="T210" s="54"/>
@@ -43861,7 +43864,7 @@
         <v>["IMG/VR", "PhiSpy", "Workflows", "Host"]</v>
       </c>
       <c r="Z210" s="54" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="AA210" s="54"/>
       <c r="AB210" s="54"/>
@@ -43897,16 +43900,16 @@
     </row>
     <row r="211" spans="1:53" ht="25.5" customHeight="1">
       <c r="A211" s="64" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B211" s="64" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="C211" s="54" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="D211" s="71" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="E211" s="54" t="s">
         <v>63</v>
@@ -43992,16 +43995,16 @@
     </row>
     <row r="212" spans="1:53" ht="25.5" customHeight="1">
       <c r="A212" s="64" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B212" s="64" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="C212" s="54" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="D212" s="71" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="E212" s="54" t="s">
         <v>63</v>
@@ -44087,16 +44090,16 @@
     </row>
     <row r="213" spans="1:53" ht="25.5" customHeight="1">
       <c r="A213" s="64" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B213" s="64" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="C213" s="54" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="D213" s="71" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="E213" s="54" t="s">
         <v>63</v>
@@ -44182,16 +44185,16 @@
     </row>
     <row r="214" spans="1:53" ht="25.5" customHeight="1">
       <c r="A214" s="64" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B214" s="64" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="C214" s="54" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="D214" s="71" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="E214" s="54" t="s">
         <v>76</v>
@@ -44277,16 +44280,16 @@
     </row>
     <row r="215" spans="1:53" ht="25.5" customHeight="1">
       <c r="A215" s="64" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="B215" s="64" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="C215" s="54" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="D215" s="71" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="E215" s="54" t="s">
         <v>63</v>
@@ -44372,16 +44375,16 @@
     </row>
     <row r="216" spans="1:53" ht="25.5" customHeight="1">
       <c r="A216" s="64" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="B216" s="64" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="C216" s="54" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="D216" s="75" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="E216" s="54" t="s">
         <v>63</v>
@@ -44399,7 +44402,7 @@
       <c r="N216" s="54"/>
       <c r="O216" s="54"/>
       <c r="P216" s="54" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="Q216" s="54"/>
       <c r="R216" s="54"/>
@@ -44410,7 +44413,7 @@
         <v>204</v>
       </c>
       <c r="W216" s="54" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="X216" s="54"/>
       <c r="Y216" s="54" t="str">
@@ -44437,7 +44440,7 @@
         <v>["IMG/VR", "Host", "Identifier"]</v>
       </c>
       <c r="Z216" s="54" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="AA216" s="54"/>
       <c r="AB216" s="54"/>
@@ -44469,16 +44472,16 @@
     </row>
     <row r="217" spans="1:53" ht="25.5" customHeight="1">
       <c r="A217" s="64" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B217" s="64" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="C217" s="54" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="D217" s="75" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="E217" s="54" t="s">
         <v>162</v>
@@ -44557,10 +44560,10 @@
       <c r="AS217" s="54"/>
       <c r="AT217" s="54"/>
       <c r="AU217" s="55" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="AV217" s="54" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="AW217" s="54"/>
       <c r="AX217" s="54"/>
@@ -44570,16 +44573,16 @@
     </row>
     <row r="218" spans="1:53" ht="25.5" customHeight="1">
       <c r="A218" s="64" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="B218" s="64" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="C218" s="54" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="D218" s="71" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="E218" s="54" t="s">
         <v>76</v>
@@ -44597,11 +44600,11 @@
       <c r="N218" s="54"/>
       <c r="O218" s="54"/>
       <c r="P218" s="60" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="Q218" s="60"/>
       <c r="R218" s="60" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="S218" s="54"/>
       <c r="T218" s="54"/>
@@ -44669,16 +44672,16 @@
     </row>
     <row r="219" spans="1:53" ht="25.5" customHeight="1">
       <c r="A219" s="64" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="B219" s="64" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="C219" s="54" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="D219" s="71" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="E219" s="54" t="s">
         <v>254</v>
@@ -44696,11 +44699,11 @@
       <c r="N219" s="54"/>
       <c r="O219" s="54"/>
       <c r="P219" s="60" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="Q219" s="60"/>
       <c r="R219" s="60" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="S219" s="54"/>
       <c r="T219" s="54"/>
@@ -44768,16 +44771,16 @@
     </row>
     <row r="220" spans="1:53" ht="25.5" customHeight="1">
       <c r="A220" s="64" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="B220" s="64" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="C220" s="54" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="D220" s="71" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="E220" s="54" t="s">
         <v>76</v>
@@ -44865,16 +44868,16 @@
     </row>
     <row r="221" spans="1:53" ht="25.5" customHeight="1">
       <c r="A221" s="64" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="B221" s="64" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="C221" s="54" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="D221" s="71" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="E221" s="54" t="s">
         <v>76</v>
@@ -44962,16 +44965,16 @@
     </row>
     <row r="222" spans="1:53" ht="25.5" customHeight="1">
       <c r="A222" s="64" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="B222" s="64" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="C222" s="54" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="D222" s="71" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="E222" s="54" t="s">
         <v>76</v>
@@ -45059,16 +45062,16 @@
     </row>
     <row r="223" spans="1:53" ht="25.5" customHeight="1">
       <c r="A223" s="64" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B223" s="64" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="C223" s="54" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="D223" s="71" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="E223" s="54" t="s">
         <v>76</v>
@@ -45156,16 +45159,16 @@
     </row>
     <row r="224" spans="1:53" ht="25.5" customHeight="1">
       <c r="A224" s="64" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="B224" s="64" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="C224" s="54" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="D224" s="71" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="E224" s="54" t="s">
         <v>216</v>
@@ -45251,16 +45254,16 @@
     </row>
     <row r="225" spans="1:53" ht="25.5" customHeight="1">
       <c r="A225" s="64" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B225" s="64" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="C225" s="66" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="D225" s="71" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="E225" s="54" t="s">
         <v>63</v>
@@ -45346,16 +45349,16 @@
     </row>
     <row r="226" spans="1:53" ht="25.5" customHeight="1">
       <c r="A226" s="64" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B226" s="64" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="C226" s="54" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="D226" s="71" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="E226" s="54" t="s">
         <v>216</v>
@@ -45441,16 +45444,16 @@
     </row>
     <row r="227" spans="1:53" ht="25.5" customHeight="1">
       <c r="A227" s="64" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="B227" s="64" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="C227" s="54" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="D227" s="71" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="E227" s="54" t="s">
         <v>216</v>
@@ -45536,16 +45539,16 @@
     </row>
     <row r="228" spans="1:53" ht="25.5" customHeight="1">
       <c r="A228" s="64" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B228" s="64" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="C228" s="54" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="D228" s="71" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="E228" s="54" t="s">
         <v>216</v>
@@ -45631,16 +45634,16 @@
     </row>
     <row r="229" spans="1:53" ht="25.5" customHeight="1">
       <c r="A229" s="64" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B229" s="64" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="C229" s="54" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="D229" s="71" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="E229" s="54" t="s">
         <v>216</v>
@@ -45726,16 +45729,16 @@
     </row>
     <row r="230" spans="1:53" ht="25.5" customHeight="1">
       <c r="A230" s="64" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="B230" s="64" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="C230" s="54" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="D230" s="71" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="E230" s="54" t="s">
         <v>63</v>
@@ -45821,16 +45824,16 @@
     </row>
     <row r="231" spans="1:53" ht="25.5" customHeight="1">
       <c r="A231" s="64" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="B231" s="64" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="C231" s="54" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="D231" s="71" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="E231" s="54" t="s">
         <v>63</v>
@@ -45916,16 +45919,16 @@
     </row>
     <row r="232" spans="1:53" ht="25.5" customHeight="1">
       <c r="A232" s="64" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B232" s="64" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="C232" s="54" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="D232" s="71" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="E232" s="54" t="s">
         <v>254</v>
@@ -46011,16 +46014,16 @@
     </row>
     <row r="233" spans="1:53" ht="25.5" customHeight="1">
       <c r="A233" s="64" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B233" s="64" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="C233" s="54" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="D233" s="71" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="E233" s="54" t="s">
         <v>76</v>
@@ -46106,16 +46109,16 @@
     </row>
     <row r="234" spans="1:53" ht="25.5" customHeight="1">
       <c r="A234" s="64" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B234" s="64" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="C234" s="54" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="D234" s="71" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="E234" s="54" t="s">
         <v>254</v>
@@ -46201,16 +46204,16 @@
     </row>
     <row r="235" spans="1:53" ht="25.5" customHeight="1">
       <c r="A235" s="64" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B235" s="64" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="C235" s="54" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="D235" s="71" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="E235" s="54" t="s">
         <v>216</v>
@@ -46296,16 +46299,16 @@
     </row>
     <row r="236" spans="1:53" ht="25.5" customHeight="1">
       <c r="A236" s="64" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="B236" s="64" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="C236" s="54" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="D236" s="71" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="E236" s="54" t="s">
         <v>63</v>
@@ -46391,16 +46394,16 @@
     </row>
     <row r="237" spans="1:53" ht="25.5" customHeight="1">
       <c r="A237" s="64" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B237" s="64" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="C237" s="54" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="D237" s="71" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="E237" s="54" t="s">
         <v>63</v>
@@ -46454,10 +46457,10 @@
       <c r="AX237" s="54"/>
       <c r="AY237" s="54"/>
       <c r="AZ237" s="56" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="BA237" s="57" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
     </row>
   </sheetData>
@@ -46492,25 +46495,25 @@
   <sheetData>
     <row r="1" spans="1:172" s="19" customFormat="1" ht="23.25" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="H1" s="18" t="s">
         <v>1</v>
@@ -46543,25 +46546,25 @@
         <v>14</v>
       </c>
       <c r="R1" s="20" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="S1" s="20" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="T1" s="20" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="U1" s="20" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="V1" s="20" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="W1" s="20" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="X1" s="18" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="Y1" s="20" t="s">
         <v>6</v>
@@ -46761,13 +46764,13 @@
         <v>22</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="E2" s="19" t="s">
         <v>24</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="G2" s="18" t="s">
         <v>20</v>
@@ -46821,7 +46824,7 @@
         <v>35</v>
       </c>
       <c r="X2" s="19" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="Y2" s="19" t="s">
         <v>36</v>
@@ -47656,7 +47659,7 @@
         <v>359</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X5" s="8"/>
       <c r="Y5" s="8"/>
@@ -47666,14 +47669,14 @@
       <c r="AC5" s="8"/>
       <c r="AD5" s="8"/>
       <c r="AE5" s="2" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="AF5" s="2" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="AG5" s="8"/>
       <c r="AH5" s="9" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI5" s="8"/>
       <c r="AJ5" s="8"/>
@@ -47700,7 +47703,7 @@
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
@@ -47725,7 +47728,7 @@
         <v>359</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X6" s="13"/>
       <c r="Y6" s="13"/>
@@ -47737,14 +47740,14 @@
       </c>
       <c r="AD6" s="13"/>
       <c r="AE6" s="1" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="AF6" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG6" s="13"/>
       <c r="AH6" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI6" s="13"/>
       <c r="AJ6" s="13"/>
@@ -47794,7 +47797,7 @@
         <v>359</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X7" s="13"/>
       <c r="Y7" s="13"/>
@@ -47806,14 +47809,14 @@
         <v>127</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="AF7" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG7" s="13"/>
       <c r="AH7" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI7" s="13"/>
       <c r="AJ7" s="13"/>
@@ -47863,7 +47866,7 @@
         <v>359</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X8" s="13"/>
       <c r="Y8" s="13"/>
@@ -47873,14 +47876,14 @@
       <c r="AC8" s="13"/>
       <c r="AD8" s="13"/>
       <c r="AE8" s="1" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="AF8" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG8" s="13"/>
       <c r="AH8" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI8" s="13"/>
       <c r="AJ8" s="13"/>
@@ -47930,7 +47933,7 @@
         <v>359</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X9" s="13"/>
       <c r="Y9" s="13"/>
@@ -47940,14 +47943,14 @@
       <c r="AC9" s="13"/>
       <c r="AD9" s="13"/>
       <c r="AE9" s="1" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="AF9" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG9" s="13"/>
       <c r="AH9" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI9" s="13"/>
       <c r="AJ9" s="13"/>
@@ -47974,7 +47977,7 @@
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="O10" s="6"/>
       <c r="P10" s="6"/>
@@ -47999,7 +48002,7 @@
         <v>359</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X10" s="13"/>
       <c r="Y10" s="13"/>
@@ -48011,14 +48014,14 @@
       </c>
       <c r="AD10" s="13"/>
       <c r="AE10" s="1" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="AF10" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG10" s="13"/>
       <c r="AH10" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI10" s="13"/>
       <c r="AJ10" s="13"/>
@@ -48045,7 +48048,7 @@
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
@@ -48070,7 +48073,7 @@
         <v>359</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X11" s="13"/>
       <c r="Y11" s="13"/>
@@ -48082,14 +48085,14 @@
       </c>
       <c r="AD11" s="13"/>
       <c r="AE11" s="1" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="AF11" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG11" s="13"/>
       <c r="AH11" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI11" s="13"/>
       <c r="AJ11" s="13"/>
@@ -48139,7 +48142,7 @@
         <v>359</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X12" s="13"/>
       <c r="Y12" s="13"/>
@@ -48149,14 +48152,14 @@
       <c r="AC12" s="13"/>
       <c r="AD12" s="13"/>
       <c r="AE12" s="1" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="AF12" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG12" s="13"/>
       <c r="AH12" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI12" s="13"/>
       <c r="AJ12" s="13"/>
@@ -48206,7 +48209,7 @@
         <v>359</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X13" s="13"/>
       <c r="Y13" s="13"/>
@@ -48216,14 +48219,14 @@
       <c r="AC13" s="13"/>
       <c r="AD13" s="13"/>
       <c r="AE13" s="1" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="AF13" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG13" s="13"/>
       <c r="AH13" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI13" s="13"/>
       <c r="AJ13" s="13"/>
@@ -48250,7 +48253,7 @@
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
@@ -48275,7 +48278,7 @@
         <v>359</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X14" s="13"/>
       <c r="Y14" s="13"/>
@@ -48283,20 +48286,20 @@
       <c r="AA14" s="13"/>
       <c r="AB14" s="13"/>
       <c r="AC14" s="1" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="AD14" s="1" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="AE14" s="1" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="AF14" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG14" s="13"/>
       <c r="AH14" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI14" s="13"/>
       <c r="AJ14" s="13"/>
@@ -48346,7 +48349,7 @@
         <v>359</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X15" s="13"/>
       <c r="Y15" s="13"/>
@@ -48355,17 +48358,17 @@
       <c r="AB15" s="13"/>
       <c r="AC15" s="13"/>
       <c r="AD15" s="1" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="AF15" s="1" t="s">
         <v>254</v>
       </c>
       <c r="AG15" s="13"/>
       <c r="AH15" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI15" s="13"/>
       <c r="AJ15" s="13"/>
@@ -48415,7 +48418,7 @@
         <v>359</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X16" s="13"/>
       <c r="Y16" s="13"/>
@@ -48425,14 +48428,14 @@
       <c r="AC16" s="13"/>
       <c r="AD16" s="13"/>
       <c r="AE16" s="1" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="AF16" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG16" s="13"/>
       <c r="AH16" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI16" s="13"/>
       <c r="AJ16" s="13"/>
@@ -48459,7 +48462,7 @@
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
       <c r="N17" s="4" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="O17" s="6"/>
       <c r="P17" s="6"/>
@@ -48484,7 +48487,7 @@
         <v>359</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X17" s="13"/>
       <c r="Y17" s="13"/>
@@ -48492,20 +48495,20 @@
       <c r="AA17" s="13"/>
       <c r="AB17" s="13"/>
       <c r="AC17" s="1" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="AD17" s="1" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="AE17" s="1" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="AF17" s="1" t="s">
         <v>254</v>
       </c>
       <c r="AG17" s="13"/>
       <c r="AH17" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI17" s="13"/>
       <c r="AJ17" s="13"/>
@@ -48532,7 +48535,7 @@
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
       <c r="N18" s="4" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="O18" s="6"/>
       <c r="P18" s="6"/>
@@ -48557,7 +48560,7 @@
         <v>359</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X18" s="13"/>
       <c r="Y18" s="13"/>
@@ -48565,20 +48568,20 @@
       <c r="AA18" s="13"/>
       <c r="AB18" s="13"/>
       <c r="AC18" s="1" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="AD18" s="1" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="AE18" s="1" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="AF18" s="1" t="s">
         <v>254</v>
       </c>
       <c r="AG18" s="13"/>
       <c r="AH18" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI18" s="13"/>
       <c r="AJ18" s="13"/>
@@ -48605,7 +48608,7 @@
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
       <c r="N19" s="4" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="O19" s="6"/>
       <c r="P19" s="6"/>
@@ -48630,7 +48633,7 @@
         <v>359</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X19" s="13"/>
       <c r="Y19" s="13"/>
@@ -48644,14 +48647,14 @@
         <v>222</v>
       </c>
       <c r="AE19" s="1" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="AF19" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG19" s="13"/>
       <c r="AH19" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI19" s="13"/>
       <c r="AJ19" s="13"/>
@@ -48678,7 +48681,7 @@
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
       <c r="N20" s="4" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="O20" s="6"/>
       <c r="P20" s="6"/>
@@ -48703,7 +48706,7 @@
         <v>359</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X20" s="13"/>
       <c r="Y20" s="13"/>
@@ -48715,14 +48718,14 @@
       </c>
       <c r="AD20" s="13"/>
       <c r="AE20" s="1" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="AF20" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG20" s="13"/>
       <c r="AH20" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI20" s="13"/>
       <c r="AJ20" s="13"/>
@@ -48794,7 +48797,7 @@
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
       <c r="N22" s="4" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="O22" s="6"/>
       <c r="P22" s="6"/>
@@ -48819,7 +48822,7 @@
         <v>359</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X22" s="13"/>
       <c r="Y22" s="13"/>
@@ -48827,20 +48830,20 @@
       <c r="AA22" s="13"/>
       <c r="AB22" s="13"/>
       <c r="AC22" s="1" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="AD22" s="1" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="AE22" s="1" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="AF22" s="1" t="s">
         <v>254</v>
       </c>
       <c r="AG22" s="13"/>
       <c r="AH22" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI22" s="13"/>
       <c r="AJ22" s="13"/>
@@ -48867,7 +48870,7 @@
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
       <c r="N23" s="4" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="O23" s="6"/>
       <c r="P23" s="6"/>
@@ -48892,7 +48895,7 @@
         <v>359</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X23" s="13"/>
       <c r="Y23" s="13"/>
@@ -48906,14 +48909,14 @@
         <v>127</v>
       </c>
       <c r="AE23" s="1" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="AF23" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG23" s="13"/>
       <c r="AH23" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI23" s="13"/>
       <c r="AJ23" s="13"/>
@@ -48940,7 +48943,7 @@
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
       <c r="N24" s="4" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="O24" s="6"/>
       <c r="P24" s="6"/>
@@ -48965,7 +48968,7 @@
         <v>359</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X24" s="13"/>
       <c r="Y24" s="13"/>
@@ -48977,14 +48980,14 @@
       </c>
       <c r="AD24" s="13"/>
       <c r="AE24" s="1" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="AF24" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG24" s="13"/>
       <c r="AH24" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI24" s="13"/>
       <c r="AJ24" s="13"/>
@@ -49034,7 +49037,7 @@
         <v>359</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X25" s="13"/>
       <c r="Y25" s="13"/>
@@ -49044,14 +49047,14 @@
       <c r="AC25" s="13"/>
       <c r="AD25" s="13"/>
       <c r="AE25" s="1" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="AF25" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG25" s="13"/>
       <c r="AH25" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI25" s="13"/>
       <c r="AJ25" s="13"/>
@@ -49078,7 +49081,7 @@
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
       <c r="N26" s="4" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="O26" s="6"/>
       <c r="P26" s="6"/>
@@ -49103,7 +49106,7 @@
         <v>359</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X26" s="13"/>
       <c r="Y26" s="13"/>
@@ -49115,14 +49118,14 @@
       </c>
       <c r="AD26" s="13"/>
       <c r="AE26" s="1" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="AF26" s="1" t="s">
         <v>714</v>
       </c>
       <c r="AG26" s="13"/>
       <c r="AH26" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI26" s="13"/>
       <c r="AJ26" s="13"/>
@@ -49149,7 +49152,7 @@
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
       <c r="N27" s="4" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="O27" s="6"/>
       <c r="P27" s="6"/>
@@ -49174,7 +49177,7 @@
         <v>359</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X27" s="13"/>
       <c r="Y27" s="13"/>
@@ -49188,14 +49191,14 @@
         <v>222</v>
       </c>
       <c r="AE27" s="1" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="AF27" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG27" s="13"/>
       <c r="AH27" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI27" s="13"/>
       <c r="AJ27" s="13"/>
@@ -49222,7 +49225,7 @@
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
       <c r="N28" s="4" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="O28" s="6"/>
       <c r="P28" s="6"/>
@@ -49247,7 +49250,7 @@
         <v>359</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X28" s="13"/>
       <c r="Y28" s="13"/>
@@ -49261,14 +49264,14 @@
         <v>222</v>
       </c>
       <c r="AE28" s="1" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="AF28" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG28" s="13"/>
       <c r="AH28" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI28" s="13"/>
       <c r="AJ28" s="13"/>
@@ -49295,7 +49298,7 @@
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
       <c r="N29" s="4" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="O29" s="6"/>
       <c r="P29" s="6"/>
@@ -49320,7 +49323,7 @@
         <v>359</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X29" s="13"/>
       <c r="Y29" s="13"/>
@@ -49334,14 +49337,14 @@
         <v>222</v>
       </c>
       <c r="AE29" s="1" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="AF29" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG29" s="13"/>
       <c r="AH29" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI29" s="13"/>
       <c r="AJ29" s="13"/>
@@ -49391,7 +49394,7 @@
         <v>359</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X30" s="13"/>
       <c r="Y30" s="13"/>
@@ -49400,17 +49403,17 @@
       <c r="AB30" s="13"/>
       <c r="AC30" s="13"/>
       <c r="AD30" s="1" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="AE30" s="1" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="AF30" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG30" s="13"/>
       <c r="AH30" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI30" s="13"/>
       <c r="AJ30" s="13"/>
@@ -49460,7 +49463,7 @@
         <v>359</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X31" s="13"/>
       <c r="Y31" s="13"/>
@@ -49469,17 +49472,17 @@
       <c r="AB31" s="13"/>
       <c r="AC31" s="13"/>
       <c r="AD31" s="1" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="AE31" s="1" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="AF31" s="1" t="s">
         <v>254</v>
       </c>
       <c r="AG31" s="13"/>
       <c r="AH31" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI31" s="13"/>
       <c r="AJ31" s="13"/>
@@ -49506,7 +49509,7 @@
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
       <c r="N32" s="4" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="O32" s="6"/>
       <c r="P32" s="6"/>
@@ -49531,7 +49534,7 @@
         <v>359</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X32" s="13"/>
       <c r="Y32" s="13"/>
@@ -49543,14 +49546,14 @@
       </c>
       <c r="AD32" s="13"/>
       <c r="AE32" s="1" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="AF32" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG32" s="13"/>
       <c r="AH32" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI32" s="13"/>
       <c r="AJ32" s="13"/>
@@ -49600,7 +49603,7 @@
         <v>359</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X33" s="13"/>
       <c r="Y33" s="13"/>
@@ -49610,14 +49613,14 @@
       <c r="AC33" s="13"/>
       <c r="AD33" s="13"/>
       <c r="AE33" s="1" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="AF33" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG33" s="13"/>
       <c r="AH33" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI33" s="13"/>
       <c r="AJ33" s="13"/>
@@ -49644,7 +49647,7 @@
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
       <c r="N34" s="4" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="O34" s="6"/>
       <c r="P34" s="6"/>
@@ -49669,7 +49672,7 @@
         <v>359</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X34" s="13"/>
       <c r="Y34" s="13"/>
@@ -49681,14 +49684,14 @@
       </c>
       <c r="AD34" s="13"/>
       <c r="AE34" s="1" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="AF34" s="1" t="s">
         <v>714</v>
       </c>
       <c r="AG34" s="13"/>
       <c r="AH34" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI34" s="13"/>
       <c r="AJ34" s="13"/>
@@ -49738,7 +49741,7 @@
         <v>359</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X35" s="13"/>
       <c r="Y35" s="13"/>
@@ -49750,14 +49753,14 @@
         <v>127</v>
       </c>
       <c r="AE35" s="1" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="AF35" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG35" s="13"/>
       <c r="AH35" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI35" s="13"/>
       <c r="AJ35" s="13"/>
@@ -49807,7 +49810,7 @@
         <v>359</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X36" s="13"/>
       <c r="Y36" s="13"/>
@@ -49817,14 +49820,14 @@
       <c r="AC36" s="13"/>
       <c r="AD36" s="13"/>
       <c r="AE36" s="1" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="AF36" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG36" s="13"/>
       <c r="AH36" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI36" s="13"/>
       <c r="AJ36" s="13"/>
@@ -49851,7 +49854,7 @@
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
       <c r="N37" s="4" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="O37" s="6"/>
       <c r="P37" s="6"/>
@@ -49876,7 +49879,7 @@
         <v>359</v>
       </c>
       <c r="W37" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X37" s="13"/>
       <c r="Y37" s="13"/>
@@ -49884,20 +49887,20 @@
       <c r="AA37" s="13"/>
       <c r="AB37" s="13"/>
       <c r="AC37" s="1" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="AD37" s="1" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="AE37" s="1" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="AF37" s="1" t="s">
         <v>254</v>
       </c>
       <c r="AG37" s="13"/>
       <c r="AH37" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI37" s="13"/>
       <c r="AJ37" s="13"/>
@@ -49924,7 +49927,7 @@
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
       <c r="N38" s="4" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="O38" s="6"/>
       <c r="P38" s="6"/>
@@ -49949,7 +49952,7 @@
         <v>359</v>
       </c>
       <c r="W38" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X38" s="13"/>
       <c r="Y38" s="13"/>
@@ -49957,20 +49960,20 @@
       <c r="AA38" s="13"/>
       <c r="AB38" s="13"/>
       <c r="AC38" s="1" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="AD38" s="1" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="AE38" s="1" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="AF38" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG38" s="13"/>
       <c r="AH38" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI38" s="13"/>
       <c r="AJ38" s="13"/>
@@ -49997,7 +50000,7 @@
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
       <c r="N39" s="4" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="O39" s="6"/>
       <c r="P39" s="6"/>
@@ -50022,7 +50025,7 @@
         <v>359</v>
       </c>
       <c r="W39" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X39" s="13"/>
       <c r="Y39" s="13"/>
@@ -50030,20 +50033,20 @@
       <c r="AA39" s="13"/>
       <c r="AB39" s="13"/>
       <c r="AC39" s="1" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="AD39" s="1" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="AE39" s="1" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="AF39" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG39" s="13"/>
       <c r="AH39" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI39" s="13"/>
       <c r="AJ39" s="13"/>
@@ -50070,7 +50073,7 @@
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
       <c r="N40" s="4" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="O40" s="6"/>
       <c r="P40" s="6"/>
@@ -50095,7 +50098,7 @@
         <v>359</v>
       </c>
       <c r="W40" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X40" s="13"/>
       <c r="Y40" s="13"/>
@@ -50103,18 +50106,18 @@
       <c r="AA40" s="13"/>
       <c r="AB40" s="13"/>
       <c r="AC40" s="1" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="AD40" s="13"/>
       <c r="AE40" s="1" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="AF40" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG40" s="13"/>
       <c r="AH40" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI40" s="13"/>
       <c r="AJ40" s="13"/>
@@ -50141,7 +50144,7 @@
       <c r="L41" s="4"/>
       <c r="M41" s="4"/>
       <c r="N41" s="4" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="O41" s="6"/>
       <c r="P41" s="6"/>
@@ -50166,7 +50169,7 @@
         <v>359</v>
       </c>
       <c r="W41" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X41" s="13"/>
       <c r="Y41" s="13"/>
@@ -50180,14 +50183,14 @@
         <v>127</v>
       </c>
       <c r="AE41" s="1" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="AF41" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG41" s="13"/>
       <c r="AH41" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI41" s="13"/>
       <c r="AJ41" s="13"/>
@@ -50237,7 +50240,7 @@
         <v>359</v>
       </c>
       <c r="W42" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X42" s="13"/>
       <c r="Y42" s="13"/>
@@ -50247,14 +50250,14 @@
       <c r="AC42" s="13"/>
       <c r="AD42" s="13"/>
       <c r="AE42" s="1" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="AF42" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG42" s="13"/>
       <c r="AH42" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI42" s="13"/>
       <c r="AJ42" s="13"/>
@@ -50281,7 +50284,7 @@
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
       <c r="N43" s="4" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="O43" s="6"/>
       <c r="P43" s="6"/>
@@ -50306,7 +50309,7 @@
         <v>359</v>
       </c>
       <c r="W43" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X43" s="13"/>
       <c r="Y43" s="13"/>
@@ -50318,14 +50321,14 @@
       </c>
       <c r="AD43" s="13"/>
       <c r="AE43" s="1" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="AF43" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG43" s="13"/>
       <c r="AH43" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI43" s="13"/>
       <c r="AJ43" s="13"/>
@@ -50352,7 +50355,7 @@
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
       <c r="N44" s="4" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="O44" s="6"/>
       <c r="P44" s="6"/>
@@ -50377,7 +50380,7 @@
         <v>359</v>
       </c>
       <c r="W44" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X44" s="13"/>
       <c r="Y44" s="13"/>
@@ -50389,14 +50392,14 @@
       </c>
       <c r="AD44" s="13"/>
       <c r="AE44" s="1" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="AF44" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG44" s="13"/>
       <c r="AH44" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI44" s="13"/>
       <c r="AJ44" s="13"/>
@@ -50423,7 +50426,7 @@
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
       <c r="N45" s="4" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="O45" s="6"/>
       <c r="P45" s="6"/>
@@ -50448,7 +50451,7 @@
         <v>359</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X45" s="13"/>
       <c r="Y45" s="13"/>
@@ -50460,14 +50463,14 @@
       </c>
       <c r="AD45" s="13"/>
       <c r="AE45" s="1" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="AF45" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG45" s="13"/>
       <c r="AH45" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI45" s="13"/>
       <c r="AJ45" s="13"/>
@@ -50517,7 +50520,7 @@
         <v>359</v>
       </c>
       <c r="W46" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X46" s="13"/>
       <c r="Y46" s="13"/>
@@ -50527,14 +50530,14 @@
       <c r="AC46" s="13"/>
       <c r="AD46" s="13"/>
       <c r="AE46" s="1" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="AF46" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG46" s="13"/>
       <c r="AH46" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI46" s="13"/>
       <c r="AJ46" s="13"/>
@@ -50561,7 +50564,7 @@
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
       <c r="N47" s="4" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="O47" s="6"/>
       <c r="P47" s="6"/>
@@ -50586,7 +50589,7 @@
         <v>359</v>
       </c>
       <c r="W47" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X47" s="13"/>
       <c r="Y47" s="13"/>
@@ -50598,14 +50601,14 @@
       </c>
       <c r="AD47" s="13"/>
       <c r="AE47" s="1" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="AF47" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG47" s="13"/>
       <c r="AH47" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI47" s="13"/>
       <c r="AJ47" s="13"/>
@@ -50655,7 +50658,7 @@
         <v>359</v>
       </c>
       <c r="W48" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X48" s="13"/>
       <c r="Y48" s="13"/>
@@ -50665,14 +50668,14 @@
       <c r="AC48" s="13"/>
       <c r="AD48" s="13"/>
       <c r="AE48" s="1" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="AF48" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG48" s="13"/>
       <c r="AH48" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI48" s="13"/>
       <c r="AJ48" s="13"/>
@@ -50699,7 +50702,7 @@
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
       <c r="N49" s="4" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="O49" s="6"/>
       <c r="P49" s="6"/>
@@ -50724,7 +50727,7 @@
         <v>359</v>
       </c>
       <c r="W49" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X49" s="13"/>
       <c r="Y49" s="13"/>
@@ -50736,14 +50739,14 @@
       </c>
       <c r="AD49" s="13"/>
       <c r="AE49" s="1" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="AF49" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG49" s="13"/>
       <c r="AH49" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI49" s="13"/>
       <c r="AJ49" s="13"/>
@@ -50793,7 +50796,7 @@
         <v>359</v>
       </c>
       <c r="W50" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X50" s="13"/>
       <c r="Y50" s="13"/>
@@ -50803,14 +50806,14 @@
       <c r="AC50" s="13"/>
       <c r="AD50" s="13"/>
       <c r="AE50" s="1" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="AF50" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG50" s="13"/>
       <c r="AH50" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI50" s="13"/>
       <c r="AJ50" s="13"/>
@@ -50860,7 +50863,7 @@
         <v>359</v>
       </c>
       <c r="W51" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X51" s="13"/>
       <c r="Y51" s="13"/>
@@ -50869,17 +50872,17 @@
       <c r="AB51" s="13"/>
       <c r="AC51" s="13"/>
       <c r="AD51" s="1" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="AE51" s="1" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="AF51" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG51" s="13"/>
       <c r="AH51" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI51" s="13"/>
       <c r="AJ51" s="13"/>
@@ -50929,7 +50932,7 @@
         <v>359</v>
       </c>
       <c r="W52" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X52" s="13"/>
       <c r="Y52" s="13"/>
@@ -50938,17 +50941,17 @@
       <c r="AB52" s="13"/>
       <c r="AC52" s="13"/>
       <c r="AD52" s="1" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="AE52" s="1" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="AF52" s="1" t="s">
         <v>254</v>
       </c>
       <c r="AG52" s="13"/>
       <c r="AH52" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI52" s="13"/>
       <c r="AJ52" s="13"/>
@@ -50975,7 +50978,7 @@
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
       <c r="N53" s="4" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="O53" s="6"/>
       <c r="P53" s="6"/>
@@ -51000,7 +51003,7 @@
         <v>359</v>
       </c>
       <c r="W53" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X53" s="13"/>
       <c r="Y53" s="13"/>
@@ -51014,14 +51017,14 @@
         <v>127</v>
       </c>
       <c r="AE53" s="1" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="AF53" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG53" s="13"/>
       <c r="AH53" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI53" s="13"/>
       <c r="AJ53" s="13"/>
@@ -51071,7 +51074,7 @@
         <v>359</v>
       </c>
       <c r="W54" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X54" s="13"/>
       <c r="Y54" s="13"/>
@@ -51083,14 +51086,14 @@
         <v>127</v>
       </c>
       <c r="AE54" s="1" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="AF54" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG54" s="13"/>
       <c r="AH54" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI54" s="13"/>
       <c r="AJ54" s="13"/>
@@ -51117,7 +51120,7 @@
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
       <c r="N55" s="4" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="O55" s="6"/>
       <c r="P55" s="6"/>
@@ -51142,7 +51145,7 @@
         <v>359</v>
       </c>
       <c r="W55" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X55" s="13"/>
       <c r="Y55" s="13"/>
@@ -51156,14 +51159,14 @@
         <v>127</v>
       </c>
       <c r="AE55" s="1" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="AF55" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG55" s="13"/>
       <c r="AH55" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI55" s="13"/>
       <c r="AJ55" s="13"/>
@@ -51237,7 +51240,7 @@
         <v>359</v>
       </c>
       <c r="W57" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X57" s="13"/>
       <c r="Y57" s="13"/>
@@ -51249,14 +51252,14 @@
         <v>127</v>
       </c>
       <c r="AE57" s="1" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="AF57" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG57" s="13"/>
       <c r="AH57" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI57" s="13"/>
       <c r="AJ57" s="13"/>
@@ -51306,7 +51309,7 @@
         <v>359</v>
       </c>
       <c r="W58" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X58" s="13"/>
       <c r="Y58" s="13"/>
@@ -51318,14 +51321,14 @@
         <v>127</v>
       </c>
       <c r="AE58" s="1" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="AF58" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG58" s="13"/>
       <c r="AH58" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI58" s="13"/>
       <c r="AJ58" s="13"/>
@@ -51352,7 +51355,7 @@
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
       <c r="N59" s="4" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="O59" s="6"/>
       <c r="P59" s="6"/>
@@ -51377,7 +51380,7 @@
         <v>359</v>
       </c>
       <c r="W59" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X59" s="13"/>
       <c r="Y59" s="13"/>
@@ -51385,20 +51388,20 @@
       <c r="AA59" s="13"/>
       <c r="AB59" s="13"/>
       <c r="AC59" s="1" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="AD59" s="1" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="AE59" s="1" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="AF59" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG59" s="13"/>
       <c r="AH59" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI59" s="13"/>
       <c r="AJ59" s="13"/>
@@ -51448,7 +51451,7 @@
         <v>359</v>
       </c>
       <c r="W60" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X60" s="13"/>
       <c r="Y60" s="13"/>
@@ -51457,17 +51460,17 @@
       <c r="AB60" s="13"/>
       <c r="AC60" s="13"/>
       <c r="AD60" s="1" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="AE60" s="1" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="AF60" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG60" s="13"/>
       <c r="AH60" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI60" s="13"/>
       <c r="AJ60" s="13"/>
@@ -51494,7 +51497,7 @@
       <c r="L61" s="4"/>
       <c r="M61" s="4"/>
       <c r="N61" s="4" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="O61" s="6"/>
       <c r="P61" s="6"/>
@@ -51519,7 +51522,7 @@
         <v>359</v>
       </c>
       <c r="W61" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X61" s="13"/>
       <c r="Y61" s="13"/>
@@ -51531,14 +51534,14 @@
       </c>
       <c r="AD61" s="13"/>
       <c r="AE61" s="1" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="AF61" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG61" s="13"/>
       <c r="AH61" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI61" s="13"/>
       <c r="AJ61" s="13"/>
@@ -51588,7 +51591,7 @@
         <v>359</v>
       </c>
       <c r="W62" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X62" s="13"/>
       <c r="Y62" s="13"/>
@@ -51598,14 +51601,14 @@
       <c r="AC62" s="13"/>
       <c r="AD62" s="13"/>
       <c r="AE62" s="1" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="AF62" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG62" s="13"/>
       <c r="AH62" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI62" s="13"/>
       <c r="AJ62" s="13"/>
@@ -51632,7 +51635,7 @@
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
       <c r="N63" s="4" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="O63" s="6"/>
       <c r="P63" s="6"/>
@@ -51657,7 +51660,7 @@
         <v>359</v>
       </c>
       <c r="W63" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X63" s="13"/>
       <c r="Y63" s="13"/>
@@ -51669,14 +51672,14 @@
       </c>
       <c r="AD63" s="13"/>
       <c r="AE63" s="1" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="AF63" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG63" s="13"/>
       <c r="AH63" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI63" s="13"/>
       <c r="AJ63" s="13"/>
@@ -51726,7 +51729,7 @@
         <v>359</v>
       </c>
       <c r="W64" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X64" s="13"/>
       <c r="Y64" s="13"/>
@@ -51736,14 +51739,14 @@
       <c r="AC64" s="13"/>
       <c r="AD64" s="13"/>
       <c r="AE64" s="1" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="AF64" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG64" s="13"/>
       <c r="AH64" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI64" s="13"/>
       <c r="AJ64" s="13"/>
@@ -51793,7 +51796,7 @@
         <v>359</v>
       </c>
       <c r="W65" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X65" s="13"/>
       <c r="Y65" s="13"/>
@@ -51802,17 +51805,17 @@
       <c r="AB65" s="13"/>
       <c r="AC65" s="13"/>
       <c r="AD65" s="1" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="AE65" s="1" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="AF65" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG65" s="13"/>
       <c r="AH65" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI65" s="13"/>
       <c r="AJ65" s="13"/>
@@ -51862,7 +51865,7 @@
         <v>359</v>
       </c>
       <c r="W66" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X66" s="13"/>
       <c r="Y66" s="13"/>
@@ -51872,14 +51875,14 @@
       <c r="AC66" s="13"/>
       <c r="AD66" s="13"/>
       <c r="AE66" s="1" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="AF66" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG66" s="13"/>
       <c r="AH66" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI66" s="13"/>
       <c r="AJ66" s="13"/>
@@ -51953,7 +51956,7 @@
         <v>359</v>
       </c>
       <c r="W68" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X68" s="13"/>
       <c r="Y68" s="13"/>
@@ -51970,7 +51973,7 @@
       </c>
       <c r="AG68" s="13"/>
       <c r="AH68" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI68" s="13"/>
       <c r="AJ68" s="13"/>
@@ -51997,7 +52000,7 @@
       <c r="L69" s="4"/>
       <c r="M69" s="4"/>
       <c r="N69" s="4" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="O69" s="6"/>
       <c r="P69" s="6"/>
@@ -52022,7 +52025,7 @@
         <v>359</v>
       </c>
       <c r="W69" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X69" s="13"/>
       <c r="Y69" s="13"/>
@@ -52034,14 +52037,14 @@
       </c>
       <c r="AD69" s="13"/>
       <c r="AE69" s="1" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="AF69" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG69" s="13"/>
       <c r="AH69" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI69" s="13"/>
       <c r="AJ69" s="13"/>
@@ -52068,7 +52071,7 @@
       <c r="L70" s="4"/>
       <c r="M70" s="4"/>
       <c r="N70" s="4" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="O70" s="6"/>
       <c r="P70" s="6"/>
@@ -52093,7 +52096,7 @@
         <v>359</v>
       </c>
       <c r="W70" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X70" s="13"/>
       <c r="Y70" s="13"/>
@@ -52107,14 +52110,14 @@
         <v>127</v>
       </c>
       <c r="AE70" s="1" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="AF70" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG70" s="13"/>
       <c r="AH70" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI70" s="13"/>
       <c r="AJ70" s="13"/>
@@ -52141,7 +52144,7 @@
       <c r="L71" s="4"/>
       <c r="M71" s="4"/>
       <c r="N71" s="4" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="O71" s="6"/>
       <c r="P71" s="6"/>
@@ -52166,7 +52169,7 @@
         <v>359</v>
       </c>
       <c r="W71" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X71" s="13"/>
       <c r="Y71" s="13"/>
@@ -52178,14 +52181,14 @@
       </c>
       <c r="AD71" s="13"/>
       <c r="AE71" s="1" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="AF71" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG71" s="13"/>
       <c r="AH71" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI71" s="13"/>
       <c r="AJ71" s="13"/>
@@ -52212,7 +52215,7 @@
       <c r="L72" s="4"/>
       <c r="M72" s="4"/>
       <c r="N72" s="4" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="O72" s="6"/>
       <c r="P72" s="6"/>
@@ -52237,7 +52240,7 @@
         <v>359</v>
       </c>
       <c r="W72" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X72" s="13"/>
       <c r="Y72" s="13"/>
@@ -52249,14 +52252,14 @@
       </c>
       <c r="AD72" s="13"/>
       <c r="AE72" s="1" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="AF72" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG72" s="13"/>
       <c r="AH72" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI72" s="13"/>
       <c r="AJ72" s="13"/>
@@ -52306,7 +52309,7 @@
         <v>359</v>
       </c>
       <c r="W73" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X73" s="13"/>
       <c r="Y73" s="13"/>
@@ -52315,17 +52318,17 @@
       <c r="AB73" s="13"/>
       <c r="AC73" s="13"/>
       <c r="AD73" s="1" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="AE73" s="1" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="AF73" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG73" s="13"/>
       <c r="AH73" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI73" s="13"/>
       <c r="AJ73" s="13"/>
@@ -52352,7 +52355,7 @@
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
       <c r="N74" s="4" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="O74" s="6"/>
       <c r="P74" s="6"/>
@@ -52377,7 +52380,7 @@
         <v>359</v>
       </c>
       <c r="W74" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X74" s="13"/>
       <c r="Y74" s="13"/>
@@ -52388,17 +52391,17 @@
         <v>712</v>
       </c>
       <c r="AD74" s="1" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="AE74" s="1" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="AF74" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG74" s="13"/>
       <c r="AH74" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI74" s="13"/>
       <c r="AJ74" s="13"/>
@@ -52448,7 +52451,7 @@
         <v>359</v>
       </c>
       <c r="W75" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X75" s="13"/>
       <c r="Y75" s="13"/>
@@ -52458,14 +52461,14 @@
       <c r="AC75" s="13"/>
       <c r="AD75" s="13"/>
       <c r="AE75" s="1" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="AF75" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG75" s="13"/>
       <c r="AH75" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI75" s="13"/>
       <c r="AJ75" s="13"/>
@@ -52515,7 +52518,7 @@
         <v>359</v>
       </c>
       <c r="W76" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X76" s="13"/>
       <c r="Y76" s="13"/>
@@ -52525,14 +52528,14 @@
       <c r="AC76" s="13"/>
       <c r="AD76" s="13"/>
       <c r="AE76" s="1" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="AF76" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG76" s="13"/>
       <c r="AH76" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI76" s="13"/>
       <c r="AJ76" s="13"/>
@@ -52582,7 +52585,7 @@
         <v>359</v>
       </c>
       <c r="W77" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X77" s="13"/>
       <c r="Y77" s="13"/>
@@ -52591,17 +52594,17 @@
       <c r="AB77" s="13"/>
       <c r="AC77" s="13"/>
       <c r="AD77" s="1" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="AE77" s="1" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="AF77" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG77" s="13"/>
       <c r="AH77" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI77" s="13"/>
       <c r="AJ77" s="13"/>
@@ -52651,7 +52654,7 @@
         <v>359</v>
       </c>
       <c r="W78" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X78" s="13"/>
       <c r="Y78" s="13"/>
@@ -52660,17 +52663,17 @@
       <c r="AB78" s="13"/>
       <c r="AC78" s="13"/>
       <c r="AD78" s="1" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="AE78" s="1" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="AF78" s="1" t="s">
         <v>254</v>
       </c>
       <c r="AG78" s="13"/>
       <c r="AH78" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI78" s="13"/>
       <c r="AJ78" s="13"/>
@@ -52697,7 +52700,7 @@
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
       <c r="N79" s="4" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="O79" s="6"/>
       <c r="P79" s="6"/>
@@ -52722,7 +52725,7 @@
         <v>359</v>
       </c>
       <c r="W79" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X79" s="13"/>
       <c r="Y79" s="13"/>
@@ -52734,14 +52737,14 @@
       </c>
       <c r="AD79" s="13"/>
       <c r="AE79" s="1" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="AF79" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG79" s="13"/>
       <c r="AH79" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI79" s="13"/>
       <c r="AJ79" s="13"/>
@@ -52768,7 +52771,7 @@
       <c r="L80" s="4"/>
       <c r="M80" s="4"/>
       <c r="N80" s="4" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="O80" s="6"/>
       <c r="P80" s="6"/>
@@ -52793,7 +52796,7 @@
         <v>359</v>
       </c>
       <c r="W80" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X80" s="13"/>
       <c r="Y80" s="13"/>
@@ -52805,14 +52808,14 @@
       </c>
       <c r="AD80" s="13"/>
       <c r="AE80" s="1" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="AF80" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG80" s="13"/>
       <c r="AH80" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI80" s="13"/>
       <c r="AJ80" s="13"/>
@@ -52862,7 +52865,7 @@
         <v>359</v>
       </c>
       <c r="W81" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X81" s="13"/>
       <c r="Y81" s="13"/>
@@ -52871,17 +52874,17 @@
       <c r="AB81" s="13"/>
       <c r="AC81" s="13"/>
       <c r="AD81" s="1" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="AE81" s="1" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="AF81" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG81" s="13"/>
       <c r="AH81" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI81" s="13"/>
       <c r="AJ81" s="13"/>
@@ -52908,7 +52911,7 @@
       <c r="L82" s="4"/>
       <c r="M82" s="4"/>
       <c r="N82" s="4" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="O82" s="6"/>
       <c r="P82" s="6"/>
@@ -52933,7 +52936,7 @@
         <v>359</v>
       </c>
       <c r="W82" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X82" s="13"/>
       <c r="Y82" s="13"/>
@@ -52945,14 +52948,14 @@
       </c>
       <c r="AD82" s="13"/>
       <c r="AE82" s="1" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="AF82" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG82" s="13"/>
       <c r="AH82" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI82" s="13"/>
       <c r="AJ82" s="13"/>
@@ -53002,7 +53005,7 @@
         <v>359</v>
       </c>
       <c r="W83" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X83" s="13"/>
       <c r="Y83" s="13"/>
@@ -53012,14 +53015,14 @@
       <c r="AC83" s="13"/>
       <c r="AD83" s="13"/>
       <c r="AE83" s="1" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="AF83" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG83" s="13"/>
       <c r="AH83" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI83" s="13"/>
       <c r="AJ83" s="13"/>
@@ -53091,7 +53094,7 @@
       <c r="L85" s="4"/>
       <c r="M85" s="4"/>
       <c r="N85" s="4" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="O85" s="6"/>
       <c r="P85" s="6"/>
@@ -53116,7 +53119,7 @@
         <v>359</v>
       </c>
       <c r="W85" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X85" s="13"/>
       <c r="Y85" s="13"/>
@@ -53130,14 +53133,14 @@
         <v>222</v>
       </c>
       <c r="AE85" s="1" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="AF85" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG85" s="13"/>
       <c r="AH85" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI85" s="13"/>
       <c r="AJ85" s="13"/>
@@ -53187,7 +53190,7 @@
         <v>359</v>
       </c>
       <c r="W86" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X86" s="13"/>
       <c r="Y86" s="13"/>
@@ -53196,17 +53199,17 @@
       <c r="AB86" s="13"/>
       <c r="AC86" s="13"/>
       <c r="AD86" s="1" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="AE86" s="1" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="AF86" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG86" s="13"/>
       <c r="AH86" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI86" s="13"/>
       <c r="AJ86" s="13"/>
@@ -53256,7 +53259,7 @@
         <v>359</v>
       </c>
       <c r="W87" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X87" s="13"/>
       <c r="Y87" s="13"/>
@@ -53265,17 +53268,17 @@
       <c r="AB87" s="13"/>
       <c r="AC87" s="13"/>
       <c r="AD87" s="1" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="AE87" s="1" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="AF87" s="1" t="s">
         <v>254</v>
       </c>
       <c r="AG87" s="13"/>
       <c r="AH87" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI87" s="13"/>
       <c r="AJ87" s="13"/>
@@ -53302,7 +53305,7 @@
       <c r="L88" s="4"/>
       <c r="M88" s="4"/>
       <c r="N88" s="4" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="O88" s="6"/>
       <c r="P88" s="6"/>
@@ -53327,7 +53330,7 @@
         <v>359</v>
       </c>
       <c r="W88" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X88" s="13"/>
       <c r="Y88" s="13"/>
@@ -53338,7 +53341,7 @@
         <v>712</v>
       </c>
       <c r="AD88" s="1" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="AE88" s="1" t="s">
         <v>64</v>
@@ -53348,7 +53351,7 @@
       </c>
       <c r="AG88" s="13"/>
       <c r="AH88" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI88" s="13"/>
       <c r="AJ88" s="13"/>
@@ -53398,7 +53401,7 @@
         <v>359</v>
       </c>
       <c r="W89" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X89" s="13"/>
       <c r="Y89" s="13"/>
@@ -53415,7 +53418,7 @@
       </c>
       <c r="AG89" s="13"/>
       <c r="AH89" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI89" s="13"/>
       <c r="AJ89" s="13"/>
@@ -53465,7 +53468,7 @@
         <v>359</v>
       </c>
       <c r="W90" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X90" s="13"/>
       <c r="Y90" s="13"/>
@@ -53475,14 +53478,14 @@
       <c r="AC90" s="13"/>
       <c r="AD90" s="13"/>
       <c r="AE90" s="1" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="AF90" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG90" s="13"/>
       <c r="AH90" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI90" s="13"/>
       <c r="AJ90" s="13"/>
@@ -53532,7 +53535,7 @@
         <v>359</v>
       </c>
       <c r="W91" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X91" s="13"/>
       <c r="Y91" s="13"/>
@@ -53541,17 +53544,17 @@
       <c r="AB91" s="13"/>
       <c r="AC91" s="13"/>
       <c r="AD91" s="1" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="AE91" s="1" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="AF91" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG91" s="13"/>
       <c r="AH91" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI91" s="13"/>
       <c r="AJ91" s="13"/>
@@ -53601,7 +53604,7 @@
         <v>359</v>
       </c>
       <c r="W92" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X92" s="13"/>
       <c r="Y92" s="13"/>
@@ -53611,14 +53614,14 @@
       <c r="AC92" s="13"/>
       <c r="AD92" s="13"/>
       <c r="AE92" s="1" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="AF92" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG92" s="13"/>
       <c r="AH92" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI92" s="13"/>
       <c r="AJ92" s="13"/>
@@ -53645,7 +53648,7 @@
       <c r="L93" s="4"/>
       <c r="M93" s="4"/>
       <c r="N93" s="4" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="O93" s="6"/>
       <c r="P93" s="6"/>
@@ -53670,7 +53673,7 @@
         <v>359</v>
       </c>
       <c r="W93" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X93" s="13"/>
       <c r="Y93" s="13"/>
@@ -53678,20 +53681,20 @@
       <c r="AA93" s="13"/>
       <c r="AB93" s="13"/>
       <c r="AC93" s="1" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="AD93" s="1" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="AE93" s="1" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="AF93" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG93" s="13"/>
       <c r="AH93" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI93" s="13"/>
       <c r="AJ93" s="13"/>
@@ -53741,7 +53744,7 @@
         <v>359</v>
       </c>
       <c r="W94" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X94" s="13"/>
       <c r="Y94" s="13"/>
@@ -53751,14 +53754,14 @@
       <c r="AC94" s="13"/>
       <c r="AD94" s="13"/>
       <c r="AE94" s="1" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="AF94" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG94" s="13"/>
       <c r="AH94" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI94" s="13"/>
       <c r="AJ94" s="13"/>
@@ -53785,7 +53788,7 @@
       <c r="L95" s="4"/>
       <c r="M95" s="4"/>
       <c r="N95" s="4" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="O95" s="6"/>
       <c r="P95" s="6"/>
@@ -53810,7 +53813,7 @@
         <v>359</v>
       </c>
       <c r="W95" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X95" s="13"/>
       <c r="Y95" s="13"/>
@@ -53824,14 +53827,14 @@
         <v>127</v>
       </c>
       <c r="AE95" s="1" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="AF95" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG95" s="13"/>
       <c r="AH95" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI95" s="13"/>
       <c r="AJ95" s="13"/>
@@ -53883,7 +53886,7 @@
         <v>359</v>
       </c>
       <c r="W96" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X96" s="13"/>
       <c r="Y96" s="13"/>
@@ -53895,14 +53898,14 @@
       </c>
       <c r="AD96" s="13"/>
       <c r="AE96" s="1" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="AF96" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG96" s="13"/>
       <c r="AH96" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI96" s="13"/>
       <c r="AJ96" s="13"/>
@@ -53952,7 +53955,7 @@
         <v>359</v>
       </c>
       <c r="W97" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X97" s="13"/>
       <c r="Y97" s="13"/>
@@ -53964,14 +53967,14 @@
         <v>222</v>
       </c>
       <c r="AE97" s="1" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="AF97" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG97" s="13"/>
       <c r="AH97" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI97" s="13"/>
       <c r="AJ97" s="13"/>
@@ -53998,7 +54001,7 @@
       <c r="L98" s="4"/>
       <c r="M98" s="4"/>
       <c r="N98" s="4" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="O98" s="6"/>
       <c r="P98" s="6"/>
@@ -54023,7 +54026,7 @@
         <v>359</v>
       </c>
       <c r="W98" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X98" s="13"/>
       <c r="Y98" s="13"/>
@@ -54035,14 +54038,14 @@
       </c>
       <c r="AD98" s="13"/>
       <c r="AE98" s="1" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="AF98" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG98" s="13"/>
       <c r="AH98" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI98" s="13"/>
       <c r="AJ98" s="13"/>
@@ -54069,7 +54072,7 @@
       <c r="L99" s="4"/>
       <c r="M99" s="4"/>
       <c r="N99" s="4" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="O99" s="6"/>
       <c r="P99" s="6"/>
@@ -54094,7 +54097,7 @@
         <v>359</v>
       </c>
       <c r="W99" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X99" s="13"/>
       <c r="Y99" s="13"/>
@@ -54106,14 +54109,14 @@
       </c>
       <c r="AD99" s="13"/>
       <c r="AE99" s="1" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="AF99" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG99" s="13"/>
       <c r="AH99" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI99" s="13"/>
       <c r="AJ99" s="13"/>
@@ -54163,7 +54166,7 @@
         <v>359</v>
       </c>
       <c r="W100" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X100" s="13"/>
       <c r="Y100" s="13"/>
@@ -54173,14 +54176,14 @@
       <c r="AC100" s="13"/>
       <c r="AD100" s="13"/>
       <c r="AE100" s="1" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="AF100" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG100" s="13"/>
       <c r="AH100" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI100" s="13"/>
       <c r="AJ100" s="13"/>
@@ -54207,7 +54210,7 @@
       <c r="L101" s="4"/>
       <c r="M101" s="4"/>
       <c r="N101" s="4" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="O101" s="6"/>
       <c r="P101" s="6"/>
@@ -54232,7 +54235,7 @@
         <v>359</v>
       </c>
       <c r="W101" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X101" s="13"/>
       <c r="Y101" s="13"/>
@@ -54246,14 +54249,14 @@
         <v>127</v>
       </c>
       <c r="AE101" s="1" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="AF101" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG101" s="13"/>
       <c r="AH101" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI101" s="13"/>
       <c r="AJ101" s="13"/>
@@ -54305,7 +54308,7 @@
         <v>359</v>
       </c>
       <c r="W102" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X102" s="13"/>
       <c r="Y102" s="13"/>
@@ -54324,7 +54327,7 @@
       </c>
       <c r="AG102" s="13"/>
       <c r="AH102" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI102" s="13"/>
       <c r="AJ102" s="13"/>
@@ -54351,7 +54354,7 @@
       <c r="L103" s="4"/>
       <c r="M103" s="4"/>
       <c r="N103" s="4" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="O103" s="6"/>
       <c r="P103" s="6"/>
@@ -54376,7 +54379,7 @@
         <v>359</v>
       </c>
       <c r="W103" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X103" s="13"/>
       <c r="Y103" s="13"/>
@@ -54388,14 +54391,14 @@
       </c>
       <c r="AD103" s="13"/>
       <c r="AE103" s="1" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="AF103" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG103" s="13"/>
       <c r="AH103" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI103" s="13"/>
       <c r="AJ103" s="13"/>
@@ -54422,7 +54425,7 @@
       <c r="L104" s="4"/>
       <c r="M104" s="4"/>
       <c r="N104" s="4" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="O104" s="6"/>
       <c r="P104" s="6"/>
@@ -54447,7 +54450,7 @@
         <v>359</v>
       </c>
       <c r="W104" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X104" s="13"/>
       <c r="Y104" s="13"/>
@@ -54459,14 +54462,14 @@
       </c>
       <c r="AD104" s="13"/>
       <c r="AE104" s="1" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="AF104" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG104" s="13"/>
       <c r="AH104" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI104" s="13"/>
       <c r="AJ104" s="13"/>
@@ -54493,7 +54496,7 @@
       <c r="L105" s="4"/>
       <c r="M105" s="4"/>
       <c r="N105" s="4" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="O105" s="6"/>
       <c r="P105" s="6"/>
@@ -54518,7 +54521,7 @@
         <v>359</v>
       </c>
       <c r="W105" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X105" s="13"/>
       <c r="Y105" s="13"/>
@@ -54532,14 +54535,14 @@
         <v>621</v>
       </c>
       <c r="AE105" s="1" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="AF105" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG105" s="13"/>
       <c r="AH105" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI105" s="13"/>
       <c r="AJ105" s="13"/>
@@ -54567,7 +54570,7 @@
       <c r="M106" s="4"/>
       <c r="AG106" s="13"/>
       <c r="AH106" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI106" s="13"/>
       <c r="AJ106" s="13"/>
@@ -54617,7 +54620,7 @@
         <v>359</v>
       </c>
       <c r="W107" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X107" s="13"/>
       <c r="Y107" s="13"/>
@@ -54627,14 +54630,14 @@
       <c r="AC107" s="13"/>
       <c r="AD107" s="13"/>
       <c r="AE107" s="1" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="AF107" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG107" s="13"/>
       <c r="AH107" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI107" s="13"/>
       <c r="AJ107" s="13"/>
@@ -54684,7 +54687,7 @@
         <v>359</v>
       </c>
       <c r="W108" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X108" s="13"/>
       <c r="Y108" s="13"/>
@@ -54697,11 +54700,11 @@
         <v>76</v>
       </c>
       <c r="AF108" s="1" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="AG108" s="13"/>
       <c r="AH108" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI108" s="13"/>
       <c r="AJ108" s="13"/>
@@ -54728,7 +54731,7 @@
       <c r="L109" s="4"/>
       <c r="M109" s="4"/>
       <c r="N109" s="4" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="O109" s="6"/>
       <c r="P109" s="6"/>
@@ -54753,7 +54756,7 @@
         <v>359</v>
       </c>
       <c r="W109" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X109" s="13"/>
       <c r="Y109" s="13"/>
@@ -54761,20 +54764,20 @@
       <c r="AA109" s="13"/>
       <c r="AB109" s="13"/>
       <c r="AC109" s="1" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="AD109" s="1" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="AE109" s="1" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="AF109" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG109" s="13"/>
       <c r="AH109" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI109" s="13"/>
       <c r="AJ109" s="13"/>
@@ -54801,7 +54804,7 @@
       <c r="L110" s="4"/>
       <c r="M110" s="4"/>
       <c r="N110" s="4" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="O110" s="6"/>
       <c r="P110" s="6"/>
@@ -54826,7 +54829,7 @@
         <v>359</v>
       </c>
       <c r="W110" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X110" s="13"/>
       <c r="Y110" s="13"/>
@@ -54838,14 +54841,14 @@
       </c>
       <c r="AD110" s="13"/>
       <c r="AE110" s="1" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="AF110" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG110" s="13"/>
       <c r="AH110" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI110" s="13"/>
       <c r="AJ110" s="13"/>
@@ -54895,7 +54898,7 @@
         <v>359</v>
       </c>
       <c r="W111" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X111" s="13"/>
       <c r="Y111" s="13"/>
@@ -54905,14 +54908,14 @@
       <c r="AC111" s="13"/>
       <c r="AD111" s="13"/>
       <c r="AE111" s="1" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="AF111" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG111" s="13"/>
       <c r="AH111" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI111" s="13"/>
       <c r="AJ111" s="13"/>
@@ -54962,7 +54965,7 @@
         <v>359</v>
       </c>
       <c r="W112" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X112" s="13"/>
       <c r="Y112" s="13"/>
@@ -54971,17 +54974,17 @@
       <c r="AB112" s="13"/>
       <c r="AC112" s="13"/>
       <c r="AD112" s="1" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="AE112" s="1" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="AF112" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG112" s="13"/>
       <c r="AH112" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI112" s="13"/>
       <c r="AJ112" s="13"/>
@@ -55031,7 +55034,7 @@
         <v>359</v>
       </c>
       <c r="W113" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X113" s="13"/>
       <c r="Y113" s="13"/>
@@ -55040,17 +55043,17 @@
       <c r="AB113" s="13"/>
       <c r="AC113" s="13"/>
       <c r="AD113" s="1" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="AE113" s="1" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="AF113" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG113" s="13"/>
       <c r="AH113" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI113" s="13"/>
       <c r="AJ113" s="13"/>
@@ -55077,7 +55080,7 @@
       <c r="L114" s="4"/>
       <c r="M114" s="4"/>
       <c r="N114" s="4" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="O114" s="6"/>
       <c r="P114" s="6"/>
@@ -55102,7 +55105,7 @@
         <v>359</v>
       </c>
       <c r="W114" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="X114" s="13"/>
       <c r="Y114" s="13"/>
@@ -55117,7 +55120,7 @@
       <c r="AF114" s="13"/>
       <c r="AG114" s="13"/>
       <c r="AH114" s="14" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AI114" s="13"/>
       <c r="AJ114" s="13"/>
@@ -55170,14 +55173,14 @@
       <c r="X115" s="34"/>
       <c r="Y115" s="34"/>
       <c r="Z115" s="36" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="AA115" s="36" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="AB115" s="34"/>
       <c r="AC115" s="34" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AD115" s="34"/>
       <c r="AE115" s="34"/>
@@ -55340,7 +55343,7 @@
       <c r="K116" s="34"/>
       <c r="L116" s="34"/>
       <c r="M116" s="36" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="N116" s="34"/>
       <c r="O116" s="34"/>
@@ -55371,14 +55374,14 @@
       <c r="X116" s="34"/>
       <c r="Y116" s="34"/>
       <c r="Z116" s="36" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="AA116" s="36" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="AB116" s="34"/>
       <c r="AC116" s="34" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="AD116" s="34"/>
       <c r="AE116" s="34"/>
@@ -55400,7 +55403,7 @@
       <c r="AU116" s="34"/>
       <c r="AV116" s="37"/>
       <c r="AW116" s="37" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="AX116" s="37"/>
       <c r="AY116" s="37"/>
@@ -55572,14 +55575,14 @@
       <c r="X117" s="34"/>
       <c r="Y117" s="34"/>
       <c r="Z117" s="36" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="AA117" s="36" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="AB117" s="34"/>
       <c r="AC117" s="34" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AD117" s="34"/>
       <c r="AE117" s="34"/>
@@ -55601,7 +55604,7 @@
       <c r="AU117" s="34"/>
       <c r="AV117" s="37"/>
       <c r="AW117" s="37" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="AX117" s="37"/>
       <c r="AY117" s="37"/>
@@ -55730,13 +55733,13 @@
     </row>
     <row r="118" spans="1:173" s="10" customFormat="1" ht="23.25" customHeight="1">
       <c r="A118" s="38" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="B118" s="39" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="C118" s="38" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="D118" s="38"/>
       <c r="E118" s="38" t="s">
@@ -55752,10 +55755,10 @@
       <c r="M118" s="39"/>
       <c r="N118" s="39"/>
       <c r="O118" s="38" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="P118" s="38" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="Q118" s="40" t="s">
         <v>99</v>
@@ -55793,12 +55796,12 @@
       <c r="AH118" s="39"/>
       <c r="AI118" s="39"/>
       <c r="AJ118" s="38" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="AK118" s="38"/>
       <c r="AL118" s="38"/>
       <c r="AM118" s="38" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="AN118" s="38"/>
       <c r="AO118" s="38" t="s">
@@ -55817,14 +55820,14 @@
         <v>132</v>
       </c>
       <c r="AT118" s="38" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="AU118" s="39" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="AV118" s="39"/>
       <c r="AW118" s="39" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="AX118" s="39"/>
       <c r="AY118" s="39"/>
@@ -55953,13 +55956,13 @@
     </row>
     <row r="119" spans="1:173" s="10" customFormat="1" ht="23.25" customHeight="1">
       <c r="A119" s="38" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="B119" s="39" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="C119" s="38" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="D119" s="38"/>
       <c r="E119" s="38" t="s">
@@ -55975,10 +55978,10 @@
       <c r="M119" s="39"/>
       <c r="N119" s="39"/>
       <c r="O119" s="38" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="P119" s="38" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="Q119" s="40" t="s">
         <v>731</v>
@@ -56016,12 +56019,12 @@
       <c r="AH119" s="39"/>
       <c r="AI119" s="39"/>
       <c r="AJ119" s="38" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="AK119" s="38"/>
       <c r="AL119" s="38"/>
       <c r="AM119" s="38" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="AN119" s="38"/>
       <c r="AO119" s="38" t="s">
@@ -56040,14 +56043,14 @@
         <v>132</v>
       </c>
       <c r="AT119" s="38" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="AU119" s="39" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="AV119" s="39"/>
       <c r="AW119" s="39" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="AX119" s="39"/>
       <c r="AY119" s="39"/>
@@ -56176,13 +56179,13 @@
     </row>
     <row r="120" spans="1:173" s="10" customFormat="1" ht="23.25" customHeight="1">
       <c r="A120" s="38" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="B120" s="39" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="C120" s="38" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="D120" s="38"/>
       <c r="E120" s="38" t="s">
@@ -56198,10 +56201,10 @@
       <c r="M120" s="39"/>
       <c r="N120" s="39"/>
       <c r="O120" s="38" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="P120" s="38" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="Q120" s="40" t="s">
         <v>873</v>
@@ -56239,12 +56242,12 @@
       <c r="AH120" s="39"/>
       <c r="AI120" s="39"/>
       <c r="AJ120" s="38" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="AK120" s="38"/>
       <c r="AL120" s="38"/>
       <c r="AM120" s="38" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="AN120" s="38"/>
       <c r="AO120" s="38" t="s">
@@ -56263,14 +56266,14 @@
         <v>132</v>
       </c>
       <c r="AT120" s="38" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="AU120" s="39" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="AV120" s="39"/>
       <c r="AW120" s="39" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="AX120" s="39"/>
       <c r="AY120" s="39"/>
@@ -56399,13 +56402,13 @@
     </row>
     <row r="121" spans="1:173" s="10" customFormat="1" ht="23.25" customHeight="1">
       <c r="A121" s="38" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="B121" s="39" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="C121" s="38" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="D121" s="38"/>
       <c r="E121" s="38" t="s">
@@ -56421,10 +56424,10 @@
       <c r="M121" s="39"/>
       <c r="N121" s="39"/>
       <c r="O121" s="38" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="P121" s="38" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="Q121" s="40" t="s">
         <v>110</v>
@@ -56462,12 +56465,12 @@
       <c r="AH121" s="39"/>
       <c r="AI121" s="39"/>
       <c r="AJ121" s="38" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="AK121" s="38"/>
       <c r="AL121" s="38"/>
       <c r="AM121" s="38" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="AN121" s="38"/>
       <c r="AO121" s="38" t="s">
@@ -56486,14 +56489,14 @@
         <v>132</v>
       </c>
       <c r="AT121" s="38" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="AU121" s="39" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="AV121" s="39"/>
       <c r="AW121" s="39" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="AX121" s="39"/>
       <c r="AY121" s="39"/>
@@ -56622,13 +56625,13 @@
     </row>
     <row r="122" spans="1:173" s="10" customFormat="1" ht="23.25" customHeight="1">
       <c r="A122" s="38" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="B122" s="39" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="C122" s="38" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="D122" s="38"/>
       <c r="E122" s="38" t="s">
@@ -56644,10 +56647,10 @@
       <c r="M122" s="39"/>
       <c r="N122" s="39"/>
       <c r="O122" s="38" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="P122" s="38" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="Q122" s="40" t="s">
         <v>873</v>
@@ -56685,12 +56688,12 @@
       <c r="AH122" s="39"/>
       <c r="AI122" s="39"/>
       <c r="AJ122" s="38" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="AK122" s="38"/>
       <c r="AL122" s="38"/>
       <c r="AM122" s="38" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="AN122" s="38"/>
       <c r="AO122" s="38" t="s">
@@ -56709,14 +56712,14 @@
         <v>132</v>
       </c>
       <c r="AT122" s="38" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="AU122" s="39" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="AV122" s="39"/>
       <c r="AW122" s="39" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="AX122" s="39"/>
       <c r="AY122" s="39"/>
@@ -56845,13 +56848,13 @@
     </row>
     <row r="123" spans="1:173" s="10" customFormat="1" ht="23.25" customHeight="1">
       <c r="A123" s="32" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="B123" s="42" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="C123" s="32" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="D123" s="32"/>
       <c r="E123" s="32" t="s">
@@ -56867,10 +56870,10 @@
       <c r="M123" s="42"/>
       <c r="N123" s="42"/>
       <c r="O123" s="32" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="P123" s="32" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="Q123" s="43" t="s">
         <v>99</v>
@@ -56908,12 +56911,12 @@
       <c r="AH123" s="42"/>
       <c r="AI123" s="42"/>
       <c r="AJ123" s="32" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="AK123" s="32"/>
       <c r="AL123" s="32"/>
       <c r="AM123" s="32" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="AN123" s="32"/>
       <c r="AO123" s="32" t="s">
@@ -56932,14 +56935,14 @@
         <v>132</v>
       </c>
       <c r="AT123" s="32" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="AU123" s="42" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="AV123" s="42"/>
       <c r="AW123" s="42" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="AX123" s="42"/>
       <c r="AY123" s="42"/>
@@ -57068,13 +57071,13 @@
     </row>
     <row r="124" spans="1:173" s="10" customFormat="1" ht="23.25" customHeight="1">
       <c r="A124" s="32" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="B124" s="42" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="C124" s="32" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D124" s="32"/>
       <c r="E124" s="32" t="s">
@@ -57090,10 +57093,10 @@
       <c r="M124" s="42"/>
       <c r="N124" s="42"/>
       <c r="O124" s="32" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="P124" s="32" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="Q124" s="43" t="s">
         <v>99</v>
@@ -57131,12 +57134,12 @@
       <c r="AH124" s="42"/>
       <c r="AI124" s="42"/>
       <c r="AJ124" s="32" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="AK124" s="32"/>
       <c r="AL124" s="32"/>
       <c r="AM124" s="32" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="AN124" s="32"/>
       <c r="AO124" s="32" t="s">
@@ -57155,14 +57158,14 @@
         <v>149</v>
       </c>
       <c r="AT124" s="32" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="AU124" s="42" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="AV124" s="42"/>
       <c r="AW124" s="42" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="AX124" s="42"/>
       <c r="AY124" s="42"/>

--- a/metadata.xlsx
+++ b/metadata.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30219"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC7CB448-705B-4C79-91AC-B0DD7B347339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{99311BF2-83E0-4BF7-9952-B0DE8E57F3E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -237,7 +237,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5034" uniqueCount="1805">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5036" uniqueCount="1804">
   <si>
     <t>VJDBv1.1</t>
   </si>
@@ -5090,19 +5090,16 @@
     <t>0iy</t>
   </si>
   <si>
-    <t>sequence_url</t>
-  </si>
-  <si>
-    <t>GenBank URL</t>
-  </si>
-  <si>
-    <t>URL to the GenBank record from the ICTV VMR</t>
-  </si>
-  <si>
-    <t>Accessions Link</t>
-  </si>
-  <si>
-    <t>Link to the GenBank record(s) in columns X.</t>
+    <t>checkv_version</t>
+  </si>
+  <si>
+    <t>CheckV Version</t>
+  </si>
+  <si>
+    <t>CheckV run version and CheckV database version used for evaluation of the record.</t>
+  </si>
+  <si>
+    <t>Checkv Version</t>
   </si>
   <si>
     <t>VJDBv0.3</t>
@@ -45174,7 +45171,7 @@
         <v>216</v>
       </c>
       <c r="F224" s="54" t="s">
-        <v>154</v>
+        <v>64</v>
       </c>
       <c r="G224" s="54"/>
       <c r="H224" s="54"/>
@@ -45269,7 +45266,7 @@
         <v>63</v>
       </c>
       <c r="F225" s="54" t="s">
-        <v>154</v>
+        <v>64</v>
       </c>
       <c r="G225" s="54"/>
       <c r="H225" s="54"/>
@@ -45364,7 +45361,7 @@
         <v>216</v>
       </c>
       <c r="F226" s="54" t="s">
-        <v>154</v>
+        <v>64</v>
       </c>
       <c r="G226" s="54"/>
       <c r="H226" s="54"/>
@@ -45459,7 +45456,7 @@
         <v>216</v>
       </c>
       <c r="F227" s="54" t="s">
-        <v>154</v>
+        <v>64</v>
       </c>
       <c r="G227" s="54"/>
       <c r="H227" s="54"/>
@@ -45554,7 +45551,7 @@
         <v>216</v>
       </c>
       <c r="F228" s="54" t="s">
-        <v>154</v>
+        <v>64</v>
       </c>
       <c r="G228" s="54"/>
       <c r="H228" s="54"/>
@@ -45649,7 +45646,7 @@
         <v>216</v>
       </c>
       <c r="F229" s="54" t="s">
-        <v>154</v>
+        <v>64</v>
       </c>
       <c r="G229" s="54"/>
       <c r="H229" s="54"/>
@@ -45744,7 +45741,7 @@
         <v>63</v>
       </c>
       <c r="F230" s="54" t="s">
-        <v>154</v>
+        <v>64</v>
       </c>
       <c r="G230" s="54"/>
       <c r="H230" s="54"/>
@@ -45839,7 +45836,7 @@
         <v>63</v>
       </c>
       <c r="F231" s="54" t="s">
-        <v>154</v>
+        <v>64</v>
       </c>
       <c r="G231" s="54"/>
       <c r="H231" s="54"/>
@@ -45934,7 +45931,7 @@
         <v>254</v>
       </c>
       <c r="F232" s="54" t="s">
-        <v>154</v>
+        <v>64</v>
       </c>
       <c r="G232" s="54"/>
       <c r="H232" s="54"/>
@@ -46029,7 +46026,7 @@
         <v>76</v>
       </c>
       <c r="F233" s="54" t="s">
-        <v>154</v>
+        <v>64</v>
       </c>
       <c r="G233" s="54"/>
       <c r="H233" s="54"/>
@@ -46124,7 +46121,7 @@
         <v>254</v>
       </c>
       <c r="F234" s="54" t="s">
-        <v>154</v>
+        <v>64</v>
       </c>
       <c r="G234" s="54"/>
       <c r="H234" s="54"/>
@@ -46219,7 +46216,7 @@
         <v>216</v>
       </c>
       <c r="F235" s="54" t="s">
-        <v>154</v>
+        <v>64</v>
       </c>
       <c r="G235" s="54"/>
       <c r="H235" s="54"/>
@@ -46314,7 +46311,7 @@
         <v>63</v>
       </c>
       <c r="F236" s="54" t="s">
-        <v>154</v>
+        <v>64</v>
       </c>
       <c r="G236" s="54"/>
       <c r="H236" s="54"/>
@@ -46409,7 +46406,7 @@
         <v>63</v>
       </c>
       <c r="F237" s="54" t="s">
-        <v>342</v>
+        <v>154</v>
       </c>
       <c r="G237" s="54"/>
       <c r="H237" s="54"/>
@@ -46426,10 +46423,36 @@
       <c r="S237" s="54"/>
       <c r="T237" s="54"/>
       <c r="U237" s="54"/>
-      <c r="V237" s="54"/>
+      <c r="V237" s="54" t="s">
+        <v>587</v>
+      </c>
       <c r="W237" s="54"/>
-      <c r="X237" s="54"/>
-      <c r="Y237" s="54"/>
+      <c r="X237" s="54" t="s">
+        <v>219</v>
+      </c>
+      <c r="Y237" s="54" t="str">
+        <f>"[" &amp; _xlfn.TEXTJOIN(", ", TRUE,
+    IF(G237&lt;&gt;"", """" &amp; G$1 &amp; """", ""),
+    IF(H237&lt;&gt;"", """" &amp; H$1 &amp; """", ""),
+    IF(I237&lt;&gt;"", """" &amp; I$1 &amp; """", ""),
+    IF(J237&lt;&gt;"", """" &amp; J$1 &amp; """", ""),
+    IF(K237&lt;&gt;"", """" &amp; K$1 &amp; """", ""),
+    IF(L237&lt;&gt;"", """" &amp; L$1 &amp; """", ""),
+    IF(M237&lt;&gt;"", """" &amp; M$1 &amp; """", ""),
+    IF(N237&lt;&gt;"", """" &amp; N$1 &amp; """", ""),
+    IF(O237&lt;&gt;"", """" &amp; O$1 &amp; """", ""),
+    IF(P237&lt;&gt;"", """" &amp; P$1 &amp; """", ""),
+    IF(Q237&lt;&gt;"", """" &amp; Q$1 &amp; """", ""),
+    IF(R237&lt;&gt;"", """" &amp; R$1 &amp; """", ""),
+    IF(S237&lt;&gt;"", """" &amp; S$1 &amp; """", ""),
+    IF(T237&lt;&gt;"", """" &amp; T237 &amp; """", ""),
+    IF(U237&lt;&gt;"", """" &amp; U237 &amp; """", ""),
+    IF(V237&lt;&gt;"", """" &amp; V237 &amp; """", ""),
+    IF(W237&lt;&gt;"", """" &amp; W237 &amp; """", ""),
+    IF(X237&lt;&gt;"", """" &amp; X237 &amp; """", "")
+) &amp; "]"</f>
+        <v>["Analysis", "Workflows"]</v>
+      </c>
       <c r="Z237" s="54"/>
       <c r="AA237" s="54"/>
       <c r="AB237" s="54"/>
@@ -46459,8 +46482,8 @@
       <c r="AZ237" s="56" t="s">
         <v>1603</v>
       </c>
-      <c r="BA237" s="57" t="s">
-        <v>1604</v>
+      <c r="BA237" s="71" t="s">
+        <v>1602</v>
       </c>
     </row>
   </sheetData>
@@ -46495,25 +46518,25 @@
   <sheetData>
     <row r="1" spans="1:172" s="19" customFormat="1" ht="23.25" customHeight="1">
       <c r="A1" s="17" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>1604</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>1604</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>1604</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>1604</v>
+      </c>
+      <c r="F1" s="18" t="s">
         <v>1605</v>
       </c>
-      <c r="B1" s="17" t="s">
-        <v>1605</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>1605</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>1605</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>1605</v>
-      </c>
-      <c r="F1" s="18" t="s">
+      <c r="G1" s="18" t="s">
         <v>1606</v>
-      </c>
-      <c r="G1" s="18" t="s">
-        <v>1607</v>
       </c>
       <c r="H1" s="18" t="s">
         <v>1</v>
@@ -46546,25 +46569,25 @@
         <v>14</v>
       </c>
       <c r="R1" s="20" t="s">
+        <v>1604</v>
+      </c>
+      <c r="S1" s="20" t="s">
+        <v>1604</v>
+      </c>
+      <c r="T1" s="20" t="s">
+        <v>1604</v>
+      </c>
+      <c r="U1" s="20" t="s">
+        <v>1604</v>
+      </c>
+      <c r="V1" s="20" t="s">
+        <v>1604</v>
+      </c>
+      <c r="W1" s="20" t="s">
+        <v>1604</v>
+      </c>
+      <c r="X1" s="18" t="s">
         <v>1605</v>
-      </c>
-      <c r="S1" s="20" t="s">
-        <v>1605</v>
-      </c>
-      <c r="T1" s="20" t="s">
-        <v>1605</v>
-      </c>
-      <c r="U1" s="20" t="s">
-        <v>1605</v>
-      </c>
-      <c r="V1" s="20" t="s">
-        <v>1605</v>
-      </c>
-      <c r="W1" s="20" t="s">
-        <v>1605</v>
-      </c>
-      <c r="X1" s="18" t="s">
-        <v>1606</v>
       </c>
       <c r="Y1" s="20" t="s">
         <v>6</v>
@@ -46764,13 +46787,13 @@
         <v>22</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="E2" s="19" t="s">
         <v>24</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="G2" s="18" t="s">
         <v>20</v>
@@ -46824,7 +46847,7 @@
         <v>35</v>
       </c>
       <c r="X2" s="19" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="Y2" s="19" t="s">
         <v>36</v>
@@ -47659,7 +47682,7 @@
         <v>359</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X5" s="8"/>
       <c r="Y5" s="8"/>
@@ -47669,14 +47692,14 @@
       <c r="AC5" s="8"/>
       <c r="AD5" s="8"/>
       <c r="AE5" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="AF5" s="2" t="s">
         <v>1612</v>
-      </c>
-      <c r="AF5" s="2" t="s">
-        <v>1613</v>
       </c>
       <c r="AG5" s="8"/>
       <c r="AH5" s="9" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI5" s="8"/>
       <c r="AJ5" s="8"/>
@@ -47703,7 +47726,7 @@
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
@@ -47728,7 +47751,7 @@
         <v>359</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X6" s="13"/>
       <c r="Y6" s="13"/>
@@ -47740,14 +47763,14 @@
       </c>
       <c r="AD6" s="13"/>
       <c r="AE6" s="1" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="AF6" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG6" s="13"/>
       <c r="AH6" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI6" s="13"/>
       <c r="AJ6" s="13"/>
@@ -47797,7 +47820,7 @@
         <v>359</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X7" s="13"/>
       <c r="Y7" s="13"/>
@@ -47809,14 +47832,14 @@
         <v>127</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="AF7" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG7" s="13"/>
       <c r="AH7" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI7" s="13"/>
       <c r="AJ7" s="13"/>
@@ -47866,7 +47889,7 @@
         <v>359</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X8" s="13"/>
       <c r="Y8" s="13"/>
@@ -47876,14 +47899,14 @@
       <c r="AC8" s="13"/>
       <c r="AD8" s="13"/>
       <c r="AE8" s="1" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="AF8" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG8" s="13"/>
       <c r="AH8" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI8" s="13"/>
       <c r="AJ8" s="13"/>
@@ -47933,7 +47956,7 @@
         <v>359</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X9" s="13"/>
       <c r="Y9" s="13"/>
@@ -47943,14 +47966,14 @@
       <c r="AC9" s="13"/>
       <c r="AD9" s="13"/>
       <c r="AE9" s="1" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="AF9" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG9" s="13"/>
       <c r="AH9" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI9" s="13"/>
       <c r="AJ9" s="13"/>
@@ -47977,7 +48000,7 @@
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="O10" s="6"/>
       <c r="P10" s="6"/>
@@ -48002,7 +48025,7 @@
         <v>359</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X10" s="13"/>
       <c r="Y10" s="13"/>
@@ -48014,14 +48037,14 @@
       </c>
       <c r="AD10" s="13"/>
       <c r="AE10" s="1" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="AF10" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG10" s="13"/>
       <c r="AH10" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI10" s="13"/>
       <c r="AJ10" s="13"/>
@@ -48048,7 +48071,7 @@
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
@@ -48073,7 +48096,7 @@
         <v>359</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X11" s="13"/>
       <c r="Y11" s="13"/>
@@ -48085,14 +48108,14 @@
       </c>
       <c r="AD11" s="13"/>
       <c r="AE11" s="1" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="AF11" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG11" s="13"/>
       <c r="AH11" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI11" s="13"/>
       <c r="AJ11" s="13"/>
@@ -48142,7 +48165,7 @@
         <v>359</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X12" s="13"/>
       <c r="Y12" s="13"/>
@@ -48152,14 +48175,14 @@
       <c r="AC12" s="13"/>
       <c r="AD12" s="13"/>
       <c r="AE12" s="1" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="AF12" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG12" s="13"/>
       <c r="AH12" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI12" s="13"/>
       <c r="AJ12" s="13"/>
@@ -48209,7 +48232,7 @@
         <v>359</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X13" s="13"/>
       <c r="Y13" s="13"/>
@@ -48219,14 +48242,14 @@
       <c r="AC13" s="13"/>
       <c r="AD13" s="13"/>
       <c r="AE13" s="1" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="AF13" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG13" s="13"/>
       <c r="AH13" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI13" s="13"/>
       <c r="AJ13" s="13"/>
@@ -48253,7 +48276,7 @@
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
@@ -48278,7 +48301,7 @@
         <v>359</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X14" s="13"/>
       <c r="Y14" s="13"/>
@@ -48286,20 +48309,20 @@
       <c r="AA14" s="13"/>
       <c r="AB14" s="13"/>
       <c r="AC14" s="1" t="s">
+        <v>1625</v>
+      </c>
+      <c r="AD14" s="1" t="s">
+        <v>1625</v>
+      </c>
+      <c r="AE14" s="1" t="s">
         <v>1626</v>
-      </c>
-      <c r="AD14" s="1" t="s">
-        <v>1626</v>
-      </c>
-      <c r="AE14" s="1" t="s">
-        <v>1627</v>
       </c>
       <c r="AF14" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG14" s="13"/>
       <c r="AH14" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI14" s="13"/>
       <c r="AJ14" s="13"/>
@@ -48349,7 +48372,7 @@
         <v>359</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X15" s="13"/>
       <c r="Y15" s="13"/>
@@ -48358,17 +48381,17 @@
       <c r="AB15" s="13"/>
       <c r="AC15" s="13"/>
       <c r="AD15" s="1" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="AF15" s="1" t="s">
         <v>254</v>
       </c>
       <c r="AG15" s="13"/>
       <c r="AH15" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI15" s="13"/>
       <c r="AJ15" s="13"/>
@@ -48418,7 +48441,7 @@
         <v>359</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X16" s="13"/>
       <c r="Y16" s="13"/>
@@ -48428,14 +48451,14 @@
       <c r="AC16" s="13"/>
       <c r="AD16" s="13"/>
       <c r="AE16" s="1" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="AF16" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG16" s="13"/>
       <c r="AH16" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI16" s="13"/>
       <c r="AJ16" s="13"/>
@@ -48462,7 +48485,7 @@
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
       <c r="N17" s="4" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="O17" s="6"/>
       <c r="P17" s="6"/>
@@ -48487,7 +48510,7 @@
         <v>359</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X17" s="13"/>
       <c r="Y17" s="13"/>
@@ -48495,20 +48518,20 @@
       <c r="AA17" s="13"/>
       <c r="AB17" s="13"/>
       <c r="AC17" s="1" t="s">
+        <v>1630</v>
+      </c>
+      <c r="AD17" s="1" t="s">
         <v>1631</v>
       </c>
-      <c r="AD17" s="1" t="s">
+      <c r="AE17" s="1" t="s">
         <v>1632</v>
-      </c>
-      <c r="AE17" s="1" t="s">
-        <v>1633</v>
       </c>
       <c r="AF17" s="1" t="s">
         <v>254</v>
       </c>
       <c r="AG17" s="13"/>
       <c r="AH17" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI17" s="13"/>
       <c r="AJ17" s="13"/>
@@ -48535,7 +48558,7 @@
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
       <c r="N18" s="4" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="O18" s="6"/>
       <c r="P18" s="6"/>
@@ -48560,7 +48583,7 @@
         <v>359</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X18" s="13"/>
       <c r="Y18" s="13"/>
@@ -48568,20 +48591,20 @@
       <c r="AA18" s="13"/>
       <c r="AB18" s="13"/>
       <c r="AC18" s="1" t="s">
+        <v>1630</v>
+      </c>
+      <c r="AD18" s="1" t="s">
         <v>1631</v>
       </c>
-      <c r="AD18" s="1" t="s">
-        <v>1632</v>
-      </c>
       <c r="AE18" s="1" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="AF18" s="1" t="s">
         <v>254</v>
       </c>
       <c r="AG18" s="13"/>
       <c r="AH18" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI18" s="13"/>
       <c r="AJ18" s="13"/>
@@ -48608,7 +48631,7 @@
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
       <c r="N19" s="4" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="O19" s="6"/>
       <c r="P19" s="6"/>
@@ -48633,7 +48656,7 @@
         <v>359</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X19" s="13"/>
       <c r="Y19" s="13"/>
@@ -48647,14 +48670,14 @@
         <v>222</v>
       </c>
       <c r="AE19" s="1" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="AF19" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG19" s="13"/>
       <c r="AH19" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI19" s="13"/>
       <c r="AJ19" s="13"/>
@@ -48681,7 +48704,7 @@
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
       <c r="N20" s="4" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="O20" s="6"/>
       <c r="P20" s="6"/>
@@ -48706,7 +48729,7 @@
         <v>359</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X20" s="13"/>
       <c r="Y20" s="13"/>
@@ -48718,14 +48741,14 @@
       </c>
       <c r="AD20" s="13"/>
       <c r="AE20" s="1" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="AF20" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG20" s="13"/>
       <c r="AH20" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI20" s="13"/>
       <c r="AJ20" s="13"/>
@@ -48797,7 +48820,7 @@
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
       <c r="N22" s="4" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="O22" s="6"/>
       <c r="P22" s="6"/>
@@ -48822,7 +48845,7 @@
         <v>359</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X22" s="13"/>
       <c r="Y22" s="13"/>
@@ -48830,20 +48853,20 @@
       <c r="AA22" s="13"/>
       <c r="AB22" s="13"/>
       <c r="AC22" s="1" t="s">
+        <v>1630</v>
+      </c>
+      <c r="AD22" s="1" t="s">
         <v>1631</v>
       </c>
-      <c r="AD22" s="1" t="s">
-        <v>1632</v>
-      </c>
       <c r="AE22" s="1" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="AF22" s="1" t="s">
         <v>254</v>
       </c>
       <c r="AG22" s="13"/>
       <c r="AH22" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI22" s="13"/>
       <c r="AJ22" s="13"/>
@@ -48870,7 +48893,7 @@
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
       <c r="N23" s="4" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="O23" s="6"/>
       <c r="P23" s="6"/>
@@ -48895,7 +48918,7 @@
         <v>359</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X23" s="13"/>
       <c r="Y23" s="13"/>
@@ -48909,14 +48932,14 @@
         <v>127</v>
       </c>
       <c r="AE23" s="1" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="AF23" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG23" s="13"/>
       <c r="AH23" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI23" s="13"/>
       <c r="AJ23" s="13"/>
@@ -48943,7 +48966,7 @@
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
       <c r="N24" s="4" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="O24" s="6"/>
       <c r="P24" s="6"/>
@@ -48968,7 +48991,7 @@
         <v>359</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X24" s="13"/>
       <c r="Y24" s="13"/>
@@ -48980,14 +49003,14 @@
       </c>
       <c r="AD24" s="13"/>
       <c r="AE24" s="1" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="AF24" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG24" s="13"/>
       <c r="AH24" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI24" s="13"/>
       <c r="AJ24" s="13"/>
@@ -49037,7 +49060,7 @@
         <v>359</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X25" s="13"/>
       <c r="Y25" s="13"/>
@@ -49047,14 +49070,14 @@
       <c r="AC25" s="13"/>
       <c r="AD25" s="13"/>
       <c r="AE25" s="1" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="AF25" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG25" s="13"/>
       <c r="AH25" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI25" s="13"/>
       <c r="AJ25" s="13"/>
@@ -49081,7 +49104,7 @@
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
       <c r="N26" s="4" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="O26" s="6"/>
       <c r="P26" s="6"/>
@@ -49106,7 +49129,7 @@
         <v>359</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X26" s="13"/>
       <c r="Y26" s="13"/>
@@ -49118,14 +49141,14 @@
       </c>
       <c r="AD26" s="13"/>
       <c r="AE26" s="1" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="AF26" s="1" t="s">
         <v>714</v>
       </c>
       <c r="AG26" s="13"/>
       <c r="AH26" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI26" s="13"/>
       <c r="AJ26" s="13"/>
@@ -49152,7 +49175,7 @@
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
       <c r="N27" s="4" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="O27" s="6"/>
       <c r="P27" s="6"/>
@@ -49177,7 +49200,7 @@
         <v>359</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X27" s="13"/>
       <c r="Y27" s="13"/>
@@ -49191,14 +49214,14 @@
         <v>222</v>
       </c>
       <c r="AE27" s="1" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="AF27" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG27" s="13"/>
       <c r="AH27" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI27" s="13"/>
       <c r="AJ27" s="13"/>
@@ -49225,7 +49248,7 @@
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
       <c r="N28" s="4" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="O28" s="6"/>
       <c r="P28" s="6"/>
@@ -49250,7 +49273,7 @@
         <v>359</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X28" s="13"/>
       <c r="Y28" s="13"/>
@@ -49264,14 +49287,14 @@
         <v>222</v>
       </c>
       <c r="AE28" s="1" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="AF28" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG28" s="13"/>
       <c r="AH28" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI28" s="13"/>
       <c r="AJ28" s="13"/>
@@ -49298,7 +49321,7 @@
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
       <c r="N29" s="4" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="O29" s="6"/>
       <c r="P29" s="6"/>
@@ -49323,7 +49346,7 @@
         <v>359</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X29" s="13"/>
       <c r="Y29" s="13"/>
@@ -49337,14 +49360,14 @@
         <v>222</v>
       </c>
       <c r="AE29" s="1" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="AF29" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG29" s="13"/>
       <c r="AH29" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI29" s="13"/>
       <c r="AJ29" s="13"/>
@@ -49394,7 +49417,7 @@
         <v>359</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X30" s="13"/>
       <c r="Y30" s="13"/>
@@ -49403,17 +49426,17 @@
       <c r="AB30" s="13"/>
       <c r="AC30" s="13"/>
       <c r="AD30" s="1" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="AE30" s="1" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="AF30" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG30" s="13"/>
       <c r="AH30" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI30" s="13"/>
       <c r="AJ30" s="13"/>
@@ -49463,7 +49486,7 @@
         <v>359</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X31" s="13"/>
       <c r="Y31" s="13"/>
@@ -49472,17 +49495,17 @@
       <c r="AB31" s="13"/>
       <c r="AC31" s="13"/>
       <c r="AD31" s="1" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="AE31" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="AF31" s="1" t="s">
         <v>254</v>
       </c>
       <c r="AG31" s="13"/>
       <c r="AH31" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI31" s="13"/>
       <c r="AJ31" s="13"/>
@@ -49509,7 +49532,7 @@
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
       <c r="N32" s="4" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="O32" s="6"/>
       <c r="P32" s="6"/>
@@ -49534,7 +49557,7 @@
         <v>359</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X32" s="13"/>
       <c r="Y32" s="13"/>
@@ -49546,14 +49569,14 @@
       </c>
       <c r="AD32" s="13"/>
       <c r="AE32" s="1" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="AF32" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG32" s="13"/>
       <c r="AH32" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI32" s="13"/>
       <c r="AJ32" s="13"/>
@@ -49603,7 +49626,7 @@
         <v>359</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X33" s="13"/>
       <c r="Y33" s="13"/>
@@ -49613,14 +49636,14 @@
       <c r="AC33" s="13"/>
       <c r="AD33" s="13"/>
       <c r="AE33" s="1" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="AF33" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG33" s="13"/>
       <c r="AH33" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI33" s="13"/>
       <c r="AJ33" s="13"/>
@@ -49647,7 +49670,7 @@
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
       <c r="N34" s="4" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="O34" s="6"/>
       <c r="P34" s="6"/>
@@ -49672,7 +49695,7 @@
         <v>359</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X34" s="13"/>
       <c r="Y34" s="13"/>
@@ -49684,14 +49707,14 @@
       </c>
       <c r="AD34" s="13"/>
       <c r="AE34" s="1" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="AF34" s="1" t="s">
         <v>714</v>
       </c>
       <c r="AG34" s="13"/>
       <c r="AH34" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI34" s="13"/>
       <c r="AJ34" s="13"/>
@@ -49741,7 +49764,7 @@
         <v>359</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X35" s="13"/>
       <c r="Y35" s="13"/>
@@ -49753,14 +49776,14 @@
         <v>127</v>
       </c>
       <c r="AE35" s="1" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="AF35" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG35" s="13"/>
       <c r="AH35" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI35" s="13"/>
       <c r="AJ35" s="13"/>
@@ -49810,7 +49833,7 @@
         <v>359</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X36" s="13"/>
       <c r="Y36" s="13"/>
@@ -49820,14 +49843,14 @@
       <c r="AC36" s="13"/>
       <c r="AD36" s="13"/>
       <c r="AE36" s="1" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="AF36" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG36" s="13"/>
       <c r="AH36" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI36" s="13"/>
       <c r="AJ36" s="13"/>
@@ -49854,7 +49877,7 @@
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
       <c r="N37" s="4" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="O37" s="6"/>
       <c r="P37" s="6"/>
@@ -49879,7 +49902,7 @@
         <v>359</v>
       </c>
       <c r="W37" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X37" s="13"/>
       <c r="Y37" s="13"/>
@@ -49887,20 +49910,20 @@
       <c r="AA37" s="13"/>
       <c r="AB37" s="13"/>
       <c r="AC37" s="1" t="s">
+        <v>1630</v>
+      </c>
+      <c r="AD37" s="1" t="s">
         <v>1631</v>
       </c>
-      <c r="AD37" s="1" t="s">
-        <v>1632</v>
-      </c>
       <c r="AE37" s="1" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="AF37" s="1" t="s">
         <v>254</v>
       </c>
       <c r="AG37" s="13"/>
       <c r="AH37" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI37" s="13"/>
       <c r="AJ37" s="13"/>
@@ -49927,7 +49950,7 @@
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
       <c r="N38" s="4" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="O38" s="6"/>
       <c r="P38" s="6"/>
@@ -49952,7 +49975,7 @@
         <v>359</v>
       </c>
       <c r="W38" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X38" s="13"/>
       <c r="Y38" s="13"/>
@@ -49960,20 +49983,20 @@
       <c r="AA38" s="13"/>
       <c r="AB38" s="13"/>
       <c r="AC38" s="1" t="s">
+        <v>1630</v>
+      </c>
+      <c r="AD38" s="1" t="s">
         <v>1631</v>
       </c>
-      <c r="AD38" s="1" t="s">
-        <v>1632</v>
-      </c>
       <c r="AE38" s="1" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="AF38" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG38" s="13"/>
       <c r="AH38" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI38" s="13"/>
       <c r="AJ38" s="13"/>
@@ -50000,7 +50023,7 @@
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
       <c r="N39" s="4" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="O39" s="6"/>
       <c r="P39" s="6"/>
@@ -50025,7 +50048,7 @@
         <v>359</v>
       </c>
       <c r="W39" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X39" s="13"/>
       <c r="Y39" s="13"/>
@@ -50033,20 +50056,20 @@
       <c r="AA39" s="13"/>
       <c r="AB39" s="13"/>
       <c r="AC39" s="1" t="s">
+        <v>1630</v>
+      </c>
+      <c r="AD39" s="1" t="s">
         <v>1631</v>
       </c>
-      <c r="AD39" s="1" t="s">
-        <v>1632</v>
-      </c>
       <c r="AE39" s="1" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="AF39" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG39" s="13"/>
       <c r="AH39" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI39" s="13"/>
       <c r="AJ39" s="13"/>
@@ -50073,7 +50096,7 @@
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
       <c r="N40" s="4" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="O40" s="6"/>
       <c r="P40" s="6"/>
@@ -50098,7 +50121,7 @@
         <v>359</v>
       </c>
       <c r="W40" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X40" s="13"/>
       <c r="Y40" s="13"/>
@@ -50106,18 +50129,18 @@
       <c r="AA40" s="13"/>
       <c r="AB40" s="13"/>
       <c r="AC40" s="1" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="AD40" s="13"/>
       <c r="AE40" s="1" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="AF40" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG40" s="13"/>
       <c r="AH40" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI40" s="13"/>
       <c r="AJ40" s="13"/>
@@ -50144,7 +50167,7 @@
       <c r="L41" s="4"/>
       <c r="M41" s="4"/>
       <c r="N41" s="4" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="O41" s="6"/>
       <c r="P41" s="6"/>
@@ -50169,7 +50192,7 @@
         <v>359</v>
       </c>
       <c r="W41" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X41" s="13"/>
       <c r="Y41" s="13"/>
@@ -50183,14 +50206,14 @@
         <v>127</v>
       </c>
       <c r="AE41" s="1" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="AF41" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG41" s="13"/>
       <c r="AH41" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI41" s="13"/>
       <c r="AJ41" s="13"/>
@@ -50240,7 +50263,7 @@
         <v>359</v>
       </c>
       <c r="W42" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X42" s="13"/>
       <c r="Y42" s="13"/>
@@ -50250,14 +50273,14 @@
       <c r="AC42" s="13"/>
       <c r="AD42" s="13"/>
       <c r="AE42" s="1" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="AF42" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG42" s="13"/>
       <c r="AH42" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI42" s="13"/>
       <c r="AJ42" s="13"/>
@@ -50284,7 +50307,7 @@
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
       <c r="N43" s="4" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="O43" s="6"/>
       <c r="P43" s="6"/>
@@ -50309,7 +50332,7 @@
         <v>359</v>
       </c>
       <c r="W43" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X43" s="13"/>
       <c r="Y43" s="13"/>
@@ -50321,14 +50344,14 @@
       </c>
       <c r="AD43" s="13"/>
       <c r="AE43" s="1" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="AF43" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG43" s="13"/>
       <c r="AH43" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI43" s="13"/>
       <c r="AJ43" s="13"/>
@@ -50355,7 +50378,7 @@
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
       <c r="N44" s="4" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="O44" s="6"/>
       <c r="P44" s="6"/>
@@ -50380,7 +50403,7 @@
         <v>359</v>
       </c>
       <c r="W44" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X44" s="13"/>
       <c r="Y44" s="13"/>
@@ -50392,14 +50415,14 @@
       </c>
       <c r="AD44" s="13"/>
       <c r="AE44" s="1" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="AF44" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG44" s="13"/>
       <c r="AH44" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI44" s="13"/>
       <c r="AJ44" s="13"/>
@@ -50426,7 +50449,7 @@
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
       <c r="N45" s="4" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="O45" s="6"/>
       <c r="P45" s="6"/>
@@ -50451,7 +50474,7 @@
         <v>359</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X45" s="13"/>
       <c r="Y45" s="13"/>
@@ -50463,14 +50486,14 @@
       </c>
       <c r="AD45" s="13"/>
       <c r="AE45" s="1" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="AF45" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG45" s="13"/>
       <c r="AH45" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI45" s="13"/>
       <c r="AJ45" s="13"/>
@@ -50520,7 +50543,7 @@
         <v>359</v>
       </c>
       <c r="W46" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X46" s="13"/>
       <c r="Y46" s="13"/>
@@ -50530,14 +50553,14 @@
       <c r="AC46" s="13"/>
       <c r="AD46" s="13"/>
       <c r="AE46" s="1" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="AF46" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG46" s="13"/>
       <c r="AH46" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI46" s="13"/>
       <c r="AJ46" s="13"/>
@@ -50564,7 +50587,7 @@
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
       <c r="N47" s="4" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="O47" s="6"/>
       <c r="P47" s="6"/>
@@ -50589,7 +50612,7 @@
         <v>359</v>
       </c>
       <c r="W47" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X47" s="13"/>
       <c r="Y47" s="13"/>
@@ -50601,14 +50624,14 @@
       </c>
       <c r="AD47" s="13"/>
       <c r="AE47" s="1" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="AF47" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG47" s="13"/>
       <c r="AH47" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI47" s="13"/>
       <c r="AJ47" s="13"/>
@@ -50658,7 +50681,7 @@
         <v>359</v>
       </c>
       <c r="W48" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X48" s="13"/>
       <c r="Y48" s="13"/>
@@ -50668,14 +50691,14 @@
       <c r="AC48" s="13"/>
       <c r="AD48" s="13"/>
       <c r="AE48" s="1" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="AF48" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG48" s="13"/>
       <c r="AH48" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI48" s="13"/>
       <c r="AJ48" s="13"/>
@@ -50702,7 +50725,7 @@
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
       <c r="N49" s="4" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="O49" s="6"/>
       <c r="P49" s="6"/>
@@ -50727,7 +50750,7 @@
         <v>359</v>
       </c>
       <c r="W49" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X49" s="13"/>
       <c r="Y49" s="13"/>
@@ -50739,14 +50762,14 @@
       </c>
       <c r="AD49" s="13"/>
       <c r="AE49" s="1" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="AF49" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG49" s="13"/>
       <c r="AH49" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI49" s="13"/>
       <c r="AJ49" s="13"/>
@@ -50796,7 +50819,7 @@
         <v>359</v>
       </c>
       <c r="W50" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X50" s="13"/>
       <c r="Y50" s="13"/>
@@ -50806,14 +50829,14 @@
       <c r="AC50" s="13"/>
       <c r="AD50" s="13"/>
       <c r="AE50" s="1" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="AF50" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG50" s="13"/>
       <c r="AH50" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI50" s="13"/>
       <c r="AJ50" s="13"/>
@@ -50863,7 +50886,7 @@
         <v>359</v>
       </c>
       <c r="W51" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X51" s="13"/>
       <c r="Y51" s="13"/>
@@ -50872,17 +50895,17 @@
       <c r="AB51" s="13"/>
       <c r="AC51" s="13"/>
       <c r="AD51" s="1" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="AE51" s="1" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="AF51" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG51" s="13"/>
       <c r="AH51" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI51" s="13"/>
       <c r="AJ51" s="13"/>
@@ -50932,7 +50955,7 @@
         <v>359</v>
       </c>
       <c r="W52" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X52" s="13"/>
       <c r="Y52" s="13"/>
@@ -50941,17 +50964,17 @@
       <c r="AB52" s="13"/>
       <c r="AC52" s="13"/>
       <c r="AD52" s="1" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="AE52" s="1" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="AF52" s="1" t="s">
         <v>254</v>
       </c>
       <c r="AG52" s="13"/>
       <c r="AH52" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI52" s="13"/>
       <c r="AJ52" s="13"/>
@@ -50978,7 +51001,7 @@
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
       <c r="N53" s="4" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="O53" s="6"/>
       <c r="P53" s="6"/>
@@ -51003,7 +51026,7 @@
         <v>359</v>
       </c>
       <c r="W53" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X53" s="13"/>
       <c r="Y53" s="13"/>
@@ -51017,14 +51040,14 @@
         <v>127</v>
       </c>
       <c r="AE53" s="1" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="AF53" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG53" s="13"/>
       <c r="AH53" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI53" s="13"/>
       <c r="AJ53" s="13"/>
@@ -51074,7 +51097,7 @@
         <v>359</v>
       </c>
       <c r="W54" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X54" s="13"/>
       <c r="Y54" s="13"/>
@@ -51086,14 +51109,14 @@
         <v>127</v>
       </c>
       <c r="AE54" s="1" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="AF54" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG54" s="13"/>
       <c r="AH54" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI54" s="13"/>
       <c r="AJ54" s="13"/>
@@ -51120,7 +51143,7 @@
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
       <c r="N55" s="4" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="O55" s="6"/>
       <c r="P55" s="6"/>
@@ -51145,7 +51168,7 @@
         <v>359</v>
       </c>
       <c r="W55" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X55" s="13"/>
       <c r="Y55" s="13"/>
@@ -51159,14 +51182,14 @@
         <v>127</v>
       </c>
       <c r="AE55" s="1" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="AF55" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG55" s="13"/>
       <c r="AH55" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI55" s="13"/>
       <c r="AJ55" s="13"/>
@@ -51240,7 +51263,7 @@
         <v>359</v>
       </c>
       <c r="W57" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X57" s="13"/>
       <c r="Y57" s="13"/>
@@ -51252,14 +51275,14 @@
         <v>127</v>
       </c>
       <c r="AE57" s="1" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="AF57" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG57" s="13"/>
       <c r="AH57" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI57" s="13"/>
       <c r="AJ57" s="13"/>
@@ -51309,7 +51332,7 @@
         <v>359</v>
       </c>
       <c r="W58" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X58" s="13"/>
       <c r="Y58" s="13"/>
@@ -51321,14 +51344,14 @@
         <v>127</v>
       </c>
       <c r="AE58" s="1" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="AF58" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG58" s="13"/>
       <c r="AH58" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI58" s="13"/>
       <c r="AJ58" s="13"/>
@@ -51355,7 +51378,7 @@
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
       <c r="N59" s="4" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="O59" s="6"/>
       <c r="P59" s="6"/>
@@ -51380,7 +51403,7 @@
         <v>359</v>
       </c>
       <c r="W59" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X59" s="13"/>
       <c r="Y59" s="13"/>
@@ -51388,20 +51411,20 @@
       <c r="AA59" s="13"/>
       <c r="AB59" s="13"/>
       <c r="AC59" s="1" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="AD59" s="1" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="AE59" s="1" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="AF59" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG59" s="13"/>
       <c r="AH59" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI59" s="13"/>
       <c r="AJ59" s="13"/>
@@ -51451,7 +51474,7 @@
         <v>359</v>
       </c>
       <c r="W60" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X60" s="13"/>
       <c r="Y60" s="13"/>
@@ -51460,17 +51483,17 @@
       <c r="AB60" s="13"/>
       <c r="AC60" s="13"/>
       <c r="AD60" s="1" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="AE60" s="1" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="AF60" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG60" s="13"/>
       <c r="AH60" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI60" s="13"/>
       <c r="AJ60" s="13"/>
@@ -51497,7 +51520,7 @@
       <c r="L61" s="4"/>
       <c r="M61" s="4"/>
       <c r="N61" s="4" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="O61" s="6"/>
       <c r="P61" s="6"/>
@@ -51522,7 +51545,7 @@
         <v>359</v>
       </c>
       <c r="W61" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X61" s="13"/>
       <c r="Y61" s="13"/>
@@ -51534,14 +51557,14 @@
       </c>
       <c r="AD61" s="13"/>
       <c r="AE61" s="1" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="AF61" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG61" s="13"/>
       <c r="AH61" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI61" s="13"/>
       <c r="AJ61" s="13"/>
@@ -51591,7 +51614,7 @@
         <v>359</v>
       </c>
       <c r="W62" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X62" s="13"/>
       <c r="Y62" s="13"/>
@@ -51601,14 +51624,14 @@
       <c r="AC62" s="13"/>
       <c r="AD62" s="13"/>
       <c r="AE62" s="1" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="AF62" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG62" s="13"/>
       <c r="AH62" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI62" s="13"/>
       <c r="AJ62" s="13"/>
@@ -51635,7 +51658,7 @@
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
       <c r="N63" s="4" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="O63" s="6"/>
       <c r="P63" s="6"/>
@@ -51660,7 +51683,7 @@
         <v>359</v>
       </c>
       <c r="W63" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X63" s="13"/>
       <c r="Y63" s="13"/>
@@ -51672,14 +51695,14 @@
       </c>
       <c r="AD63" s="13"/>
       <c r="AE63" s="1" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="AF63" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG63" s="13"/>
       <c r="AH63" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI63" s="13"/>
       <c r="AJ63" s="13"/>
@@ -51729,7 +51752,7 @@
         <v>359</v>
       </c>
       <c r="W64" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X64" s="13"/>
       <c r="Y64" s="13"/>
@@ -51739,14 +51762,14 @@
       <c r="AC64" s="13"/>
       <c r="AD64" s="13"/>
       <c r="AE64" s="1" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="AF64" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG64" s="13"/>
       <c r="AH64" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI64" s="13"/>
       <c r="AJ64" s="13"/>
@@ -51796,7 +51819,7 @@
         <v>359</v>
       </c>
       <c r="W65" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X65" s="13"/>
       <c r="Y65" s="13"/>
@@ -51805,17 +51828,17 @@
       <c r="AB65" s="13"/>
       <c r="AC65" s="13"/>
       <c r="AD65" s="1" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="AE65" s="1" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="AF65" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG65" s="13"/>
       <c r="AH65" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI65" s="13"/>
       <c r="AJ65" s="13"/>
@@ -51865,7 +51888,7 @@
         <v>359</v>
       </c>
       <c r="W66" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X66" s="13"/>
       <c r="Y66" s="13"/>
@@ -51875,14 +51898,14 @@
       <c r="AC66" s="13"/>
       <c r="AD66" s="13"/>
       <c r="AE66" s="1" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="AF66" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG66" s="13"/>
       <c r="AH66" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI66" s="13"/>
       <c r="AJ66" s="13"/>
@@ -51956,7 +51979,7 @@
         <v>359</v>
       </c>
       <c r="W68" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X68" s="13"/>
       <c r="Y68" s="13"/>
@@ -51973,7 +51996,7 @@
       </c>
       <c r="AG68" s="13"/>
       <c r="AH68" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI68" s="13"/>
       <c r="AJ68" s="13"/>
@@ -52000,7 +52023,7 @@
       <c r="L69" s="4"/>
       <c r="M69" s="4"/>
       <c r="N69" s="4" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="O69" s="6"/>
       <c r="P69" s="6"/>
@@ -52025,7 +52048,7 @@
         <v>359</v>
       </c>
       <c r="W69" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X69" s="13"/>
       <c r="Y69" s="13"/>
@@ -52037,14 +52060,14 @@
       </c>
       <c r="AD69" s="13"/>
       <c r="AE69" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="AF69" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG69" s="13"/>
       <c r="AH69" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI69" s="13"/>
       <c r="AJ69" s="13"/>
@@ -52071,7 +52094,7 @@
       <c r="L70" s="4"/>
       <c r="M70" s="4"/>
       <c r="N70" s="4" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="O70" s="6"/>
       <c r="P70" s="6"/>
@@ -52096,7 +52119,7 @@
         <v>359</v>
       </c>
       <c r="W70" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X70" s="13"/>
       <c r="Y70" s="13"/>
@@ -52110,14 +52133,14 @@
         <v>127</v>
       </c>
       <c r="AE70" s="1" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="AF70" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG70" s="13"/>
       <c r="AH70" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI70" s="13"/>
       <c r="AJ70" s="13"/>
@@ -52144,7 +52167,7 @@
       <c r="L71" s="4"/>
       <c r="M71" s="4"/>
       <c r="N71" s="4" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="O71" s="6"/>
       <c r="P71" s="6"/>
@@ -52169,7 +52192,7 @@
         <v>359</v>
       </c>
       <c r="W71" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X71" s="13"/>
       <c r="Y71" s="13"/>
@@ -52181,14 +52204,14 @@
       </c>
       <c r="AD71" s="13"/>
       <c r="AE71" s="1" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="AF71" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG71" s="13"/>
       <c r="AH71" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI71" s="13"/>
       <c r="AJ71" s="13"/>
@@ -52215,7 +52238,7 @@
       <c r="L72" s="4"/>
       <c r="M72" s="4"/>
       <c r="N72" s="4" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="O72" s="6"/>
       <c r="P72" s="6"/>
@@ -52240,7 +52263,7 @@
         <v>359</v>
       </c>
       <c r="W72" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X72" s="13"/>
       <c r="Y72" s="13"/>
@@ -52252,14 +52275,14 @@
       </c>
       <c r="AD72" s="13"/>
       <c r="AE72" s="1" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="AF72" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG72" s="13"/>
       <c r="AH72" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI72" s="13"/>
       <c r="AJ72" s="13"/>
@@ -52309,7 +52332,7 @@
         <v>359</v>
       </c>
       <c r="W73" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X73" s="13"/>
       <c r="Y73" s="13"/>
@@ -52318,17 +52341,17 @@
       <c r="AB73" s="13"/>
       <c r="AC73" s="13"/>
       <c r="AD73" s="1" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="AE73" s="1" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="AF73" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG73" s="13"/>
       <c r="AH73" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI73" s="13"/>
       <c r="AJ73" s="13"/>
@@ -52355,7 +52378,7 @@
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
       <c r="N74" s="4" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="O74" s="6"/>
       <c r="P74" s="6"/>
@@ -52380,7 +52403,7 @@
         <v>359</v>
       </c>
       <c r="W74" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X74" s="13"/>
       <c r="Y74" s="13"/>
@@ -52391,17 +52414,17 @@
         <v>712</v>
       </c>
       <c r="AD74" s="1" t="s">
+        <v>1716</v>
+      </c>
+      <c r="AE74" s="1" t="s">
         <v>1717</v>
-      </c>
-      <c r="AE74" s="1" t="s">
-        <v>1718</v>
       </c>
       <c r="AF74" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG74" s="13"/>
       <c r="AH74" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI74" s="13"/>
       <c r="AJ74" s="13"/>
@@ -52451,7 +52474,7 @@
         <v>359</v>
       </c>
       <c r="W75" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X75" s="13"/>
       <c r="Y75" s="13"/>
@@ -52461,14 +52484,14 @@
       <c r="AC75" s="13"/>
       <c r="AD75" s="13"/>
       <c r="AE75" s="1" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="AF75" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG75" s="13"/>
       <c r="AH75" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI75" s="13"/>
       <c r="AJ75" s="13"/>
@@ -52518,7 +52541,7 @@
         <v>359</v>
       </c>
       <c r="W76" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X76" s="13"/>
       <c r="Y76" s="13"/>
@@ -52528,14 +52551,14 @@
       <c r="AC76" s="13"/>
       <c r="AD76" s="13"/>
       <c r="AE76" s="1" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="AF76" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG76" s="13"/>
       <c r="AH76" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI76" s="13"/>
       <c r="AJ76" s="13"/>
@@ -52585,7 +52608,7 @@
         <v>359</v>
       </c>
       <c r="W77" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X77" s="13"/>
       <c r="Y77" s="13"/>
@@ -52594,17 +52617,17 @@
       <c r="AB77" s="13"/>
       <c r="AC77" s="13"/>
       <c r="AD77" s="1" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="AE77" s="1" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="AF77" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG77" s="13"/>
       <c r="AH77" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI77" s="13"/>
       <c r="AJ77" s="13"/>
@@ -52654,7 +52677,7 @@
         <v>359</v>
       </c>
       <c r="W78" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X78" s="13"/>
       <c r="Y78" s="13"/>
@@ -52663,17 +52686,17 @@
       <c r="AB78" s="13"/>
       <c r="AC78" s="13"/>
       <c r="AD78" s="1" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="AE78" s="1" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="AF78" s="1" t="s">
         <v>254</v>
       </c>
       <c r="AG78" s="13"/>
       <c r="AH78" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI78" s="13"/>
       <c r="AJ78" s="13"/>
@@ -52700,7 +52723,7 @@
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
       <c r="N79" s="4" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="O79" s="6"/>
       <c r="P79" s="6"/>
@@ -52725,7 +52748,7 @@
         <v>359</v>
       </c>
       <c r="W79" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X79" s="13"/>
       <c r="Y79" s="13"/>
@@ -52737,14 +52760,14 @@
       </c>
       <c r="AD79" s="13"/>
       <c r="AE79" s="1" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="AF79" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG79" s="13"/>
       <c r="AH79" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI79" s="13"/>
       <c r="AJ79" s="13"/>
@@ -52771,7 +52794,7 @@
       <c r="L80" s="4"/>
       <c r="M80" s="4"/>
       <c r="N80" s="4" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="O80" s="6"/>
       <c r="P80" s="6"/>
@@ -52796,7 +52819,7 @@
         <v>359</v>
       </c>
       <c r="W80" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X80" s="13"/>
       <c r="Y80" s="13"/>
@@ -52808,14 +52831,14 @@
       </c>
       <c r="AD80" s="13"/>
       <c r="AE80" s="1" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="AF80" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG80" s="13"/>
       <c r="AH80" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI80" s="13"/>
       <c r="AJ80" s="13"/>
@@ -52865,7 +52888,7 @@
         <v>359</v>
       </c>
       <c r="W81" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X81" s="13"/>
       <c r="Y81" s="13"/>
@@ -52874,17 +52897,17 @@
       <c r="AB81" s="13"/>
       <c r="AC81" s="13"/>
       <c r="AD81" s="1" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="AE81" s="1" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="AF81" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG81" s="13"/>
       <c r="AH81" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI81" s="13"/>
       <c r="AJ81" s="13"/>
@@ -52911,7 +52934,7 @@
       <c r="L82" s="4"/>
       <c r="M82" s="4"/>
       <c r="N82" s="4" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="O82" s="6"/>
       <c r="P82" s="6"/>
@@ -52936,7 +52959,7 @@
         <v>359</v>
       </c>
       <c r="W82" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X82" s="13"/>
       <c r="Y82" s="13"/>
@@ -52948,14 +52971,14 @@
       </c>
       <c r="AD82" s="13"/>
       <c r="AE82" s="1" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="AF82" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG82" s="13"/>
       <c r="AH82" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI82" s="13"/>
       <c r="AJ82" s="13"/>
@@ -53005,7 +53028,7 @@
         <v>359</v>
       </c>
       <c r="W83" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X83" s="13"/>
       <c r="Y83" s="13"/>
@@ -53015,14 +53038,14 @@
       <c r="AC83" s="13"/>
       <c r="AD83" s="13"/>
       <c r="AE83" s="1" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="AF83" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG83" s="13"/>
       <c r="AH83" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI83" s="13"/>
       <c r="AJ83" s="13"/>
@@ -53094,7 +53117,7 @@
       <c r="L85" s="4"/>
       <c r="M85" s="4"/>
       <c r="N85" s="4" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="O85" s="6"/>
       <c r="P85" s="6"/>
@@ -53119,7 +53142,7 @@
         <v>359</v>
       </c>
       <c r="W85" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X85" s="13"/>
       <c r="Y85" s="13"/>
@@ -53133,14 +53156,14 @@
         <v>222</v>
       </c>
       <c r="AE85" s="1" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="AF85" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG85" s="13"/>
       <c r="AH85" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI85" s="13"/>
       <c r="AJ85" s="13"/>
@@ -53190,7 +53213,7 @@
         <v>359</v>
       </c>
       <c r="W86" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X86" s="13"/>
       <c r="Y86" s="13"/>
@@ -53199,17 +53222,17 @@
       <c r="AB86" s="13"/>
       <c r="AC86" s="13"/>
       <c r="AD86" s="1" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="AE86" s="1" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="AF86" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG86" s="13"/>
       <c r="AH86" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI86" s="13"/>
       <c r="AJ86" s="13"/>
@@ -53259,7 +53282,7 @@
         <v>359</v>
       </c>
       <c r="W87" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X87" s="13"/>
       <c r="Y87" s="13"/>
@@ -53268,17 +53291,17 @@
       <c r="AB87" s="13"/>
       <c r="AC87" s="13"/>
       <c r="AD87" s="1" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="AE87" s="1" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="AF87" s="1" t="s">
         <v>254</v>
       </c>
       <c r="AG87" s="13"/>
       <c r="AH87" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI87" s="13"/>
       <c r="AJ87" s="13"/>
@@ -53305,7 +53328,7 @@
       <c r="L88" s="4"/>
       <c r="M88" s="4"/>
       <c r="N88" s="4" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="O88" s="6"/>
       <c r="P88" s="6"/>
@@ -53330,7 +53353,7 @@
         <v>359</v>
       </c>
       <c r="W88" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X88" s="13"/>
       <c r="Y88" s="13"/>
@@ -53341,7 +53364,7 @@
         <v>712</v>
       </c>
       <c r="AD88" s="1" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="AE88" s="1" t="s">
         <v>64</v>
@@ -53351,7 +53374,7 @@
       </c>
       <c r="AG88" s="13"/>
       <c r="AH88" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI88" s="13"/>
       <c r="AJ88" s="13"/>
@@ -53401,7 +53424,7 @@
         <v>359</v>
       </c>
       <c r="W89" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X89" s="13"/>
       <c r="Y89" s="13"/>
@@ -53418,7 +53441,7 @@
       </c>
       <c r="AG89" s="13"/>
       <c r="AH89" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI89" s="13"/>
       <c r="AJ89" s="13"/>
@@ -53468,7 +53491,7 @@
         <v>359</v>
       </c>
       <c r="W90" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X90" s="13"/>
       <c r="Y90" s="13"/>
@@ -53478,14 +53501,14 @@
       <c r="AC90" s="13"/>
       <c r="AD90" s="13"/>
       <c r="AE90" s="1" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="AF90" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG90" s="13"/>
       <c r="AH90" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI90" s="13"/>
       <c r="AJ90" s="13"/>
@@ -53535,7 +53558,7 @@
         <v>359</v>
       </c>
       <c r="W91" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X91" s="13"/>
       <c r="Y91" s="13"/>
@@ -53544,17 +53567,17 @@
       <c r="AB91" s="13"/>
       <c r="AC91" s="13"/>
       <c r="AD91" s="1" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="AE91" s="1" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="AF91" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG91" s="13"/>
       <c r="AH91" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI91" s="13"/>
       <c r="AJ91" s="13"/>
@@ -53604,7 +53627,7 @@
         <v>359</v>
       </c>
       <c r="W92" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X92" s="13"/>
       <c r="Y92" s="13"/>
@@ -53614,14 +53637,14 @@
       <c r="AC92" s="13"/>
       <c r="AD92" s="13"/>
       <c r="AE92" s="1" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="AF92" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG92" s="13"/>
       <c r="AH92" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI92" s="13"/>
       <c r="AJ92" s="13"/>
@@ -53648,7 +53671,7 @@
       <c r="L93" s="4"/>
       <c r="M93" s="4"/>
       <c r="N93" s="4" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="O93" s="6"/>
       <c r="P93" s="6"/>
@@ -53673,7 +53696,7 @@
         <v>359</v>
       </c>
       <c r="W93" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X93" s="13"/>
       <c r="Y93" s="13"/>
@@ -53681,20 +53704,20 @@
       <c r="AA93" s="13"/>
       <c r="AB93" s="13"/>
       <c r="AC93" s="1" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="AD93" s="1" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="AE93" s="1" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="AF93" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG93" s="13"/>
       <c r="AH93" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI93" s="13"/>
       <c r="AJ93" s="13"/>
@@ -53744,7 +53767,7 @@
         <v>359</v>
       </c>
       <c r="W94" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X94" s="13"/>
       <c r="Y94" s="13"/>
@@ -53754,14 +53777,14 @@
       <c r="AC94" s="13"/>
       <c r="AD94" s="13"/>
       <c r="AE94" s="1" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="AF94" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG94" s="13"/>
       <c r="AH94" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI94" s="13"/>
       <c r="AJ94" s="13"/>
@@ -53788,7 +53811,7 @@
       <c r="L95" s="4"/>
       <c r="M95" s="4"/>
       <c r="N95" s="4" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="O95" s="6"/>
       <c r="P95" s="6"/>
@@ -53813,7 +53836,7 @@
         <v>359</v>
       </c>
       <c r="W95" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X95" s="13"/>
       <c r="Y95" s="13"/>
@@ -53827,14 +53850,14 @@
         <v>127</v>
       </c>
       <c r="AE95" s="1" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="AF95" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG95" s="13"/>
       <c r="AH95" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI95" s="13"/>
       <c r="AJ95" s="13"/>
@@ -53886,7 +53909,7 @@
         <v>359</v>
       </c>
       <c r="W96" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X96" s="13"/>
       <c r="Y96" s="13"/>
@@ -53898,14 +53921,14 @@
       </c>
       <c r="AD96" s="13"/>
       <c r="AE96" s="1" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="AF96" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG96" s="13"/>
       <c r="AH96" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI96" s="13"/>
       <c r="AJ96" s="13"/>
@@ -53955,7 +53978,7 @@
         <v>359</v>
       </c>
       <c r="W97" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X97" s="13"/>
       <c r="Y97" s="13"/>
@@ -53967,14 +53990,14 @@
         <v>222</v>
       </c>
       <c r="AE97" s="1" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="AF97" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG97" s="13"/>
       <c r="AH97" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI97" s="13"/>
       <c r="AJ97" s="13"/>
@@ -54001,7 +54024,7 @@
       <c r="L98" s="4"/>
       <c r="M98" s="4"/>
       <c r="N98" s="4" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="O98" s="6"/>
       <c r="P98" s="6"/>
@@ -54026,7 +54049,7 @@
         <v>359</v>
       </c>
       <c r="W98" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X98" s="13"/>
       <c r="Y98" s="13"/>
@@ -54038,14 +54061,14 @@
       </c>
       <c r="AD98" s="13"/>
       <c r="AE98" s="1" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="AF98" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG98" s="13"/>
       <c r="AH98" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI98" s="13"/>
       <c r="AJ98" s="13"/>
@@ -54072,7 +54095,7 @@
       <c r="L99" s="4"/>
       <c r="M99" s="4"/>
       <c r="N99" s="4" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="O99" s="6"/>
       <c r="P99" s="6"/>
@@ -54097,7 +54120,7 @@
         <v>359</v>
       </c>
       <c r="W99" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X99" s="13"/>
       <c r="Y99" s="13"/>
@@ -54109,14 +54132,14 @@
       </c>
       <c r="AD99" s="13"/>
       <c r="AE99" s="1" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="AF99" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG99" s="13"/>
       <c r="AH99" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI99" s="13"/>
       <c r="AJ99" s="13"/>
@@ -54166,7 +54189,7 @@
         <v>359</v>
       </c>
       <c r="W100" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X100" s="13"/>
       <c r="Y100" s="13"/>
@@ -54176,14 +54199,14 @@
       <c r="AC100" s="13"/>
       <c r="AD100" s="13"/>
       <c r="AE100" s="1" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="AF100" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG100" s="13"/>
       <c r="AH100" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI100" s="13"/>
       <c r="AJ100" s="13"/>
@@ -54210,7 +54233,7 @@
       <c r="L101" s="4"/>
       <c r="M101" s="4"/>
       <c r="N101" s="4" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="O101" s="6"/>
       <c r="P101" s="6"/>
@@ -54235,7 +54258,7 @@
         <v>359</v>
       </c>
       <c r="W101" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X101" s="13"/>
       <c r="Y101" s="13"/>
@@ -54249,14 +54272,14 @@
         <v>127</v>
       </c>
       <c r="AE101" s="1" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="AF101" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG101" s="13"/>
       <c r="AH101" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI101" s="13"/>
       <c r="AJ101" s="13"/>
@@ -54308,7 +54331,7 @@
         <v>359</v>
       </c>
       <c r="W102" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X102" s="13"/>
       <c r="Y102" s="13"/>
@@ -54327,7 +54350,7 @@
       </c>
       <c r="AG102" s="13"/>
       <c r="AH102" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI102" s="13"/>
       <c r="AJ102" s="13"/>
@@ -54354,7 +54377,7 @@
       <c r="L103" s="4"/>
       <c r="M103" s="4"/>
       <c r="N103" s="4" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="O103" s="6"/>
       <c r="P103" s="6"/>
@@ -54379,7 +54402,7 @@
         <v>359</v>
       </c>
       <c r="W103" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X103" s="13"/>
       <c r="Y103" s="13"/>
@@ -54391,14 +54414,14 @@
       </c>
       <c r="AD103" s="13"/>
       <c r="AE103" s="1" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="AF103" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG103" s="13"/>
       <c r="AH103" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI103" s="13"/>
       <c r="AJ103" s="13"/>
@@ -54425,7 +54448,7 @@
       <c r="L104" s="4"/>
       <c r="M104" s="4"/>
       <c r="N104" s="4" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="O104" s="6"/>
       <c r="P104" s="6"/>
@@ -54450,7 +54473,7 @@
         <v>359</v>
       </c>
       <c r="W104" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X104" s="13"/>
       <c r="Y104" s="13"/>
@@ -54462,14 +54485,14 @@
       </c>
       <c r="AD104" s="13"/>
       <c r="AE104" s="1" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="AF104" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG104" s="13"/>
       <c r="AH104" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI104" s="13"/>
       <c r="AJ104" s="13"/>
@@ -54496,7 +54519,7 @@
       <c r="L105" s="4"/>
       <c r="M105" s="4"/>
       <c r="N105" s="4" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="O105" s="6"/>
       <c r="P105" s="6"/>
@@ -54521,7 +54544,7 @@
         <v>359</v>
       </c>
       <c r="W105" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X105" s="13"/>
       <c r="Y105" s="13"/>
@@ -54535,14 +54558,14 @@
         <v>621</v>
       </c>
       <c r="AE105" s="1" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="AF105" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG105" s="13"/>
       <c r="AH105" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI105" s="13"/>
       <c r="AJ105" s="13"/>
@@ -54570,7 +54593,7 @@
       <c r="M106" s="4"/>
       <c r="AG106" s="13"/>
       <c r="AH106" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI106" s="13"/>
       <c r="AJ106" s="13"/>
@@ -54620,7 +54643,7 @@
         <v>359</v>
       </c>
       <c r="W107" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X107" s="13"/>
       <c r="Y107" s="13"/>
@@ -54630,14 +54653,14 @@
       <c r="AC107" s="13"/>
       <c r="AD107" s="13"/>
       <c r="AE107" s="1" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="AF107" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG107" s="13"/>
       <c r="AH107" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI107" s="13"/>
       <c r="AJ107" s="13"/>
@@ -54687,7 +54710,7 @@
         <v>359</v>
       </c>
       <c r="W108" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X108" s="13"/>
       <c r="Y108" s="13"/>
@@ -54700,11 +54723,11 @@
         <v>76</v>
       </c>
       <c r="AF108" s="1" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="AG108" s="13"/>
       <c r="AH108" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI108" s="13"/>
       <c r="AJ108" s="13"/>
@@ -54731,7 +54754,7 @@
       <c r="L109" s="4"/>
       <c r="M109" s="4"/>
       <c r="N109" s="4" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="O109" s="6"/>
       <c r="P109" s="6"/>
@@ -54756,7 +54779,7 @@
         <v>359</v>
       </c>
       <c r="W109" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X109" s="13"/>
       <c r="Y109" s="13"/>
@@ -54764,20 +54787,20 @@
       <c r="AA109" s="13"/>
       <c r="AB109" s="13"/>
       <c r="AC109" s="1" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="AD109" s="1" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="AE109" s="1" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="AF109" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG109" s="13"/>
       <c r="AH109" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI109" s="13"/>
       <c r="AJ109" s="13"/>
@@ -54804,7 +54827,7 @@
       <c r="L110" s="4"/>
       <c r="M110" s="4"/>
       <c r="N110" s="4" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="O110" s="6"/>
       <c r="P110" s="6"/>
@@ -54829,7 +54852,7 @@
         <v>359</v>
       </c>
       <c r="W110" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X110" s="13"/>
       <c r="Y110" s="13"/>
@@ -54841,14 +54864,14 @@
       </c>
       <c r="AD110" s="13"/>
       <c r="AE110" s="1" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="AF110" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG110" s="13"/>
       <c r="AH110" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI110" s="13"/>
       <c r="AJ110" s="13"/>
@@ -54898,7 +54921,7 @@
         <v>359</v>
       </c>
       <c r="W111" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X111" s="13"/>
       <c r="Y111" s="13"/>
@@ -54908,14 +54931,14 @@
       <c r="AC111" s="13"/>
       <c r="AD111" s="13"/>
       <c r="AE111" s="1" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="AF111" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG111" s="13"/>
       <c r="AH111" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI111" s="13"/>
       <c r="AJ111" s="13"/>
@@ -54965,7 +54988,7 @@
         <v>359</v>
       </c>
       <c r="W112" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X112" s="13"/>
       <c r="Y112" s="13"/>
@@ -54974,17 +54997,17 @@
       <c r="AB112" s="13"/>
       <c r="AC112" s="13"/>
       <c r="AD112" s="1" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="AE112" s="1" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="AF112" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG112" s="13"/>
       <c r="AH112" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI112" s="13"/>
       <c r="AJ112" s="13"/>
@@ -55034,7 +55057,7 @@
         <v>359</v>
       </c>
       <c r="W113" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X113" s="13"/>
       <c r="Y113" s="13"/>
@@ -55043,17 +55066,17 @@
       <c r="AB113" s="13"/>
       <c r="AC113" s="13"/>
       <c r="AD113" s="1" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="AE113" s="1" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="AF113" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG113" s="13"/>
       <c r="AH113" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI113" s="13"/>
       <c r="AJ113" s="13"/>
@@ -55080,7 +55103,7 @@
       <c r="L114" s="4"/>
       <c r="M114" s="4"/>
       <c r="N114" s="4" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="O114" s="6"/>
       <c r="P114" s="6"/>
@@ -55105,7 +55128,7 @@
         <v>359</v>
       </c>
       <c r="W114" s="1" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="X114" s="13"/>
       <c r="Y114" s="13"/>
@@ -55120,7 +55143,7 @@
       <c r="AF114" s="13"/>
       <c r="AG114" s="13"/>
       <c r="AH114" s="14" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI114" s="13"/>
       <c r="AJ114" s="13"/>
@@ -55173,14 +55196,14 @@
       <c r="X115" s="34"/>
       <c r="Y115" s="34"/>
       <c r="Z115" s="36" t="s">
+        <v>1767</v>
+      </c>
+      <c r="AA115" s="36" t="s">
         <v>1768</v>
-      </c>
-      <c r="AA115" s="36" t="s">
-        <v>1769</v>
       </c>
       <c r="AB115" s="34"/>
       <c r="AC115" s="34" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AD115" s="34"/>
       <c r="AE115" s="34"/>
@@ -55343,7 +55366,7 @@
       <c r="K116" s="34"/>
       <c r="L116" s="34"/>
       <c r="M116" s="36" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="N116" s="34"/>
       <c r="O116" s="34"/>
@@ -55374,14 +55397,14 @@
       <c r="X116" s="34"/>
       <c r="Y116" s="34"/>
       <c r="Z116" s="36" t="s">
+        <v>1769</v>
+      </c>
+      <c r="AA116" s="36" t="s">
         <v>1770</v>
-      </c>
-      <c r="AA116" s="36" t="s">
-        <v>1771</v>
       </c>
       <c r="AB116" s="34"/>
       <c r="AC116" s="34" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="AD116" s="34"/>
       <c r="AE116" s="34"/>
@@ -55403,7 +55426,7 @@
       <c r="AU116" s="34"/>
       <c r="AV116" s="37"/>
       <c r="AW116" s="37" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="AX116" s="37"/>
       <c r="AY116" s="37"/>
@@ -55575,14 +55598,14 @@
       <c r="X117" s="34"/>
       <c r="Y117" s="34"/>
       <c r="Z117" s="36" t="s">
+        <v>1773</v>
+      </c>
+      <c r="AA117" s="36" t="s">
         <v>1774</v>
-      </c>
-      <c r="AA117" s="36" t="s">
-        <v>1775</v>
       </c>
       <c r="AB117" s="34"/>
       <c r="AC117" s="34" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AD117" s="34"/>
       <c r="AE117" s="34"/>
@@ -55604,7 +55627,7 @@
       <c r="AU117" s="34"/>
       <c r="AV117" s="37"/>
       <c r="AW117" s="37" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="AX117" s="37"/>
       <c r="AY117" s="37"/>
@@ -55733,13 +55756,13 @@
     </row>
     <row r="118" spans="1:173" s="10" customFormat="1" ht="23.25" customHeight="1">
       <c r="A118" s="38" t="s">
+        <v>1775</v>
+      </c>
+      <c r="B118" s="39" t="s">
         <v>1776</v>
       </c>
-      <c r="B118" s="39" t="s">
+      <c r="C118" s="38" t="s">
         <v>1777</v>
-      </c>
-      <c r="C118" s="38" t="s">
-        <v>1778</v>
       </c>
       <c r="D118" s="38"/>
       <c r="E118" s="38" t="s">
@@ -55755,10 +55778,10 @@
       <c r="M118" s="39"/>
       <c r="N118" s="39"/>
       <c r="O118" s="38" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="P118" s="38" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="Q118" s="40" t="s">
         <v>99</v>
@@ -55796,12 +55819,12 @@
       <c r="AH118" s="39"/>
       <c r="AI118" s="39"/>
       <c r="AJ118" s="38" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="AK118" s="38"/>
       <c r="AL118" s="38"/>
       <c r="AM118" s="38" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="AN118" s="38"/>
       <c r="AO118" s="38" t="s">
@@ -55820,14 +55843,14 @@
         <v>132</v>
       </c>
       <c r="AT118" s="38" t="s">
+        <v>1775</v>
+      </c>
+      <c r="AU118" s="39" t="s">
         <v>1776</v>
-      </c>
-      <c r="AU118" s="39" t="s">
-        <v>1777</v>
       </c>
       <c r="AV118" s="39"/>
       <c r="AW118" s="39" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="AX118" s="39"/>
       <c r="AY118" s="39"/>
@@ -55956,13 +55979,13 @@
     </row>
     <row r="119" spans="1:173" s="10" customFormat="1" ht="23.25" customHeight="1">
       <c r="A119" s="38" t="s">
+        <v>1781</v>
+      </c>
+      <c r="B119" s="39" t="s">
         <v>1782</v>
       </c>
-      <c r="B119" s="39" t="s">
+      <c r="C119" s="38" t="s">
         <v>1783</v>
-      </c>
-      <c r="C119" s="38" t="s">
-        <v>1784</v>
       </c>
       <c r="D119" s="38"/>
       <c r="E119" s="38" t="s">
@@ -55978,10 +56001,10 @@
       <c r="M119" s="39"/>
       <c r="N119" s="39"/>
       <c r="O119" s="38" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="P119" s="38" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="Q119" s="40" t="s">
         <v>731</v>
@@ -56019,12 +56042,12 @@
       <c r="AH119" s="39"/>
       <c r="AI119" s="39"/>
       <c r="AJ119" s="38" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="AK119" s="38"/>
       <c r="AL119" s="38"/>
       <c r="AM119" s="38" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="AN119" s="38"/>
       <c r="AO119" s="38" t="s">
@@ -56043,14 +56066,14 @@
         <v>132</v>
       </c>
       <c r="AT119" s="38" t="s">
+        <v>1781</v>
+      </c>
+      <c r="AU119" s="39" t="s">
         <v>1782</v>
-      </c>
-      <c r="AU119" s="39" t="s">
-        <v>1783</v>
       </c>
       <c r="AV119" s="39"/>
       <c r="AW119" s="39" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="AX119" s="39"/>
       <c r="AY119" s="39"/>
@@ -56179,13 +56202,13 @@
     </row>
     <row r="120" spans="1:173" s="10" customFormat="1" ht="23.25" customHeight="1">
       <c r="A120" s="38" t="s">
+        <v>1785</v>
+      </c>
+      <c r="B120" s="39" t="s">
         <v>1786</v>
       </c>
-      <c r="B120" s="39" t="s">
+      <c r="C120" s="38" t="s">
         <v>1787</v>
-      </c>
-      <c r="C120" s="38" t="s">
-        <v>1788</v>
       </c>
       <c r="D120" s="38"/>
       <c r="E120" s="38" t="s">
@@ -56201,10 +56224,10 @@
       <c r="M120" s="39"/>
       <c r="N120" s="39"/>
       <c r="O120" s="38" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="P120" s="38" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="Q120" s="40" t="s">
         <v>873</v>
@@ -56242,12 +56265,12 @@
       <c r="AH120" s="39"/>
       <c r="AI120" s="39"/>
       <c r="AJ120" s="38" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="AK120" s="38"/>
       <c r="AL120" s="38"/>
       <c r="AM120" s="38" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="AN120" s="38"/>
       <c r="AO120" s="38" t="s">
@@ -56266,14 +56289,14 @@
         <v>132</v>
       </c>
       <c r="AT120" s="38" t="s">
+        <v>1785</v>
+      </c>
+      <c r="AU120" s="39" t="s">
         <v>1786</v>
-      </c>
-      <c r="AU120" s="39" t="s">
-        <v>1787</v>
       </c>
       <c r="AV120" s="39"/>
       <c r="AW120" s="39" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="AX120" s="39"/>
       <c r="AY120" s="39"/>
@@ -56402,13 +56425,13 @@
     </row>
     <row r="121" spans="1:173" s="10" customFormat="1" ht="23.25" customHeight="1">
       <c r="A121" s="38" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B121" s="39" t="s">
         <v>1791</v>
       </c>
-      <c r="B121" s="39" t="s">
+      <c r="C121" s="38" t="s">
         <v>1792</v>
-      </c>
-      <c r="C121" s="38" t="s">
-        <v>1793</v>
       </c>
       <c r="D121" s="38"/>
       <c r="E121" s="38" t="s">
@@ -56424,10 +56447,10 @@
       <c r="M121" s="39"/>
       <c r="N121" s="39"/>
       <c r="O121" s="38" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="P121" s="38" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="Q121" s="40" t="s">
         <v>110</v>
@@ -56465,12 +56488,12 @@
       <c r="AH121" s="39"/>
       <c r="AI121" s="39"/>
       <c r="AJ121" s="38" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="AK121" s="38"/>
       <c r="AL121" s="38"/>
       <c r="AM121" s="38" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="AN121" s="38"/>
       <c r="AO121" s="38" t="s">
@@ -56489,14 +56512,14 @@
         <v>132</v>
       </c>
       <c r="AT121" s="38" t="s">
+        <v>1790</v>
+      </c>
+      <c r="AU121" s="39" t="s">
         <v>1791</v>
-      </c>
-      <c r="AU121" s="39" t="s">
-        <v>1792</v>
       </c>
       <c r="AV121" s="39"/>
       <c r="AW121" s="39" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="AX121" s="39"/>
       <c r="AY121" s="39"/>
@@ -56625,13 +56648,13 @@
     </row>
     <row r="122" spans="1:173" s="10" customFormat="1" ht="23.25" customHeight="1">
       <c r="A122" s="38" t="s">
+        <v>1781</v>
+      </c>
+      <c r="B122" s="39" t="s">
         <v>1782</v>
       </c>
-      <c r="B122" s="39" t="s">
-        <v>1783</v>
-      </c>
       <c r="C122" s="38" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="D122" s="38"/>
       <c r="E122" s="38" t="s">
@@ -56647,10 +56670,10 @@
       <c r="M122" s="39"/>
       <c r="N122" s="39"/>
       <c r="O122" s="38" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="P122" s="38" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="Q122" s="40" t="s">
         <v>873</v>
@@ -56688,12 +56711,12 @@
       <c r="AH122" s="39"/>
       <c r="AI122" s="39"/>
       <c r="AJ122" s="38" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="AK122" s="38"/>
       <c r="AL122" s="38"/>
       <c r="AM122" s="38" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="AN122" s="38"/>
       <c r="AO122" s="38" t="s">
@@ -56712,14 +56735,14 @@
         <v>132</v>
       </c>
       <c r="AT122" s="38" t="s">
+        <v>1781</v>
+      </c>
+      <c r="AU122" s="39" t="s">
         <v>1782</v>
-      </c>
-      <c r="AU122" s="39" t="s">
-        <v>1783</v>
       </c>
       <c r="AV122" s="39"/>
       <c r="AW122" s="39" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="AX122" s="39"/>
       <c r="AY122" s="39"/>
@@ -56848,13 +56871,13 @@
     </row>
     <row r="123" spans="1:173" s="10" customFormat="1" ht="23.25" customHeight="1">
       <c r="A123" s="32" t="s">
+        <v>1795</v>
+      </c>
+      <c r="B123" s="42" t="s">
         <v>1796</v>
       </c>
-      <c r="B123" s="42" t="s">
+      <c r="C123" s="32" t="s">
         <v>1797</v>
-      </c>
-      <c r="C123" s="32" t="s">
-        <v>1798</v>
       </c>
       <c r="D123" s="32"/>
       <c r="E123" s="32" t="s">
@@ -56870,10 +56893,10 @@
       <c r="M123" s="42"/>
       <c r="N123" s="42"/>
       <c r="O123" s="32" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="P123" s="32" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="Q123" s="43" t="s">
         <v>99</v>
@@ -56911,12 +56934,12 @@
       <c r="AH123" s="42"/>
       <c r="AI123" s="42"/>
       <c r="AJ123" s="32" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="AK123" s="32"/>
       <c r="AL123" s="32"/>
       <c r="AM123" s="32" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="AN123" s="32"/>
       <c r="AO123" s="32" t="s">
@@ -56935,14 +56958,14 @@
         <v>132</v>
       </c>
       <c r="AT123" s="32" t="s">
+        <v>1795</v>
+      </c>
+      <c r="AU123" s="42" t="s">
         <v>1796</v>
-      </c>
-      <c r="AU123" s="42" t="s">
-        <v>1797</v>
       </c>
       <c r="AV123" s="42"/>
       <c r="AW123" s="42" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="AX123" s="42"/>
       <c r="AY123" s="42"/>
@@ -57071,13 +57094,13 @@
     </row>
     <row r="124" spans="1:173" s="10" customFormat="1" ht="23.25" customHeight="1">
       <c r="A124" s="32" t="s">
+        <v>1800</v>
+      </c>
+      <c r="B124" s="42" t="s">
         <v>1801</v>
       </c>
-      <c r="B124" s="42" t="s">
+      <c r="C124" s="32" t="s">
         <v>1802</v>
-      </c>
-      <c r="C124" s="32" t="s">
-        <v>1803</v>
       </c>
       <c r="D124" s="32"/>
       <c r="E124" s="32" t="s">
@@ -57093,10 +57116,10 @@
       <c r="M124" s="42"/>
       <c r="N124" s="42"/>
       <c r="O124" s="32" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="P124" s="32" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="Q124" s="43" t="s">
         <v>99</v>
@@ -57134,12 +57157,12 @@
       <c r="AH124" s="42"/>
       <c r="AI124" s="42"/>
       <c r="AJ124" s="32" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="AK124" s="32"/>
       <c r="AL124" s="32"/>
       <c r="AM124" s="32" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="AN124" s="32"/>
       <c r="AO124" s="32" t="s">
@@ -57158,14 +57181,14 @@
         <v>149</v>
       </c>
       <c r="AT124" s="32" t="s">
+        <v>1800</v>
+      </c>
+      <c r="AU124" s="42" t="s">
         <v>1801</v>
-      </c>
-      <c r="AU124" s="42" t="s">
-        <v>1802</v>
       </c>
       <c r="AV124" s="42"/>
       <c r="AW124" s="42" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="AX124" s="42"/>
       <c r="AY124" s="42"/>

--- a/metadata.xlsx
+++ b/metadata.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30219"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{99311BF2-83E0-4BF7-9952-B0DE8E57F3E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDEEB2B0-5037-4254-AE17-C53FFBB837D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4931,7 +4931,7 @@
     <t>contig_length_checkv</t>
   </si>
   <si>
-    <t xml:space="preserve"> Contig Length CheckV</t>
+    <t>Contig Length CheckV</t>
   </si>
   <si>
     <t>Length of the sequence as calculated by CheckV v1.1.1 against the default CheckV database v1.5. For more information about CheckV please see the tool page at: https://bitbucket.org/berkeleylab/checkv/src/master</t>
@@ -4943,7 +4943,7 @@
     <t>provirus_checkv</t>
   </si>
   <si>
-    <t xml:space="preserve"> Provirus CheckV</t>
+    <t>Provirus CheckV</t>
   </si>
   <si>
     <t>Prediction of whether the sequence is a provirus by CheckV v1.1.1 against the default CheckV database v1.5. [Yes/No] For more information about CheckV please see the tool page at: https://bitbucket.org/berkeleylab/checkv/src/master</t>
@@ -4955,7 +4955,7 @@
     <t>proviral_length_checkv</t>
   </si>
   <si>
-    <t xml:space="preserve"> Proviral Length CheckV</t>
+    <t>Proviral Length CheckV</t>
   </si>
   <si>
     <t>If the sequence is predicated as a provirus, the length ofthe provirus, calculated by CheckV v1.1.1 against the default CheckV database v1.5. For more information about CheckV please see the tool page at: https://bitbucket.org/berkeleylab/checkv/src/master</t>
@@ -4967,7 +4967,7 @@
     <t>gene_count_checkv</t>
   </si>
   <si>
-    <t xml:space="preserve"> Gene Count CheckV</t>
+    <t>Gene Count CheckV</t>
   </si>
   <si>
     <t>The number of genes in the virus sequence as calculated by CheckV v1.1.1 against the default CheckV database v1.5. For more information about CheckV please see the tool page at: https://bitbucket.org/berkeleylab/checkv/src/master</t>
@@ -4979,7 +4979,7 @@
     <t>viral_genes_checkv</t>
   </si>
   <si>
-    <t xml:space="preserve"> Viral Genes CheckV</t>
+    <t>Viral Genes CheckV</t>
   </si>
   <si>
     <t>The number of virus genes in the virus sequence as calculated by CheckV v1.1.1 against the default CheckV database v1.5. For more information about CheckV please see the tool page at: https://bitbucket.org/berkeleylab/checkv/src/master</t>
@@ -4991,7 +4991,7 @@
     <t>host_genes_checkv</t>
   </si>
   <si>
-    <t xml:space="preserve"> Host Genes CheckV</t>
+    <t>Host Genes CheckV</t>
   </si>
   <si>
     <t>The number of host genes as calculated by CheckV v1.1.1 against the default CheckV database v1.5. For more information about CheckV please see the tool page at: https://bitbucket.org/berkeleylab/checkv/src/master</t>
@@ -5003,7 +5003,7 @@
     <t>quality_checkv</t>
   </si>
   <si>
-    <t xml:space="preserve"> Quality CheckV</t>
+    <t>Quality CheckV</t>
   </si>
   <si>
     <t>Quality tier of the virus genome as noted by CheckV v1.1.1 against the default CheckV database v1.5. For more information about CheckV please see the tool page at: https://bitbucket.org/berkeleylab/checkv/src/master 
@@ -5021,7 +5021,7 @@
     <t>miuvig_quality_checkv</t>
   </si>
   <si>
-    <t xml:space="preserve"> MIUVIG Quality CheckV</t>
+    <t>MIUVIG Quality CheckV</t>
   </si>
   <si>
     <t>MIUVIG quality as noted by CheckV v1.1.1 against the default CheckV database v1.5. For more information about CheckV please see the tool page at: https://bitbucket.org/berkeleylab/checkv/src/master</t>
@@ -5033,7 +5033,7 @@
     <t>completeness_checkv</t>
   </si>
   <si>
-    <t xml:space="preserve"> Completeness CheckV</t>
+    <t>Completeness CheckV</t>
   </si>
   <si>
     <t>Completeness of the virus genome sequenceas calculated by CheckV v1.1.1 against the default CheckV database v1.5. For more information about CheckV please see the tool page at: https://bitbucket.org/berkeleylab/checkv/src/master</t>
@@ -5045,7 +5045,7 @@
     <t>completeness_method_checkv</t>
   </si>
   <si>
-    <t xml:space="preserve"> Completeness Method CheckV</t>
+    <t>Completeness Method CheckV</t>
   </si>
   <si>
     <t>Method of determining the completeness of the virus genome sequence as calculated by CheckV v1.1.1 against the default CheckV database v1.5. For more information about CheckV please see the tool page at: https://bitbucket.org/berkeleylab/checkv/src/master</t>
@@ -5057,7 +5057,7 @@
     <t>contamination_checkv</t>
   </si>
   <si>
-    <t xml:space="preserve"> Contamination CheckV</t>
+    <t>Contamination CheckV</t>
   </si>
   <si>
     <t>Amount of virus genome sequence contamination as calculated by CheckV v1.1.1 against the default CheckV database v1.5. For more information about CheckV please see the tool page at: https://bitbucket.org/berkeleylab/checkv/src/master</t>
@@ -5069,7 +5069,7 @@
     <t>kmer_freq_checkv</t>
   </si>
   <si>
-    <t xml:space="preserve"> Kmer Freq CheckV</t>
+    <t>Kmer Freq CheckV</t>
   </si>
   <si>
     <t>Number of times the virus genome was found in the as calculated by CheckV v1.1.1 against the default CheckV database v1.5. For more information about CheckV please see the tool page at: https://bitbucket.org/berkeleylab/checkv/src/master</t>
@@ -5081,7 +5081,7 @@
     <t>warnings_checkv</t>
   </si>
   <si>
-    <t xml:space="preserve"> Warnings CheckV</t>
+    <t>Warnings CheckV</t>
   </si>
   <si>
     <t>Warnings generated by running CheckV v1.1.1 against the default CheckV database v1.5. For more information about CheckV please see the tool page at: https://bitbucket.org/berkeleylab/checkv/src/master</t>

--- a/metadata.xlsx
+++ b/metadata.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30219"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDEEB2B0-5037-4254-AE17-C53FFBB837D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE2FB830-7967-4A9E-934D-5F078ADA9EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1450,10 +1450,10 @@
     <t>0bh</t>
   </si>
   <si>
-    <t>collection_geolocation</t>
-  </si>
-  <si>
-    <t>Collection GeoLocation</t>
+    <t>collection_geopoint</t>
+  </si>
+  <si>
+    <t>Collection GeoPoint</t>
   </si>
   <si>
     <t>The geographic location by longitude, where the sample the sequence originates from was collected. (DD)</t>

--- a/metadata.xlsx
+++ b/metadata.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE2FB830-7967-4A9E-934D-5F078ADA9EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{95F02E05-0D41-47AE-8ED6-2948F96E31E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42223,7 +42223,7 @@
         <v>1419</v>
       </c>
       <c r="E194" s="54" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="F194" s="54" t="s">
         <v>154</v>

--- a/metadata.xlsx
+++ b/metadata.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{95F02E05-0D41-47AE-8ED6-2948F96E31E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{368FE683-6CCE-43A7-B1CE-A2D2BEFB873A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -237,7 +237,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5036" uniqueCount="1804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5037" uniqueCount="1804">
   <si>
     <t>VJDBv1.1</t>
   </si>
@@ -4843,26 +4843,27 @@
     <t>Coding Strand</t>
   </si>
   <si>
-    <t>True if the current virus sequence is a coding strand. Calculated by part of the ViralClust tool suite. Only intended for ssRNA viruses.</t>
+    <t>True if the current virus sequence is a coding strand. Calculated by part of the ViralClust tool suite. Only intended for ssRNA viruses."TRUE: is coding strand
+FALSE: is reverse complement"</t>
   </si>
   <si>
     <t>TRUE</t>
+  </si>
+  <si>
+    <t>0if</t>
+  </si>
+  <si>
+    <t>host_association_method</t>
+  </si>
+  <si>
+    <t>Host Association Method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Method by which the fields "Host Accession ID" from NCBI GenBank or "NCBI Taxonomy Lineage" was associated to the virus sequence. Currently (v1.1) either a host association from the data source or PhiSpy prophage prediction. Multiple host associations/predictions separated by semicolons. </t>
   </si>
   <si>
     <t>TRUE: is coding strand
 FALSE: is reverse complement</t>
-  </si>
-  <si>
-    <t>0if</t>
-  </si>
-  <si>
-    <t>host_association_method</t>
-  </si>
-  <si>
-    <t>Host Association Method</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Method by which the fields "Host Accession ID" from NCBI GenBank or "NCBI Taxonomy Lineage" was associated to the virus sequence. Currently (v1.1) either a host association from the data source or PhiSpy prophage prediction. Multiple host associations/predictions separated by semicolons. </t>
   </si>
   <si>
     <t>0ig</t>
@@ -6607,7 +6608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:FX237"/>
+  <dimension ref="A1:FX238"/>
   <sheetFormatPr defaultColWidth="23.5703125" defaultRowHeight="25.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="24.140625" style="67" bestFit="1" customWidth="1"/>
@@ -44477,7 +44478,7 @@
       <c r="C217" s="54" t="s">
         <v>1519</v>
       </c>
-      <c r="D217" s="75" t="s">
+      <c r="D217" s="71" t="s">
         <v>1520</v>
       </c>
       <c r="E217" s="54" t="s">
@@ -44560,7 +44561,7 @@
         <v>1521</v>
       </c>
       <c r="AV217" s="54" t="s">
-        <v>1522</v>
+        <v>169</v>
       </c>
       <c r="AW217" s="54"/>
       <c r="AX217" s="54"/>
@@ -44570,16 +44571,16 @@
     </row>
     <row r="218" spans="1:53" ht="25.5" customHeight="1">
       <c r="A218" s="64" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B218" s="64" t="s">
         <v>1523</v>
       </c>
-      <c r="B218" s="64" t="s">
+      <c r="C218" s="54" t="s">
         <v>1524</v>
       </c>
-      <c r="C218" s="54" t="s">
+      <c r="D218" s="71" t="s">
         <v>1525</v>
-      </c>
-      <c r="D218" s="71" t="s">
-        <v>1526</v>
       </c>
       <c r="E218" s="54" t="s">
         <v>76</v>
@@ -44660,7 +44661,9 @@
       <c r="AS218" s="54"/>
       <c r="AT218" s="54"/>
       <c r="AU218" s="55"/>
-      <c r="AV218" s="54"/>
+      <c r="AV218" s="54" t="s">
+        <v>1526</v>
+      </c>
       <c r="AW218" s="54"/>
       <c r="AX218" s="54"/>
       <c r="AY218" s="54"/>
@@ -45249,7 +45252,7 @@
       <c r="AZ224" s="54"/>
       <c r="BA224" s="54"/>
     </row>
-    <row r="225" spans="1:53" ht="25.5" customHeight="1">
+    <row r="225" spans="1:180" ht="25.5" customHeight="1">
       <c r="A225" s="64" t="s">
         <v>1551</v>
       </c>
@@ -45344,7 +45347,7 @@
       <c r="AZ225" s="54"/>
       <c r="BA225" s="54"/>
     </row>
-    <row r="226" spans="1:53" ht="25.5" customHeight="1">
+    <row r="226" spans="1:180" ht="25.5" customHeight="1">
       <c r="A226" s="64" t="s">
         <v>1555</v>
       </c>
@@ -45439,7 +45442,7 @@
       <c r="AZ226" s="54"/>
       <c r="BA226" s="54"/>
     </row>
-    <row r="227" spans="1:53" ht="25.5" customHeight="1">
+    <row r="227" spans="1:180" ht="25.5" customHeight="1">
       <c r="A227" s="64" t="s">
         <v>1559</v>
       </c>
@@ -45534,7 +45537,7 @@
       <c r="AZ227" s="54"/>
       <c r="BA227" s="54"/>
     </row>
-    <row r="228" spans="1:53" ht="25.5" customHeight="1">
+    <row r="228" spans="1:180" ht="25.5" customHeight="1">
       <c r="A228" s="64" t="s">
         <v>1563</v>
       </c>
@@ -45629,7 +45632,7 @@
       <c r="AZ228" s="54"/>
       <c r="BA228" s="54"/>
     </row>
-    <row r="229" spans="1:53" ht="25.5" customHeight="1">
+    <row r="229" spans="1:180" ht="25.5" customHeight="1">
       <c r="A229" s="64" t="s">
         <v>1567</v>
       </c>
@@ -45724,7 +45727,7 @@
       <c r="AZ229" s="54"/>
       <c r="BA229" s="54"/>
     </row>
-    <row r="230" spans="1:53" ht="25.5" customHeight="1">
+    <row r="230" spans="1:180" ht="25.5" customHeight="1">
       <c r="A230" s="64" t="s">
         <v>1571</v>
       </c>
@@ -45819,7 +45822,7 @@
       <c r="AZ230" s="54"/>
       <c r="BA230" s="54"/>
     </row>
-    <row r="231" spans="1:53" ht="25.5" customHeight="1">
+    <row r="231" spans="1:180" ht="25.5" customHeight="1">
       <c r="A231" s="64" t="s">
         <v>1575</v>
       </c>
@@ -45914,7 +45917,7 @@
       <c r="AZ231" s="54"/>
       <c r="BA231" s="54"/>
     </row>
-    <row r="232" spans="1:53" ht="25.5" customHeight="1">
+    <row r="232" spans="1:180" ht="25.5" customHeight="1">
       <c r="A232" s="64" t="s">
         <v>1579</v>
       </c>
@@ -46009,7 +46012,7 @@
       <c r="AZ232" s="54"/>
       <c r="BA232" s="54"/>
     </row>
-    <row r="233" spans="1:53" ht="25.5" customHeight="1">
+    <row r="233" spans="1:180" ht="25.5" customHeight="1">
       <c r="A233" s="64" t="s">
         <v>1583</v>
       </c>
@@ -46104,7 +46107,7 @@
       <c r="AZ233" s="54"/>
       <c r="BA233" s="54"/>
     </row>
-    <row r="234" spans="1:53" ht="25.5" customHeight="1">
+    <row r="234" spans="1:180" ht="25.5" customHeight="1">
       <c r="A234" s="64" t="s">
         <v>1587</v>
       </c>
@@ -46199,7 +46202,7 @@
       <c r="AZ234" s="54"/>
       <c r="BA234" s="54"/>
     </row>
-    <row r="235" spans="1:53" ht="25.5" customHeight="1">
+    <row r="235" spans="1:180" ht="25.5" customHeight="1">
       <c r="A235" s="64" t="s">
         <v>1591</v>
       </c>
@@ -46294,7 +46297,7 @@
       <c r="AZ235" s="54"/>
       <c r="BA235" s="54"/>
     </row>
-    <row r="236" spans="1:53" ht="25.5" customHeight="1">
+    <row r="236" spans="1:180" ht="25.5" customHeight="1">
       <c r="A236" s="64" t="s">
         <v>1595</v>
       </c>
@@ -46389,7 +46392,7 @@
       <c r="AZ236" s="54"/>
       <c r="BA236" s="54"/>
     </row>
-    <row r="237" spans="1:53" ht="25.5" customHeight="1">
+    <row r="237" spans="1:180" ht="25.5" customHeight="1">
       <c r="A237" s="64" t="s">
         <v>1599</v>
       </c>
@@ -46486,14 +46489,196 @@
         <v>1602</v>
       </c>
     </row>
+    <row r="238" spans="1:180" ht="25.5" customHeight="1">
+      <c r="A238" s="64"/>
+      <c r="B238" s="64"/>
+      <c r="C238" s="64"/>
+      <c r="D238" s="64"/>
+      <c r="E238" s="64"/>
+      <c r="F238" s="64"/>
+      <c r="G238" s="64"/>
+      <c r="H238" s="64"/>
+      <c r="I238" s="64"/>
+      <c r="J238" s="64"/>
+      <c r="K238" s="64"/>
+      <c r="L238" s="64"/>
+      <c r="M238" s="64"/>
+      <c r="N238" s="64"/>
+      <c r="O238" s="64"/>
+      <c r="P238" s="64"/>
+      <c r="Q238" s="64"/>
+      <c r="R238" s="64"/>
+      <c r="S238" s="64"/>
+      <c r="T238" s="64"/>
+      <c r="U238" s="64"/>
+      <c r="V238" s="64"/>
+      <c r="W238" s="64"/>
+      <c r="X238" s="64"/>
+      <c r="Y238" s="64"/>
+      <c r="Z238" s="64"/>
+      <c r="AA238" s="64"/>
+      <c r="AB238" s="64"/>
+      <c r="AC238" s="64"/>
+      <c r="AD238" s="64"/>
+      <c r="AE238" s="64"/>
+      <c r="AF238" s="64"/>
+      <c r="AG238" s="64"/>
+      <c r="AH238" s="64"/>
+      <c r="AI238" s="64"/>
+      <c r="AJ238" s="64"/>
+      <c r="AK238" s="64"/>
+      <c r="AL238" s="64"/>
+      <c r="AM238" s="64"/>
+      <c r="AN238" s="64"/>
+      <c r="AO238" s="64"/>
+      <c r="AP238" s="64"/>
+      <c r="AQ238" s="64"/>
+      <c r="AR238" s="64"/>
+      <c r="AS238" s="64"/>
+      <c r="AT238" s="64"/>
+      <c r="AU238" s="64"/>
+      <c r="AV238" s="64"/>
+      <c r="AW238" s="64"/>
+      <c r="AX238" s="64"/>
+      <c r="AY238" s="64"/>
+      <c r="AZ238" s="64"/>
+      <c r="BA238" s="64"/>
+      <c r="BB238" s="64"/>
+      <c r="BC238" s="64"/>
+      <c r="BD238" s="64"/>
+      <c r="BE238" s="64"/>
+      <c r="BF238" s="64"/>
+      <c r="BG238" s="64"/>
+      <c r="BH238" s="64"/>
+      <c r="BI238" s="64"/>
+      <c r="BJ238" s="64"/>
+      <c r="BK238" s="64"/>
+      <c r="BL238" s="64"/>
+      <c r="BM238" s="64"/>
+      <c r="BN238" s="64"/>
+      <c r="BO238" s="64"/>
+      <c r="BP238" s="64"/>
+      <c r="BQ238" s="64"/>
+      <c r="BR238" s="64"/>
+      <c r="BS238" s="64"/>
+      <c r="BT238" s="64"/>
+      <c r="BU238" s="64"/>
+      <c r="BV238" s="64"/>
+      <c r="BW238" s="64"/>
+      <c r="BX238" s="64"/>
+      <c r="BY238" s="64"/>
+      <c r="BZ238" s="64"/>
+      <c r="CA238" s="64"/>
+      <c r="CB238" s="64"/>
+      <c r="CC238" s="64"/>
+      <c r="CD238" s="64"/>
+      <c r="CE238" s="64"/>
+      <c r="CF238" s="64"/>
+      <c r="CG238" s="64"/>
+      <c r="CH238" s="64"/>
+      <c r="CI238" s="64"/>
+      <c r="CJ238" s="64"/>
+      <c r="CK238" s="64"/>
+      <c r="CL238" s="64"/>
+      <c r="CM238" s="64"/>
+      <c r="CN238" s="64"/>
+      <c r="CO238" s="64"/>
+      <c r="CP238" s="64"/>
+      <c r="CQ238" s="64"/>
+      <c r="CR238" s="64"/>
+      <c r="CS238" s="64"/>
+      <c r="CT238" s="64"/>
+      <c r="CU238" s="64"/>
+      <c r="CV238" s="64"/>
+      <c r="CW238" s="64"/>
+      <c r="CX238" s="64"/>
+      <c r="CY238" s="64"/>
+      <c r="CZ238" s="64"/>
+      <c r="DA238" s="64"/>
+      <c r="DB238" s="64"/>
+      <c r="DC238" s="64"/>
+      <c r="DD238" s="64"/>
+      <c r="DE238" s="64"/>
+      <c r="DF238" s="64"/>
+      <c r="DG238" s="64"/>
+      <c r="DH238" s="64"/>
+      <c r="DI238" s="64"/>
+      <c r="DJ238" s="64"/>
+      <c r="DK238" s="64"/>
+      <c r="DL238" s="64"/>
+      <c r="DM238" s="64"/>
+      <c r="DN238" s="64"/>
+      <c r="DO238" s="64"/>
+      <c r="DP238" s="64"/>
+      <c r="DQ238" s="64"/>
+      <c r="DR238" s="64"/>
+      <c r="DS238" s="64"/>
+      <c r="DT238" s="64"/>
+      <c r="DU238" s="64"/>
+      <c r="DV238" s="64"/>
+      <c r="DW238" s="64"/>
+      <c r="DX238" s="64"/>
+      <c r="DY238" s="64"/>
+      <c r="DZ238" s="64"/>
+      <c r="EA238" s="64"/>
+      <c r="EB238" s="64"/>
+      <c r="EC238" s="64"/>
+      <c r="ED238" s="64"/>
+      <c r="EE238" s="64"/>
+      <c r="EF238" s="64"/>
+      <c r="EG238" s="64"/>
+      <c r="EH238" s="64"/>
+      <c r="EI238" s="64"/>
+      <c r="EJ238" s="64"/>
+      <c r="EK238" s="64"/>
+      <c r="EL238" s="64"/>
+      <c r="EM238" s="64"/>
+      <c r="EN238" s="64"/>
+      <c r="EO238" s="64"/>
+      <c r="EP238" s="64"/>
+      <c r="EQ238" s="64"/>
+      <c r="ER238" s="64"/>
+      <c r="ES238" s="64"/>
+      <c r="ET238" s="64"/>
+      <c r="EU238" s="64"/>
+      <c r="EV238" s="64"/>
+      <c r="EW238" s="64"/>
+      <c r="EX238" s="64"/>
+      <c r="EY238" s="64"/>
+      <c r="EZ238" s="64"/>
+      <c r="FA238" s="64"/>
+      <c r="FB238" s="64"/>
+      <c r="FC238" s="64"/>
+      <c r="FD238" s="64"/>
+      <c r="FE238" s="64"/>
+      <c r="FF238" s="64"/>
+      <c r="FG238" s="64"/>
+      <c r="FH238" s="64"/>
+      <c r="FI238" s="64"/>
+      <c r="FJ238" s="64"/>
+      <c r="FK238" s="64"/>
+      <c r="FL238" s="64"/>
+      <c r="FM238" s="64"/>
+      <c r="FN238" s="64"/>
+      <c r="FO238" s="64"/>
+      <c r="FP238" s="64"/>
+      <c r="FQ238" s="64"/>
+      <c r="FR238" s="64"/>
+      <c r="FS238" s="64"/>
+      <c r="FT238" s="64"/>
+      <c r="FU238" s="64"/>
+      <c r="FV238" s="64"/>
+      <c r="FW238" s="64"/>
+      <c r="FX238" s="64"/>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:BC237">
     <sortCondition ref="A5:A237"/>
   </sortState>
-  <conditionalFormatting sqref="A8:B1048576 A5:A7 A1 A2:B4 C3:BC3">
+  <conditionalFormatting sqref="A8:B237 A5:A7 A1 A2:B4 C3:BC3 A239:B1048576 A238:FX238">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E2 E4:E1048576">
+  <conditionalFormatting sqref="E1:E2 E4:E237 E239:E1048576">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"boolean"</formula>
     </cfRule>

--- a/metadata.xlsx
+++ b/metadata.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{368FE683-6CCE-43A7-B1CE-A2D2BEFB873A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{02A7165D-88D0-49DD-8261-61A6AF26BFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11810,7 +11810,7 @@
         <v>288</v>
       </c>
       <c r="E24" s="54" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="F24" s="54" t="s">
         <v>64</v>
@@ -46678,7 +46678,7 @@
   <conditionalFormatting sqref="A8:B237 A5:A7 A1 A2:B4 C3:BC3 A239:B1048576 A238:FX238">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E2 E4:E237 E239:E1048576">
+  <conditionalFormatting sqref="E1:E2 E239:E1048576 E4:E237">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"boolean"</formula>
     </cfRule>

--- a/metadata.xlsx
+++ b/metadata.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{02A7165D-88D0-49DD-8261-61A6AF26BFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C741A750-42D3-4540-9636-3D6CCFB0435C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -237,7 +237,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5037" uniqueCount="1804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5034" uniqueCount="1804">
   <si>
     <t>VJDBv1.1</t>
   </si>
@@ -22949,9 +22949,7 @@
       </c>
       <c r="BA70" s="54"/>
       <c r="BB70" s="50"/>
-      <c r="BC70" s="58" t="s">
-        <v>80</v>
-      </c>
+      <c r="BC70" s="58"/>
       <c r="BD70" s="50"/>
       <c r="BE70" s="50"/>
       <c r="BF70" s="50"/>
@@ -24140,9 +24138,7 @@
       <c r="AZ75" s="54"/>
       <c r="BA75" s="54"/>
       <c r="BB75" s="50"/>
-      <c r="BC75" s="58" t="s">
-        <v>80</v>
-      </c>
+      <c r="BC75" s="58"/>
       <c r="BD75" s="50"/>
       <c r="BE75" s="50"/>
       <c r="BF75" s="50"/>
@@ -41614,9 +41610,7 @@
       <c r="BA187" s="57" t="s">
         <v>1384</v>
       </c>
-      <c r="BC187" s="58" t="s">
-        <v>80</v>
-      </c>
+      <c r="BC187" s="58"/>
     </row>
     <row r="188" spans="1:55" ht="25.5" customHeight="1">
       <c r="A188" s="64" t="s">

--- a/metadata.xlsx
+++ b/metadata.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C741A750-42D3-4540-9636-3D6CCFB0435C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{52BCC12C-C43D-4A9F-B847-69537D36D6E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -237,7 +237,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5034" uniqueCount="1804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5034" uniqueCount="1803">
   <si>
     <t>VJDBv1.1</t>
   </si>
@@ -4490,9 +4490,6 @@
   </si>
   <si>
     <t>List of VirJenDB metadata fields and their content when they are updated in each release in compare to the previous version</t>
-  </si>
-  <si>
-    <t>nested</t>
   </si>
   <si>
     <t>0hf</t>
@@ -25222,7 +25219,7 @@
         <v>718</v>
       </c>
       <c r="E80" s="54" t="s">
-        <v>63</v>
+        <v>216</v>
       </c>
       <c r="F80" s="54" t="s">
         <v>672</v>
@@ -41921,7 +41918,7 @@
         <v>1402</v>
       </c>
       <c r="E191" s="54" t="s">
-        <v>1403</v>
+        <v>117</v>
       </c>
       <c r="F191" s="54" t="s">
         <v>154</v>
@@ -42004,16 +42001,16 @@
     </row>
     <row r="192" spans="1:55" ht="25.5" customHeight="1">
       <c r="A192" s="64" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B192" s="64" t="s">
         <v>1404</v>
       </c>
-      <c r="B192" s="64" t="s">
+      <c r="C192" s="54" t="s">
         <v>1405</v>
       </c>
-      <c r="C192" s="54" t="s">
+      <c r="D192" s="71" t="s">
         <v>1406</v>
-      </c>
-      <c r="D192" s="71" t="s">
-        <v>1407</v>
       </c>
       <c r="E192" s="54" t="s">
         <v>76</v>
@@ -42101,16 +42098,16 @@
     </row>
     <row r="193" spans="1:55" ht="25.5" customHeight="1">
       <c r="A193" s="64" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B193" s="64" t="s">
         <v>1408</v>
       </c>
-      <c r="B193" s="64" t="s">
+      <c r="C193" s="54" t="s">
         <v>1409</v>
       </c>
-      <c r="C193" s="54" t="s">
+      <c r="D193" s="73" t="s">
         <v>1410</v>
-      </c>
-      <c r="D193" s="73" t="s">
-        <v>1411</v>
       </c>
       <c r="E193" s="54" t="s">
         <v>76</v>
@@ -42128,16 +42125,16 @@
       <c r="N193" s="54"/>
       <c r="O193" s="54"/>
       <c r="P193" s="60" t="s">
+        <v>1411</v>
+      </c>
+      <c r="Q193" s="60" t="s">
+        <v>1411</v>
+      </c>
+      <c r="R193" s="60" t="s">
+        <v>1411</v>
+      </c>
+      <c r="S193" s="60" t="s">
         <v>1412</v>
-      </c>
-      <c r="Q193" s="60" t="s">
-        <v>1412</v>
-      </c>
-      <c r="R193" s="60" t="s">
-        <v>1412</v>
-      </c>
-      <c r="S193" s="60" t="s">
-        <v>1413</v>
       </c>
       <c r="T193" s="54"/>
       <c r="U193" s="54"/>
@@ -42148,7 +42145,7 @@
         <v>205</v>
       </c>
       <c r="X193" s="52" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="Y193" s="54" t="str">
         <f>"[" &amp; _xlfn.TEXTJOIN(", ", TRUE,
@@ -42174,7 +42171,7 @@
         <v>["IMG/VR", "PHD", "PhiSpy", "GTDB", "Host", "Host Taxonomy", "GTDB Taxonomy"]</v>
       </c>
       <c r="Z193" s="54" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="AA193" s="54"/>
       <c r="AB193" s="54"/>
@@ -42206,16 +42203,16 @@
     </row>
     <row r="194" spans="1:55" ht="25.5" customHeight="1">
       <c r="A194" s="64" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B194" s="64" t="s">
         <v>1416</v>
       </c>
-      <c r="B194" s="64" t="s">
+      <c r="C194" s="54" t="s">
         <v>1417</v>
       </c>
-      <c r="C194" s="54" t="s">
+      <c r="D194" s="71" t="s">
         <v>1418</v>
-      </c>
-      <c r="D194" s="71" t="s">
-        <v>1419</v>
       </c>
       <c r="E194" s="54" t="s">
         <v>76</v>
@@ -42269,7 +42266,7 @@
         <v>["Internal", "Workflows"]</v>
       </c>
       <c r="Z194" s="54" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="AA194" s="54"/>
       <c r="AB194" s="54"/>
@@ -42301,16 +42298,16 @@
     </row>
     <row r="195" spans="1:55" ht="25.5" customHeight="1">
       <c r="A195" s="64" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B195" s="64" t="s">
         <v>1421</v>
       </c>
-      <c r="B195" s="64" t="s">
+      <c r="C195" s="54" t="s">
         <v>1422</v>
       </c>
-      <c r="C195" s="54" t="s">
+      <c r="D195" s="71" t="s">
         <v>1423</v>
-      </c>
-      <c r="D195" s="71" t="s">
-        <v>1424</v>
       </c>
       <c r="E195" s="54" t="s">
         <v>63</v>
@@ -42396,16 +42393,16 @@
     </row>
     <row r="196" spans="1:55" ht="25.5" customHeight="1">
       <c r="A196" s="64" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B196" s="64" t="s">
         <v>1425</v>
       </c>
-      <c r="B196" s="64" t="s">
+      <c r="C196" s="54" t="s">
         <v>1426</v>
       </c>
-      <c r="C196" s="54" t="s">
+      <c r="D196" s="71" t="s">
         <v>1427</v>
-      </c>
-      <c r="D196" s="71" t="s">
-        <v>1428</v>
       </c>
       <c r="E196" s="54" t="s">
         <v>162</v>
@@ -42494,16 +42491,16 @@
     </row>
     <row r="197" spans="1:55" ht="25.5" customHeight="1">
       <c r="A197" s="64" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B197" s="64" t="s">
         <v>1429</v>
       </c>
-      <c r="B197" s="64" t="s">
+      <c r="C197" s="54" t="s">
         <v>1430</v>
       </c>
-      <c r="C197" s="54" t="s">
+      <c r="D197" s="71" t="s">
         <v>1431</v>
-      </c>
-      <c r="D197" s="71" t="s">
-        <v>1432</v>
       </c>
       <c r="E197" s="54" t="s">
         <v>63</v>
@@ -42591,16 +42588,16 @@
     </row>
     <row r="198" spans="1:55" ht="25.5" customHeight="1">
       <c r="A198" s="64" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B198" s="64" t="s">
         <v>1433</v>
       </c>
-      <c r="B198" s="64" t="s">
+      <c r="C198" s="54" t="s">
         <v>1434</v>
       </c>
-      <c r="C198" s="54" t="s">
+      <c r="D198" s="71" t="s">
         <v>1435</v>
-      </c>
-      <c r="D198" s="71" t="s">
-        <v>1436</v>
       </c>
       <c r="E198" s="54" t="s">
         <v>162</v>
@@ -42689,16 +42686,16 @@
     </row>
     <row r="199" spans="1:55" ht="25.5" customHeight="1">
       <c r="A199" s="64" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B199" s="64" t="s">
         <v>1437</v>
       </c>
-      <c r="B199" s="64" t="s">
+      <c r="C199" s="54" t="s">
         <v>1438</v>
       </c>
-      <c r="C199" s="54" t="s">
+      <c r="D199" s="71" t="s">
         <v>1439</v>
-      </c>
-      <c r="D199" s="71" t="s">
-        <v>1440</v>
       </c>
       <c r="E199" s="54" t="s">
         <v>63</v>
@@ -42782,16 +42779,16 @@
     </row>
     <row r="200" spans="1:55" ht="25.5" customHeight="1">
       <c r="A200" s="64" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B200" s="64" t="s">
         <v>1441</v>
       </c>
-      <c r="B200" s="64" t="s">
+      <c r="C200" s="54" t="s">
         <v>1442</v>
       </c>
-      <c r="C200" s="54" t="s">
+      <c r="D200" s="71" t="s">
         <v>1443</v>
-      </c>
-      <c r="D200" s="71" t="s">
-        <v>1444</v>
       </c>
       <c r="E200" s="54" t="s">
         <v>76</v>
@@ -42845,7 +42842,7 @@
         <v>["Analysis", "Workflows"]</v>
       </c>
       <c r="Z200" s="54" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="AA200" s="54"/>
       <c r="AB200" s="54"/>
@@ -42877,16 +42874,16 @@
     </row>
     <row r="201" spans="1:55" ht="25.5" customHeight="1">
       <c r="A201" s="64" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B201" s="64" t="s">
         <v>1445</v>
       </c>
-      <c r="B201" s="64" t="s">
+      <c r="C201" s="54" t="s">
         <v>1446</v>
       </c>
-      <c r="C201" s="54" t="s">
+      <c r="D201" s="71" t="s">
         <v>1447</v>
-      </c>
-      <c r="D201" s="71" t="s">
-        <v>1448</v>
       </c>
       <c r="E201" s="54" t="s">
         <v>63</v>
@@ -42904,11 +42901,11 @@
       <c r="N201" s="54"/>
       <c r="O201" s="54"/>
       <c r="P201" s="60" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="Q201" s="60"/>
       <c r="R201" s="60" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="S201" s="54"/>
       <c r="T201" s="54"/>
@@ -42979,16 +42976,16 @@
     </row>
     <row r="202" spans="1:55" ht="25.5" customHeight="1">
       <c r="A202" s="64" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B202" s="64" t="s">
         <v>1450</v>
       </c>
-      <c r="B202" s="64" t="s">
+      <c r="C202" s="54" t="s">
         <v>1451</v>
       </c>
-      <c r="C202" s="54" t="s">
+      <c r="D202" s="71" t="s">
         <v>1452</v>
-      </c>
-      <c r="D202" s="71" t="s">
-        <v>1453</v>
       </c>
       <c r="E202" s="54" t="s">
         <v>76</v>
@@ -43006,11 +43003,11 @@
       <c r="N202" s="54"/>
       <c r="O202" s="54"/>
       <c r="P202" s="60" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="Q202" s="60"/>
       <c r="R202" s="60" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="S202" s="54"/>
       <c r="T202" s="53"/>
@@ -43046,7 +43043,7 @@
         <v>["IMG/VR", "PhiSpy", "Host", "Workflows"]</v>
       </c>
       <c r="Z202" s="54" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="AA202" s="54"/>
       <c r="AB202" s="54"/>
@@ -43080,16 +43077,16 @@
     </row>
     <row r="203" spans="1:55" ht="25.5" customHeight="1">
       <c r="A203" s="64" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B203" s="64" t="s">
         <v>1454</v>
       </c>
-      <c r="B203" s="64" t="s">
+      <c r="C203" s="54" t="s">
         <v>1455</v>
       </c>
-      <c r="C203" s="54" t="s">
+      <c r="D203" s="71" t="s">
         <v>1456</v>
-      </c>
-      <c r="D203" s="71" t="s">
-        <v>1457</v>
       </c>
       <c r="E203" s="54" t="s">
         <v>63</v>
@@ -43107,11 +43104,11 @@
       <c r="N203" s="54"/>
       <c r="O203" s="54"/>
       <c r="P203" s="60" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="Q203" s="60"/>
       <c r="R203" s="60" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="S203" s="54"/>
       <c r="T203" s="53"/>
@@ -43147,7 +43144,7 @@
         <v>["IMG/VR", "PhiSpy", "Host", "Identifiers"]</v>
       </c>
       <c r="Z203" s="54" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="AA203" s="54"/>
       <c r="AB203" s="54"/>
@@ -43179,16 +43176,16 @@
     </row>
     <row r="204" spans="1:55" ht="25.5" customHeight="1">
       <c r="A204" s="64" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B204" s="64" t="s">
         <v>1459</v>
       </c>
-      <c r="B204" s="64" t="s">
+      <c r="C204" s="54" t="s">
         <v>1460</v>
       </c>
-      <c r="C204" s="54" t="s">
+      <c r="D204" s="71" t="s">
         <v>1461</v>
-      </c>
-      <c r="D204" s="71" t="s">
-        <v>1462</v>
       </c>
       <c r="E204" s="54" t="s">
         <v>63</v>
@@ -43206,11 +43203,11 @@
       <c r="N204" s="54"/>
       <c r="O204" s="54"/>
       <c r="P204" s="60" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="Q204" s="60"/>
       <c r="R204" s="60" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="S204" s="54"/>
       <c r="T204" s="53"/>
@@ -43246,7 +43243,7 @@
         <v>["IMG/VR", "PhiSpy", "Host", "Identifiers"]</v>
       </c>
       <c r="Z204" s="54" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="AA204" s="54"/>
       <c r="AB204" s="54"/>
@@ -43278,16 +43275,16 @@
     </row>
     <row r="205" spans="1:55" ht="25.5" customHeight="1">
       <c r="A205" s="64" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B205" s="64" t="s">
         <v>1464</v>
       </c>
-      <c r="B205" s="64" t="s">
+      <c r="C205" s="54" t="s">
         <v>1465</v>
       </c>
-      <c r="C205" s="54" t="s">
+      <c r="D205" s="71" t="s">
         <v>1466</v>
-      </c>
-      <c r="D205" s="71" t="s">
-        <v>1467</v>
       </c>
       <c r="E205" s="54" t="s">
         <v>76</v>
@@ -43305,11 +43302,11 @@
       <c r="N205" s="54"/>
       <c r="O205" s="54"/>
       <c r="P205" s="60" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="Q205" s="60"/>
       <c r="R205" s="60" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="S205" s="54"/>
       <c r="T205" s="53"/>
@@ -43345,7 +43342,7 @@
         <v>["IMG/VR", "PhiSpy", "Host", "Collection"]</v>
       </c>
       <c r="Z205" s="54" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="AA205" s="54"/>
       <c r="AB205" s="54"/>
@@ -43381,16 +43378,16 @@
     </row>
     <row r="206" spans="1:55" ht="25.5" customHeight="1">
       <c r="A206" s="64" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B206" s="64" t="s">
         <v>1469</v>
       </c>
-      <c r="B206" s="64" t="s">
+      <c r="C206" s="54" t="s">
         <v>1470</v>
       </c>
-      <c r="C206" s="54" t="s">
+      <c r="D206" s="71" t="s">
         <v>1471</v>
-      </c>
-      <c r="D206" s="71" t="s">
-        <v>1472</v>
       </c>
       <c r="E206" s="54" t="s">
         <v>117</v>
@@ -43408,11 +43405,11 @@
       <c r="N206" s="54"/>
       <c r="O206" s="54"/>
       <c r="P206" s="60" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="Q206" s="60"/>
       <c r="R206" s="60" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="S206" s="54"/>
       <c r="T206" s="53"/>
@@ -43448,7 +43445,7 @@
         <v>["IMG/VR", "PhiSpy", "Host", "Collection"]</v>
       </c>
       <c r="Z206" s="54" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="AA206" s="54"/>
       <c r="AB206" s="54"/>
@@ -43471,7 +43468,7 @@
       <c r="AS206" s="54"/>
       <c r="AT206" s="54"/>
       <c r="AU206" s="55" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="AV206" s="54" t="s">
         <v>131</v>
@@ -43484,16 +43481,16 @@
     </row>
     <row r="207" spans="1:55" ht="25.5" customHeight="1">
       <c r="A207" s="64" t="s">
+        <v>1473</v>
+      </c>
+      <c r="B207" s="64" t="s">
         <v>1474</v>
       </c>
-      <c r="B207" s="64" t="s">
+      <c r="C207" s="54" t="s">
         <v>1475</v>
       </c>
-      <c r="C207" s="54" t="s">
+      <c r="D207" s="74" t="s">
         <v>1476</v>
-      </c>
-      <c r="D207" s="74" t="s">
-        <v>1477</v>
       </c>
       <c r="E207" s="54" t="s">
         <v>63</v>
@@ -43511,7 +43508,7 @@
       <c r="N207" s="54"/>
       <c r="O207" s="54"/>
       <c r="P207" s="54" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="Q207" s="54"/>
       <c r="R207" s="54"/>
@@ -43549,7 +43546,7 @@
         <v>["IMG/VR", "Host", "Identifiers"]</v>
       </c>
       <c r="Z207" s="54" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="AA207" s="54"/>
       <c r="AB207" s="54"/>
@@ -43581,16 +43578,16 @@
     </row>
     <row r="208" spans="1:55" ht="25.5" customHeight="1">
       <c r="A208" s="51" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B208" s="51" t="s">
         <v>1479</v>
       </c>
-      <c r="B208" s="51" t="s">
+      <c r="C208" s="52" t="s">
         <v>1480</v>
       </c>
-      <c r="C208" s="52" t="s">
+      <c r="D208" s="72" t="s">
         <v>1481</v>
-      </c>
-      <c r="D208" s="72" t="s">
-        <v>1482</v>
       </c>
       <c r="E208" s="54" t="s">
         <v>63</v>
@@ -43608,13 +43605,13 @@
       <c r="N208" s="52"/>
       <c r="O208" s="52"/>
       <c r="P208" s="60" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="Q208" s="60" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="R208" s="60" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="S208" s="52"/>
       <c r="T208" s="52"/>
@@ -43653,7 +43650,7 @@
         <v>16</v>
       </c>
       <c r="AA208" s="52" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="AB208" s="52"/>
       <c r="AC208" s="52"/>
@@ -43686,16 +43683,16 @@
     </row>
     <row r="209" spans="1:53" ht="25.5" customHeight="1">
       <c r="A209" s="64" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B209" s="64" t="s">
         <v>1484</v>
       </c>
-      <c r="B209" s="64" t="s">
+      <c r="C209" s="54" t="s">
         <v>1485</v>
       </c>
-      <c r="C209" s="54" t="s">
+      <c r="D209" s="71" t="s">
         <v>1486</v>
-      </c>
-      <c r="D209" s="71" t="s">
-        <v>1487</v>
       </c>
       <c r="E209" s="54" t="s">
         <v>254</v>
@@ -43713,11 +43710,11 @@
       <c r="N209" s="54"/>
       <c r="O209" s="54"/>
       <c r="P209" s="60" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="Q209" s="60"/>
       <c r="R209" s="60" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="S209" s="54"/>
       <c r="T209" s="54"/>
@@ -43753,7 +43750,7 @@
         <v>["IMG/VR", "PhiSpy", "Host", "Workflows"]</v>
       </c>
       <c r="Z209" s="54" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="AA209" s="54"/>
       <c r="AB209" s="54"/>
@@ -43789,16 +43786,16 @@
     </row>
     <row r="210" spans="1:53" ht="25.5" customHeight="1">
       <c r="A210" s="64" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B210" s="64" t="s">
         <v>1489</v>
       </c>
-      <c r="B210" s="64" t="s">
+      <c r="C210" s="54" t="s">
         <v>1490</v>
       </c>
-      <c r="C210" s="54" t="s">
+      <c r="D210" s="71" t="s">
         <v>1491</v>
-      </c>
-      <c r="D210" s="71" t="s">
-        <v>1492</v>
       </c>
       <c r="E210" s="54" t="s">
         <v>76</v>
@@ -43816,11 +43813,11 @@
       <c r="N210" s="54"/>
       <c r="O210" s="54"/>
       <c r="P210" s="60" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="Q210" s="60"/>
       <c r="R210" s="60" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="S210" s="54"/>
       <c r="T210" s="54"/>
@@ -43856,7 +43853,7 @@
         <v>["IMG/VR", "PhiSpy", "Workflows", "Host"]</v>
       </c>
       <c r="Z210" s="54" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="AA210" s="54"/>
       <c r="AB210" s="54"/>
@@ -43892,16 +43889,16 @@
     </row>
     <row r="211" spans="1:53" ht="25.5" customHeight="1">
       <c r="A211" s="64" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B211" s="64" t="s">
         <v>1493</v>
       </c>
-      <c r="B211" s="64" t="s">
+      <c r="C211" s="54" t="s">
         <v>1494</v>
       </c>
-      <c r="C211" s="54" t="s">
+      <c r="D211" s="71" t="s">
         <v>1495</v>
-      </c>
-      <c r="D211" s="71" t="s">
-        <v>1496</v>
       </c>
       <c r="E211" s="54" t="s">
         <v>63</v>
@@ -43987,16 +43984,16 @@
     </row>
     <row r="212" spans="1:53" ht="25.5" customHeight="1">
       <c r="A212" s="64" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B212" s="64" t="s">
         <v>1497</v>
       </c>
-      <c r="B212" s="64" t="s">
+      <c r="C212" s="54" t="s">
         <v>1498</v>
       </c>
-      <c r="C212" s="54" t="s">
+      <c r="D212" s="71" t="s">
         <v>1499</v>
-      </c>
-      <c r="D212" s="71" t="s">
-        <v>1500</v>
       </c>
       <c r="E212" s="54" t="s">
         <v>63</v>
@@ -44082,16 +44079,16 @@
     </row>
     <row r="213" spans="1:53" ht="25.5" customHeight="1">
       <c r="A213" s="64" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B213" s="64" t="s">
         <v>1501</v>
       </c>
-      <c r="B213" s="64" t="s">
+      <c r="C213" s="54" t="s">
         <v>1502</v>
       </c>
-      <c r="C213" s="54" t="s">
+      <c r="D213" s="71" t="s">
         <v>1503</v>
-      </c>
-      <c r="D213" s="71" t="s">
-        <v>1504</v>
       </c>
       <c r="E213" s="54" t="s">
         <v>63</v>
@@ -44177,16 +44174,16 @@
     </row>
     <row r="214" spans="1:53" ht="25.5" customHeight="1">
       <c r="A214" s="64" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B214" s="64" t="s">
         <v>1505</v>
       </c>
-      <c r="B214" s="64" t="s">
+      <c r="C214" s="54" t="s">
         <v>1506</v>
       </c>
-      <c r="C214" s="54" t="s">
+      <c r="D214" s="71" t="s">
         <v>1507</v>
-      </c>
-      <c r="D214" s="71" t="s">
-        <v>1508</v>
       </c>
       <c r="E214" s="54" t="s">
         <v>76</v>
@@ -44272,16 +44269,16 @@
     </row>
     <row r="215" spans="1:53" ht="25.5" customHeight="1">
       <c r="A215" s="64" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B215" s="64" t="s">
         <v>1509</v>
       </c>
-      <c r="B215" s="64" t="s">
+      <c r="C215" s="54" t="s">
         <v>1510</v>
       </c>
-      <c r="C215" s="54" t="s">
+      <c r="D215" s="71" t="s">
         <v>1511</v>
-      </c>
-      <c r="D215" s="71" t="s">
-        <v>1512</v>
       </c>
       <c r="E215" s="54" t="s">
         <v>63</v>
@@ -44367,16 +44364,16 @@
     </row>
     <row r="216" spans="1:53" ht="25.5" customHeight="1">
       <c r="A216" s="64" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B216" s="64" t="s">
         <v>1513</v>
       </c>
-      <c r="B216" s="64" t="s">
+      <c r="C216" s="54" t="s">
         <v>1514</v>
       </c>
-      <c r="C216" s="54" t="s">
-        <v>1515</v>
-      </c>
       <c r="D216" s="75" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="E216" s="54" t="s">
         <v>63</v>
@@ -44394,7 +44391,7 @@
       <c r="N216" s="54"/>
       <c r="O216" s="54"/>
       <c r="P216" s="54" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="Q216" s="54"/>
       <c r="R216" s="54"/>
@@ -44405,7 +44402,7 @@
         <v>204</v>
       </c>
       <c r="W216" s="54" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="X216" s="54"/>
       <c r="Y216" s="54" t="str">
@@ -44432,7 +44429,7 @@
         <v>["IMG/VR", "Host", "Identifier"]</v>
       </c>
       <c r="Z216" s="54" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="AA216" s="54"/>
       <c r="AB216" s="54"/>
@@ -44464,16 +44461,16 @@
     </row>
     <row r="217" spans="1:53" ht="25.5" customHeight="1">
       <c r="A217" s="64" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B217" s="64" t="s">
         <v>1517</v>
       </c>
-      <c r="B217" s="64" t="s">
+      <c r="C217" s="54" t="s">
         <v>1518</v>
       </c>
-      <c r="C217" s="54" t="s">
+      <c r="D217" s="71" t="s">
         <v>1519</v>
-      </c>
-      <c r="D217" s="71" t="s">
-        <v>1520</v>
       </c>
       <c r="E217" s="54" t="s">
         <v>162</v>
@@ -44552,7 +44549,7 @@
       <c r="AS217" s="54"/>
       <c r="AT217" s="54"/>
       <c r="AU217" s="55" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="AV217" s="54" t="s">
         <v>169</v>
@@ -44565,16 +44562,16 @@
     </row>
     <row r="218" spans="1:53" ht="25.5" customHeight="1">
       <c r="A218" s="64" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B218" s="64" t="s">
         <v>1522</v>
       </c>
-      <c r="B218" s="64" t="s">
+      <c r="C218" s="54" t="s">
         <v>1523</v>
       </c>
-      <c r="C218" s="54" t="s">
+      <c r="D218" s="71" t="s">
         <v>1524</v>
-      </c>
-      <c r="D218" s="71" t="s">
-        <v>1525</v>
       </c>
       <c r="E218" s="54" t="s">
         <v>76</v>
@@ -44592,11 +44589,11 @@
       <c r="N218" s="54"/>
       <c r="O218" s="54"/>
       <c r="P218" s="60" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="Q218" s="60"/>
       <c r="R218" s="60" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="S218" s="54"/>
       <c r="T218" s="54"/>
@@ -44656,7 +44653,7 @@
       <c r="AT218" s="54"/>
       <c r="AU218" s="55"/>
       <c r="AV218" s="54" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="AW218" s="54"/>
       <c r="AX218" s="54"/>
@@ -44666,16 +44663,16 @@
     </row>
     <row r="219" spans="1:53" ht="25.5" customHeight="1">
       <c r="A219" s="64" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B219" s="64" t="s">
         <v>1527</v>
       </c>
-      <c r="B219" s="64" t="s">
+      <c r="C219" s="54" t="s">
         <v>1528</v>
       </c>
-      <c r="C219" s="54" t="s">
+      <c r="D219" s="71" t="s">
         <v>1529</v>
-      </c>
-      <c r="D219" s="71" t="s">
-        <v>1530</v>
       </c>
       <c r="E219" s="54" t="s">
         <v>254</v>
@@ -44693,11 +44690,11 @@
       <c r="N219" s="54"/>
       <c r="O219" s="54"/>
       <c r="P219" s="60" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="Q219" s="60"/>
       <c r="R219" s="60" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="S219" s="54"/>
       <c r="T219" s="54"/>
@@ -44765,16 +44762,16 @@
     </row>
     <row r="220" spans="1:53" ht="25.5" customHeight="1">
       <c r="A220" s="64" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B220" s="64" t="s">
         <v>1531</v>
       </c>
-      <c r="B220" s="64" t="s">
+      <c r="C220" s="54" t="s">
         <v>1532</v>
       </c>
-      <c r="C220" s="54" t="s">
+      <c r="D220" s="71" t="s">
         <v>1533</v>
-      </c>
-      <c r="D220" s="71" t="s">
-        <v>1534</v>
       </c>
       <c r="E220" s="54" t="s">
         <v>76</v>
@@ -44862,16 +44859,16 @@
     </row>
     <row r="221" spans="1:53" ht="25.5" customHeight="1">
       <c r="A221" s="64" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B221" s="64" t="s">
         <v>1535</v>
       </c>
-      <c r="B221" s="64" t="s">
+      <c r="C221" s="54" t="s">
         <v>1536</v>
       </c>
-      <c r="C221" s="54" t="s">
+      <c r="D221" s="71" t="s">
         <v>1537</v>
-      </c>
-      <c r="D221" s="71" t="s">
-        <v>1538</v>
       </c>
       <c r="E221" s="54" t="s">
         <v>76</v>
@@ -44959,16 +44956,16 @@
     </row>
     <row r="222" spans="1:53" ht="25.5" customHeight="1">
       <c r="A222" s="64" t="s">
+        <v>1538</v>
+      </c>
+      <c r="B222" s="64" t="s">
         <v>1539</v>
       </c>
-      <c r="B222" s="64" t="s">
+      <c r="C222" s="54" t="s">
         <v>1540</v>
       </c>
-      <c r="C222" s="54" t="s">
+      <c r="D222" s="71" t="s">
         <v>1541</v>
-      </c>
-      <c r="D222" s="71" t="s">
-        <v>1542</v>
       </c>
       <c r="E222" s="54" t="s">
         <v>76</v>
@@ -45056,16 +45053,16 @@
     </row>
     <row r="223" spans="1:53" ht="25.5" customHeight="1">
       <c r="A223" s="64" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B223" s="64" t="s">
         <v>1543</v>
       </c>
-      <c r="B223" s="64" t="s">
+      <c r="C223" s="54" t="s">
         <v>1544</v>
       </c>
-      <c r="C223" s="54" t="s">
+      <c r="D223" s="71" t="s">
         <v>1545</v>
-      </c>
-      <c r="D223" s="71" t="s">
-        <v>1546</v>
       </c>
       <c r="E223" s="54" t="s">
         <v>76</v>
@@ -45153,16 +45150,16 @@
     </row>
     <row r="224" spans="1:53" ht="25.5" customHeight="1">
       <c r="A224" s="64" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B224" s="64" t="s">
         <v>1547</v>
       </c>
-      <c r="B224" s="64" t="s">
+      <c r="C224" s="54" t="s">
         <v>1548</v>
       </c>
-      <c r="C224" s="54" t="s">
+      <c r="D224" s="71" t="s">
         <v>1549</v>
-      </c>
-      <c r="D224" s="71" t="s">
-        <v>1550</v>
       </c>
       <c r="E224" s="54" t="s">
         <v>216</v>
@@ -45248,16 +45245,16 @@
     </row>
     <row r="225" spans="1:180" ht="25.5" customHeight="1">
       <c r="A225" s="64" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B225" s="64" t="s">
         <v>1551</v>
       </c>
-      <c r="B225" s="64" t="s">
+      <c r="C225" s="66" t="s">
         <v>1552</v>
       </c>
-      <c r="C225" s="66" t="s">
+      <c r="D225" s="71" t="s">
         <v>1553</v>
-      </c>
-      <c r="D225" s="71" t="s">
-        <v>1554</v>
       </c>
       <c r="E225" s="54" t="s">
         <v>63</v>
@@ -45343,16 +45340,16 @@
     </row>
     <row r="226" spans="1:180" ht="25.5" customHeight="1">
       <c r="A226" s="64" t="s">
+        <v>1554</v>
+      </c>
+      <c r="B226" s="64" t="s">
         <v>1555</v>
       </c>
-      <c r="B226" s="64" t="s">
+      <c r="C226" s="54" t="s">
         <v>1556</v>
       </c>
-      <c r="C226" s="54" t="s">
+      <c r="D226" s="71" t="s">
         <v>1557</v>
-      </c>
-      <c r="D226" s="71" t="s">
-        <v>1558</v>
       </c>
       <c r="E226" s="54" t="s">
         <v>216</v>
@@ -45438,16 +45435,16 @@
     </row>
     <row r="227" spans="1:180" ht="25.5" customHeight="1">
       <c r="A227" s="64" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B227" s="64" t="s">
         <v>1559</v>
       </c>
-      <c r="B227" s="64" t="s">
+      <c r="C227" s="54" t="s">
         <v>1560</v>
       </c>
-      <c r="C227" s="54" t="s">
+      <c r="D227" s="71" t="s">
         <v>1561</v>
-      </c>
-      <c r="D227" s="71" t="s">
-        <v>1562</v>
       </c>
       <c r="E227" s="54" t="s">
         <v>216</v>
@@ -45533,16 +45530,16 @@
     </row>
     <row r="228" spans="1:180" ht="25.5" customHeight="1">
       <c r="A228" s="64" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B228" s="64" t="s">
         <v>1563</v>
       </c>
-      <c r="B228" s="64" t="s">
+      <c r="C228" s="54" t="s">
         <v>1564</v>
       </c>
-      <c r="C228" s="54" t="s">
+      <c r="D228" s="71" t="s">
         <v>1565</v>
-      </c>
-      <c r="D228" s="71" t="s">
-        <v>1566</v>
       </c>
       <c r="E228" s="54" t="s">
         <v>216</v>
@@ -45628,16 +45625,16 @@
     </row>
     <row r="229" spans="1:180" ht="25.5" customHeight="1">
       <c r="A229" s="64" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B229" s="64" t="s">
         <v>1567</v>
       </c>
-      <c r="B229" s="64" t="s">
+      <c r="C229" s="54" t="s">
         <v>1568</v>
       </c>
-      <c r="C229" s="54" t="s">
+      <c r="D229" s="71" t="s">
         <v>1569</v>
-      </c>
-      <c r="D229" s="71" t="s">
-        <v>1570</v>
       </c>
       <c r="E229" s="54" t="s">
         <v>216</v>
@@ -45723,16 +45720,16 @@
     </row>
     <row r="230" spans="1:180" ht="25.5" customHeight="1">
       <c r="A230" s="64" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B230" s="64" t="s">
         <v>1571</v>
       </c>
-      <c r="B230" s="64" t="s">
+      <c r="C230" s="54" t="s">
         <v>1572</v>
       </c>
-      <c r="C230" s="54" t="s">
+      <c r="D230" s="71" t="s">
         <v>1573</v>
-      </c>
-      <c r="D230" s="71" t="s">
-        <v>1574</v>
       </c>
       <c r="E230" s="54" t="s">
         <v>63</v>
@@ -45818,16 +45815,16 @@
     </row>
     <row r="231" spans="1:180" ht="25.5" customHeight="1">
       <c r="A231" s="64" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B231" s="64" t="s">
         <v>1575</v>
       </c>
-      <c r="B231" s="64" t="s">
+      <c r="C231" s="54" t="s">
         <v>1576</v>
       </c>
-      <c r="C231" s="54" t="s">
+      <c r="D231" s="71" t="s">
         <v>1577</v>
-      </c>
-      <c r="D231" s="71" t="s">
-        <v>1578</v>
       </c>
       <c r="E231" s="54" t="s">
         <v>63</v>
@@ -45913,16 +45910,16 @@
     </row>
     <row r="232" spans="1:180" ht="25.5" customHeight="1">
       <c r="A232" s="64" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B232" s="64" t="s">
         <v>1579</v>
       </c>
-      <c r="B232" s="64" t="s">
+      <c r="C232" s="54" t="s">
         <v>1580</v>
       </c>
-      <c r="C232" s="54" t="s">
+      <c r="D232" s="71" t="s">
         <v>1581</v>
-      </c>
-      <c r="D232" s="71" t="s">
-        <v>1582</v>
       </c>
       <c r="E232" s="54" t="s">
         <v>254</v>
@@ -46008,16 +46005,16 @@
     </row>
     <row r="233" spans="1:180" ht="25.5" customHeight="1">
       <c r="A233" s="64" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B233" s="64" t="s">
         <v>1583</v>
       </c>
-      <c r="B233" s="64" t="s">
+      <c r="C233" s="54" t="s">
         <v>1584</v>
       </c>
-      <c r="C233" s="54" t="s">
+      <c r="D233" s="71" t="s">
         <v>1585</v>
-      </c>
-      <c r="D233" s="71" t="s">
-        <v>1586</v>
       </c>
       <c r="E233" s="54" t="s">
         <v>76</v>
@@ -46103,16 +46100,16 @@
     </row>
     <row r="234" spans="1:180" ht="25.5" customHeight="1">
       <c r="A234" s="64" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B234" s="64" t="s">
         <v>1587</v>
       </c>
-      <c r="B234" s="64" t="s">
+      <c r="C234" s="54" t="s">
         <v>1588</v>
       </c>
-      <c r="C234" s="54" t="s">
+      <c r="D234" s="71" t="s">
         <v>1589</v>
-      </c>
-      <c r="D234" s="71" t="s">
-        <v>1590</v>
       </c>
       <c r="E234" s="54" t="s">
         <v>254</v>
@@ -46198,16 +46195,16 @@
     </row>
     <row r="235" spans="1:180" ht="25.5" customHeight="1">
       <c r="A235" s="64" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B235" s="64" t="s">
         <v>1591</v>
       </c>
-      <c r="B235" s="64" t="s">
+      <c r="C235" s="54" t="s">
         <v>1592</v>
       </c>
-      <c r="C235" s="54" t="s">
+      <c r="D235" s="71" t="s">
         <v>1593</v>
-      </c>
-      <c r="D235" s="71" t="s">
-        <v>1594</v>
       </c>
       <c r="E235" s="54" t="s">
         <v>216</v>
@@ -46293,16 +46290,16 @@
     </row>
     <row r="236" spans="1:180" ht="25.5" customHeight="1">
       <c r="A236" s="64" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B236" s="64" t="s">
         <v>1595</v>
       </c>
-      <c r="B236" s="64" t="s">
+      <c r="C236" s="54" t="s">
         <v>1596</v>
       </c>
-      <c r="C236" s="54" t="s">
+      <c r="D236" s="71" t="s">
         <v>1597</v>
-      </c>
-      <c r="D236" s="71" t="s">
-        <v>1598</v>
       </c>
       <c r="E236" s="54" t="s">
         <v>63</v>
@@ -46388,16 +46385,16 @@
     </row>
     <row r="237" spans="1:180" ht="25.5" customHeight="1">
       <c r="A237" s="64" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B237" s="64" t="s">
         <v>1599</v>
       </c>
-      <c r="B237" s="64" t="s">
+      <c r="C237" s="54" t="s">
         <v>1600</v>
       </c>
-      <c r="C237" s="54" t="s">
+      <c r="D237" s="71" t="s">
         <v>1601</v>
-      </c>
-      <c r="D237" s="71" t="s">
-        <v>1602</v>
       </c>
       <c r="E237" s="54" t="s">
         <v>63</v>
@@ -46477,10 +46474,10 @@
       <c r="AX237" s="54"/>
       <c r="AY237" s="54"/>
       <c r="AZ237" s="56" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="BA237" s="71" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="238" spans="1:180" ht="25.5" customHeight="1">
@@ -46697,25 +46694,25 @@
   <sheetData>
     <row r="1" spans="1:172" s="19" customFormat="1" ht="23.25" customHeight="1">
       <c r="A1" s="17" t="s">
+        <v>1603</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>1603</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>1603</v>
+      </c>
+      <c r="F1" s="18" t="s">
         <v>1604</v>
       </c>
-      <c r="B1" s="17" t="s">
-        <v>1604</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>1604</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>1604</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>1604</v>
-      </c>
-      <c r="F1" s="18" t="s">
+      <c r="G1" s="18" t="s">
         <v>1605</v>
-      </c>
-      <c r="G1" s="18" t="s">
-        <v>1606</v>
       </c>
       <c r="H1" s="18" t="s">
         <v>1</v>
@@ -46748,25 +46745,25 @@
         <v>14</v>
       </c>
       <c r="R1" s="20" t="s">
+        <v>1603</v>
+      </c>
+      <c r="S1" s="20" t="s">
+        <v>1603</v>
+      </c>
+      <c r="T1" s="20" t="s">
+        <v>1603</v>
+      </c>
+      <c r="U1" s="20" t="s">
+        <v>1603</v>
+      </c>
+      <c r="V1" s="20" t="s">
+        <v>1603</v>
+      </c>
+      <c r="W1" s="20" t="s">
+        <v>1603</v>
+      </c>
+      <c r="X1" s="18" t="s">
         <v>1604</v>
-      </c>
-      <c r="S1" s="20" t="s">
-        <v>1604</v>
-      </c>
-      <c r="T1" s="20" t="s">
-        <v>1604</v>
-      </c>
-      <c r="U1" s="20" t="s">
-        <v>1604</v>
-      </c>
-      <c r="V1" s="20" t="s">
-        <v>1604</v>
-      </c>
-      <c r="W1" s="20" t="s">
-        <v>1604</v>
-      </c>
-      <c r="X1" s="18" t="s">
-        <v>1605</v>
       </c>
       <c r="Y1" s="20" t="s">
         <v>6</v>
@@ -46966,13 +46963,13 @@
         <v>22</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="E2" s="19" t="s">
         <v>24</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="G2" s="18" t="s">
         <v>20</v>
@@ -47026,7 +47023,7 @@
         <v>35</v>
       </c>
       <c r="X2" s="19" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="Y2" s="19" t="s">
         <v>36</v>
@@ -47861,7 +47858,7 @@
         <v>359</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X5" s="8"/>
       <c r="Y5" s="8"/>
@@ -47871,14 +47868,14 @@
       <c r="AC5" s="8"/>
       <c r="AD5" s="8"/>
       <c r="AE5" s="2" t="s">
+        <v>1610</v>
+      </c>
+      <c r="AF5" s="2" t="s">
         <v>1611</v>
-      </c>
-      <c r="AF5" s="2" t="s">
-        <v>1612</v>
       </c>
       <c r="AG5" s="8"/>
       <c r="AH5" s="9" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI5" s="8"/>
       <c r="AJ5" s="8"/>
@@ -47905,7 +47902,7 @@
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
@@ -47930,7 +47927,7 @@
         <v>359</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X6" s="13"/>
       <c r="Y6" s="13"/>
@@ -47942,14 +47939,14 @@
       </c>
       <c r="AD6" s="13"/>
       <c r="AE6" s="1" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="AF6" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG6" s="13"/>
       <c r="AH6" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI6" s="13"/>
       <c r="AJ6" s="13"/>
@@ -47999,7 +47996,7 @@
         <v>359</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X7" s="13"/>
       <c r="Y7" s="13"/>
@@ -48011,14 +48008,14 @@
         <v>127</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="AF7" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG7" s="13"/>
       <c r="AH7" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI7" s="13"/>
       <c r="AJ7" s="13"/>
@@ -48068,7 +48065,7 @@
         <v>359</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X8" s="13"/>
       <c r="Y8" s="13"/>
@@ -48078,14 +48075,14 @@
       <c r="AC8" s="13"/>
       <c r="AD8" s="13"/>
       <c r="AE8" s="1" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="AF8" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG8" s="13"/>
       <c r="AH8" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI8" s="13"/>
       <c r="AJ8" s="13"/>
@@ -48135,7 +48132,7 @@
         <v>359</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X9" s="13"/>
       <c r="Y9" s="13"/>
@@ -48145,14 +48142,14 @@
       <c r="AC9" s="13"/>
       <c r="AD9" s="13"/>
       <c r="AE9" s="1" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="AF9" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG9" s="13"/>
       <c r="AH9" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI9" s="13"/>
       <c r="AJ9" s="13"/>
@@ -48179,7 +48176,7 @@
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="O10" s="6"/>
       <c r="P10" s="6"/>
@@ -48204,7 +48201,7 @@
         <v>359</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X10" s="13"/>
       <c r="Y10" s="13"/>
@@ -48216,14 +48213,14 @@
       </c>
       <c r="AD10" s="13"/>
       <c r="AE10" s="1" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="AF10" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG10" s="13"/>
       <c r="AH10" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI10" s="13"/>
       <c r="AJ10" s="13"/>
@@ -48250,7 +48247,7 @@
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
@@ -48275,7 +48272,7 @@
         <v>359</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X11" s="13"/>
       <c r="Y11" s="13"/>
@@ -48287,14 +48284,14 @@
       </c>
       <c r="AD11" s="13"/>
       <c r="AE11" s="1" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="AF11" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG11" s="13"/>
       <c r="AH11" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI11" s="13"/>
       <c r="AJ11" s="13"/>
@@ -48344,7 +48341,7 @@
         <v>359</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X12" s="13"/>
       <c r="Y12" s="13"/>
@@ -48354,14 +48351,14 @@
       <c r="AC12" s="13"/>
       <c r="AD12" s="13"/>
       <c r="AE12" s="1" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="AF12" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG12" s="13"/>
       <c r="AH12" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI12" s="13"/>
       <c r="AJ12" s="13"/>
@@ -48411,7 +48408,7 @@
         <v>359</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X13" s="13"/>
       <c r="Y13" s="13"/>
@@ -48421,14 +48418,14 @@
       <c r="AC13" s="13"/>
       <c r="AD13" s="13"/>
       <c r="AE13" s="1" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="AF13" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG13" s="13"/>
       <c r="AH13" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI13" s="13"/>
       <c r="AJ13" s="13"/>
@@ -48455,7 +48452,7 @@
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
@@ -48480,7 +48477,7 @@
         <v>359</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X14" s="13"/>
       <c r="Y14" s="13"/>
@@ -48488,20 +48485,20 @@
       <c r="AA14" s="13"/>
       <c r="AB14" s="13"/>
       <c r="AC14" s="1" t="s">
+        <v>1624</v>
+      </c>
+      <c r="AD14" s="1" t="s">
+        <v>1624</v>
+      </c>
+      <c r="AE14" s="1" t="s">
         <v>1625</v>
-      </c>
-      <c r="AD14" s="1" t="s">
-        <v>1625</v>
-      </c>
-      <c r="AE14" s="1" t="s">
-        <v>1626</v>
       </c>
       <c r="AF14" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG14" s="13"/>
       <c r="AH14" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI14" s="13"/>
       <c r="AJ14" s="13"/>
@@ -48551,7 +48548,7 @@
         <v>359</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X15" s="13"/>
       <c r="Y15" s="13"/>
@@ -48560,17 +48557,17 @@
       <c r="AB15" s="13"/>
       <c r="AC15" s="13"/>
       <c r="AD15" s="1" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="AF15" s="1" t="s">
         <v>254</v>
       </c>
       <c r="AG15" s="13"/>
       <c r="AH15" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI15" s="13"/>
       <c r="AJ15" s="13"/>
@@ -48620,7 +48617,7 @@
         <v>359</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X16" s="13"/>
       <c r="Y16" s="13"/>
@@ -48630,14 +48627,14 @@
       <c r="AC16" s="13"/>
       <c r="AD16" s="13"/>
       <c r="AE16" s="1" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="AF16" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG16" s="13"/>
       <c r="AH16" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI16" s="13"/>
       <c r="AJ16" s="13"/>
@@ -48664,7 +48661,7 @@
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
       <c r="N17" s="4" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="O17" s="6"/>
       <c r="P17" s="6"/>
@@ -48689,7 +48686,7 @@
         <v>359</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X17" s="13"/>
       <c r="Y17" s="13"/>
@@ -48697,20 +48694,20 @@
       <c r="AA17" s="13"/>
       <c r="AB17" s="13"/>
       <c r="AC17" s="1" t="s">
+        <v>1629</v>
+      </c>
+      <c r="AD17" s="1" t="s">
         <v>1630</v>
       </c>
-      <c r="AD17" s="1" t="s">
+      <c r="AE17" s="1" t="s">
         <v>1631</v>
-      </c>
-      <c r="AE17" s="1" t="s">
-        <v>1632</v>
       </c>
       <c r="AF17" s="1" t="s">
         <v>254</v>
       </c>
       <c r="AG17" s="13"/>
       <c r="AH17" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI17" s="13"/>
       <c r="AJ17" s="13"/>
@@ -48737,7 +48734,7 @@
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
       <c r="N18" s="4" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="O18" s="6"/>
       <c r="P18" s="6"/>
@@ -48762,7 +48759,7 @@
         <v>359</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X18" s="13"/>
       <c r="Y18" s="13"/>
@@ -48770,20 +48767,20 @@
       <c r="AA18" s="13"/>
       <c r="AB18" s="13"/>
       <c r="AC18" s="1" t="s">
+        <v>1629</v>
+      </c>
+      <c r="AD18" s="1" t="s">
         <v>1630</v>
       </c>
-      <c r="AD18" s="1" t="s">
-        <v>1631</v>
-      </c>
       <c r="AE18" s="1" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="AF18" s="1" t="s">
         <v>254</v>
       </c>
       <c r="AG18" s="13"/>
       <c r="AH18" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI18" s="13"/>
       <c r="AJ18" s="13"/>
@@ -48810,7 +48807,7 @@
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
       <c r="N19" s="4" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="O19" s="6"/>
       <c r="P19" s="6"/>
@@ -48835,7 +48832,7 @@
         <v>359</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X19" s="13"/>
       <c r="Y19" s="13"/>
@@ -48849,14 +48846,14 @@
         <v>222</v>
       </c>
       <c r="AE19" s="1" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="AF19" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG19" s="13"/>
       <c r="AH19" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI19" s="13"/>
       <c r="AJ19" s="13"/>
@@ -48883,7 +48880,7 @@
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
       <c r="N20" s="4" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="O20" s="6"/>
       <c r="P20" s="6"/>
@@ -48908,7 +48905,7 @@
         <v>359</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X20" s="13"/>
       <c r="Y20" s="13"/>
@@ -48920,14 +48917,14 @@
       </c>
       <c r="AD20" s="13"/>
       <c r="AE20" s="1" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="AF20" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG20" s="13"/>
       <c r="AH20" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI20" s="13"/>
       <c r="AJ20" s="13"/>
@@ -48999,7 +48996,7 @@
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
       <c r="N22" s="4" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="O22" s="6"/>
       <c r="P22" s="6"/>
@@ -49024,7 +49021,7 @@
         <v>359</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X22" s="13"/>
       <c r="Y22" s="13"/>
@@ -49032,20 +49029,20 @@
       <c r="AA22" s="13"/>
       <c r="AB22" s="13"/>
       <c r="AC22" s="1" t="s">
+        <v>1629</v>
+      </c>
+      <c r="AD22" s="1" t="s">
         <v>1630</v>
       </c>
-      <c r="AD22" s="1" t="s">
-        <v>1631</v>
-      </c>
       <c r="AE22" s="1" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="AF22" s="1" t="s">
         <v>254</v>
       </c>
       <c r="AG22" s="13"/>
       <c r="AH22" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI22" s="13"/>
       <c r="AJ22" s="13"/>
@@ -49072,7 +49069,7 @@
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
       <c r="N23" s="4" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="O23" s="6"/>
       <c r="P23" s="6"/>
@@ -49097,7 +49094,7 @@
         <v>359</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X23" s="13"/>
       <c r="Y23" s="13"/>
@@ -49111,14 +49108,14 @@
         <v>127</v>
       </c>
       <c r="AE23" s="1" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="AF23" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG23" s="13"/>
       <c r="AH23" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI23" s="13"/>
       <c r="AJ23" s="13"/>
@@ -49145,7 +49142,7 @@
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
       <c r="N24" s="4" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="O24" s="6"/>
       <c r="P24" s="6"/>
@@ -49170,7 +49167,7 @@
         <v>359</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X24" s="13"/>
       <c r="Y24" s="13"/>
@@ -49182,14 +49179,14 @@
       </c>
       <c r="AD24" s="13"/>
       <c r="AE24" s="1" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="AF24" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG24" s="13"/>
       <c r="AH24" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI24" s="13"/>
       <c r="AJ24" s="13"/>
@@ -49239,7 +49236,7 @@
         <v>359</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X25" s="13"/>
       <c r="Y25" s="13"/>
@@ -49249,14 +49246,14 @@
       <c r="AC25" s="13"/>
       <c r="AD25" s="13"/>
       <c r="AE25" s="1" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="AF25" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG25" s="13"/>
       <c r="AH25" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI25" s="13"/>
       <c r="AJ25" s="13"/>
@@ -49283,7 +49280,7 @@
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
       <c r="N26" s="4" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="O26" s="6"/>
       <c r="P26" s="6"/>
@@ -49308,7 +49305,7 @@
         <v>359</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X26" s="13"/>
       <c r="Y26" s="13"/>
@@ -49320,14 +49317,14 @@
       </c>
       <c r="AD26" s="13"/>
       <c r="AE26" s="1" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="AF26" s="1" t="s">
         <v>714</v>
       </c>
       <c r="AG26" s="13"/>
       <c r="AH26" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI26" s="13"/>
       <c r="AJ26" s="13"/>
@@ -49354,7 +49351,7 @@
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
       <c r="N27" s="4" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="O27" s="6"/>
       <c r="P27" s="6"/>
@@ -49379,7 +49376,7 @@
         <v>359</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X27" s="13"/>
       <c r="Y27" s="13"/>
@@ -49393,14 +49390,14 @@
         <v>222</v>
       </c>
       <c r="AE27" s="1" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="AF27" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG27" s="13"/>
       <c r="AH27" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI27" s="13"/>
       <c r="AJ27" s="13"/>
@@ -49427,7 +49424,7 @@
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
       <c r="N28" s="4" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="O28" s="6"/>
       <c r="P28" s="6"/>
@@ -49452,7 +49449,7 @@
         <v>359</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X28" s="13"/>
       <c r="Y28" s="13"/>
@@ -49466,14 +49463,14 @@
         <v>222</v>
       </c>
       <c r="AE28" s="1" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="AF28" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG28" s="13"/>
       <c r="AH28" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI28" s="13"/>
       <c r="AJ28" s="13"/>
@@ -49500,7 +49497,7 @@
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
       <c r="N29" s="4" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="O29" s="6"/>
       <c r="P29" s="6"/>
@@ -49525,7 +49522,7 @@
         <v>359</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X29" s="13"/>
       <c r="Y29" s="13"/>
@@ -49539,14 +49536,14 @@
         <v>222</v>
       </c>
       <c r="AE29" s="1" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="AF29" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG29" s="13"/>
       <c r="AH29" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI29" s="13"/>
       <c r="AJ29" s="13"/>
@@ -49596,7 +49593,7 @@
         <v>359</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X30" s="13"/>
       <c r="Y30" s="13"/>
@@ -49605,17 +49602,17 @@
       <c r="AB30" s="13"/>
       <c r="AC30" s="13"/>
       <c r="AD30" s="1" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="AE30" s="1" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="AF30" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG30" s="13"/>
       <c r="AH30" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI30" s="13"/>
       <c r="AJ30" s="13"/>
@@ -49665,7 +49662,7 @@
         <v>359</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X31" s="13"/>
       <c r="Y31" s="13"/>
@@ -49674,17 +49671,17 @@
       <c r="AB31" s="13"/>
       <c r="AC31" s="13"/>
       <c r="AD31" s="1" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="AE31" s="1" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="AF31" s="1" t="s">
         <v>254</v>
       </c>
       <c r="AG31" s="13"/>
       <c r="AH31" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI31" s="13"/>
       <c r="AJ31" s="13"/>
@@ -49711,7 +49708,7 @@
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
       <c r="N32" s="4" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="O32" s="6"/>
       <c r="P32" s="6"/>
@@ -49736,7 +49733,7 @@
         <v>359</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X32" s="13"/>
       <c r="Y32" s="13"/>
@@ -49748,14 +49745,14 @@
       </c>
       <c r="AD32" s="13"/>
       <c r="AE32" s="1" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="AF32" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG32" s="13"/>
       <c r="AH32" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI32" s="13"/>
       <c r="AJ32" s="13"/>
@@ -49805,7 +49802,7 @@
         <v>359</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X33" s="13"/>
       <c r="Y33" s="13"/>
@@ -49815,14 +49812,14 @@
       <c r="AC33" s="13"/>
       <c r="AD33" s="13"/>
       <c r="AE33" s="1" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="AF33" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG33" s="13"/>
       <c r="AH33" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI33" s="13"/>
       <c r="AJ33" s="13"/>
@@ -49849,7 +49846,7 @@
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
       <c r="N34" s="4" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="O34" s="6"/>
       <c r="P34" s="6"/>
@@ -49874,7 +49871,7 @@
         <v>359</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X34" s="13"/>
       <c r="Y34" s="13"/>
@@ -49886,14 +49883,14 @@
       </c>
       <c r="AD34" s="13"/>
       <c r="AE34" s="1" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="AF34" s="1" t="s">
         <v>714</v>
       </c>
       <c r="AG34" s="13"/>
       <c r="AH34" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI34" s="13"/>
       <c r="AJ34" s="13"/>
@@ -49943,7 +49940,7 @@
         <v>359</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X35" s="13"/>
       <c r="Y35" s="13"/>
@@ -49955,14 +49952,14 @@
         <v>127</v>
       </c>
       <c r="AE35" s="1" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="AF35" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG35" s="13"/>
       <c r="AH35" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI35" s="13"/>
       <c r="AJ35" s="13"/>
@@ -50012,7 +50009,7 @@
         <v>359</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X36" s="13"/>
       <c r="Y36" s="13"/>
@@ -50022,14 +50019,14 @@
       <c r="AC36" s="13"/>
       <c r="AD36" s="13"/>
       <c r="AE36" s="1" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="AF36" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG36" s="13"/>
       <c r="AH36" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI36" s="13"/>
       <c r="AJ36" s="13"/>
@@ -50056,7 +50053,7 @@
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
       <c r="N37" s="4" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="O37" s="6"/>
       <c r="P37" s="6"/>
@@ -50081,7 +50078,7 @@
         <v>359</v>
       </c>
       <c r="W37" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X37" s="13"/>
       <c r="Y37" s="13"/>
@@ -50089,20 +50086,20 @@
       <c r="AA37" s="13"/>
       <c r="AB37" s="13"/>
       <c r="AC37" s="1" t="s">
+        <v>1629</v>
+      </c>
+      <c r="AD37" s="1" t="s">
         <v>1630</v>
       </c>
-      <c r="AD37" s="1" t="s">
-        <v>1631</v>
-      </c>
       <c r="AE37" s="1" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="AF37" s="1" t="s">
         <v>254</v>
       </c>
       <c r="AG37" s="13"/>
       <c r="AH37" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI37" s="13"/>
       <c r="AJ37" s="13"/>
@@ -50129,7 +50126,7 @@
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
       <c r="N38" s="4" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="O38" s="6"/>
       <c r="P38" s="6"/>
@@ -50154,7 +50151,7 @@
         <v>359</v>
       </c>
       <c r="W38" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X38" s="13"/>
       <c r="Y38" s="13"/>
@@ -50162,20 +50159,20 @@
       <c r="AA38" s="13"/>
       <c r="AB38" s="13"/>
       <c r="AC38" s="1" t="s">
+        <v>1629</v>
+      </c>
+      <c r="AD38" s="1" t="s">
         <v>1630</v>
       </c>
-      <c r="AD38" s="1" t="s">
-        <v>1631</v>
-      </c>
       <c r="AE38" s="1" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="AF38" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG38" s="13"/>
       <c r="AH38" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI38" s="13"/>
       <c r="AJ38" s="13"/>
@@ -50202,7 +50199,7 @@
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
       <c r="N39" s="4" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="O39" s="6"/>
       <c r="P39" s="6"/>
@@ -50227,7 +50224,7 @@
         <v>359</v>
       </c>
       <c r="W39" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X39" s="13"/>
       <c r="Y39" s="13"/>
@@ -50235,20 +50232,20 @@
       <c r="AA39" s="13"/>
       <c r="AB39" s="13"/>
       <c r="AC39" s="1" t="s">
+        <v>1629</v>
+      </c>
+      <c r="AD39" s="1" t="s">
         <v>1630</v>
       </c>
-      <c r="AD39" s="1" t="s">
-        <v>1631</v>
-      </c>
       <c r="AE39" s="1" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="AF39" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG39" s="13"/>
       <c r="AH39" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI39" s="13"/>
       <c r="AJ39" s="13"/>
@@ -50275,7 +50272,7 @@
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
       <c r="N40" s="4" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="O40" s="6"/>
       <c r="P40" s="6"/>
@@ -50300,7 +50297,7 @@
         <v>359</v>
       </c>
       <c r="W40" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X40" s="13"/>
       <c r="Y40" s="13"/>
@@ -50308,18 +50305,18 @@
       <c r="AA40" s="13"/>
       <c r="AB40" s="13"/>
       <c r="AC40" s="1" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="AD40" s="13"/>
       <c r="AE40" s="1" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="AF40" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG40" s="13"/>
       <c r="AH40" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI40" s="13"/>
       <c r="AJ40" s="13"/>
@@ -50346,7 +50343,7 @@
       <c r="L41" s="4"/>
       <c r="M41" s="4"/>
       <c r="N41" s="4" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="O41" s="6"/>
       <c r="P41" s="6"/>
@@ -50371,7 +50368,7 @@
         <v>359</v>
       </c>
       <c r="W41" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X41" s="13"/>
       <c r="Y41" s="13"/>
@@ -50385,14 +50382,14 @@
         <v>127</v>
       </c>
       <c r="AE41" s="1" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="AF41" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG41" s="13"/>
       <c r="AH41" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI41" s="13"/>
       <c r="AJ41" s="13"/>
@@ -50442,7 +50439,7 @@
         <v>359</v>
       </c>
       <c r="W42" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X42" s="13"/>
       <c r="Y42" s="13"/>
@@ -50452,14 +50449,14 @@
       <c r="AC42" s="13"/>
       <c r="AD42" s="13"/>
       <c r="AE42" s="1" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="AF42" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG42" s="13"/>
       <c r="AH42" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI42" s="13"/>
       <c r="AJ42" s="13"/>
@@ -50486,7 +50483,7 @@
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
       <c r="N43" s="4" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="O43" s="6"/>
       <c r="P43" s="6"/>
@@ -50511,7 +50508,7 @@
         <v>359</v>
       </c>
       <c r="W43" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X43" s="13"/>
       <c r="Y43" s="13"/>
@@ -50523,14 +50520,14 @@
       </c>
       <c r="AD43" s="13"/>
       <c r="AE43" s="1" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="AF43" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG43" s="13"/>
       <c r="AH43" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI43" s="13"/>
       <c r="AJ43" s="13"/>
@@ -50557,7 +50554,7 @@
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
       <c r="N44" s="4" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="O44" s="6"/>
       <c r="P44" s="6"/>
@@ -50582,7 +50579,7 @@
         <v>359</v>
       </c>
       <c r="W44" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X44" s="13"/>
       <c r="Y44" s="13"/>
@@ -50594,14 +50591,14 @@
       </c>
       <c r="AD44" s="13"/>
       <c r="AE44" s="1" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="AF44" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG44" s="13"/>
       <c r="AH44" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI44" s="13"/>
       <c r="AJ44" s="13"/>
@@ -50628,7 +50625,7 @@
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
       <c r="N45" s="4" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="O45" s="6"/>
       <c r="P45" s="6"/>
@@ -50653,7 +50650,7 @@
         <v>359</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X45" s="13"/>
       <c r="Y45" s="13"/>
@@ -50665,14 +50662,14 @@
       </c>
       <c r="AD45" s="13"/>
       <c r="AE45" s="1" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="AF45" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG45" s="13"/>
       <c r="AH45" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI45" s="13"/>
       <c r="AJ45" s="13"/>
@@ -50722,7 +50719,7 @@
         <v>359</v>
       </c>
       <c r="W46" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X46" s="13"/>
       <c r="Y46" s="13"/>
@@ -50732,14 +50729,14 @@
       <c r="AC46" s="13"/>
       <c r="AD46" s="13"/>
       <c r="AE46" s="1" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="AF46" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG46" s="13"/>
       <c r="AH46" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI46" s="13"/>
       <c r="AJ46" s="13"/>
@@ -50766,7 +50763,7 @@
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
       <c r="N47" s="4" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="O47" s="6"/>
       <c r="P47" s="6"/>
@@ -50791,7 +50788,7 @@
         <v>359</v>
       </c>
       <c r="W47" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X47" s="13"/>
       <c r="Y47" s="13"/>
@@ -50803,14 +50800,14 @@
       </c>
       <c r="AD47" s="13"/>
       <c r="AE47" s="1" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="AF47" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG47" s="13"/>
       <c r="AH47" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI47" s="13"/>
       <c r="AJ47" s="13"/>
@@ -50860,7 +50857,7 @@
         <v>359</v>
       </c>
       <c r="W48" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X48" s="13"/>
       <c r="Y48" s="13"/>
@@ -50870,14 +50867,14 @@
       <c r="AC48" s="13"/>
       <c r="AD48" s="13"/>
       <c r="AE48" s="1" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="AF48" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG48" s="13"/>
       <c r="AH48" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI48" s="13"/>
       <c r="AJ48" s="13"/>
@@ -50904,7 +50901,7 @@
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
       <c r="N49" s="4" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="O49" s="6"/>
       <c r="P49" s="6"/>
@@ -50929,7 +50926,7 @@
         <v>359</v>
       </c>
       <c r="W49" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X49" s="13"/>
       <c r="Y49" s="13"/>
@@ -50941,14 +50938,14 @@
       </c>
       <c r="AD49" s="13"/>
       <c r="AE49" s="1" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="AF49" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG49" s="13"/>
       <c r="AH49" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI49" s="13"/>
       <c r="AJ49" s="13"/>
@@ -50998,7 +50995,7 @@
         <v>359</v>
       </c>
       <c r="W50" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X50" s="13"/>
       <c r="Y50" s="13"/>
@@ -51008,14 +51005,14 @@
       <c r="AC50" s="13"/>
       <c r="AD50" s="13"/>
       <c r="AE50" s="1" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="AF50" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG50" s="13"/>
       <c r="AH50" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI50" s="13"/>
       <c r="AJ50" s="13"/>
@@ -51065,7 +51062,7 @@
         <v>359</v>
       </c>
       <c r="W51" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X51" s="13"/>
       <c r="Y51" s="13"/>
@@ -51074,17 +51071,17 @@
       <c r="AB51" s="13"/>
       <c r="AC51" s="13"/>
       <c r="AD51" s="1" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="AE51" s="1" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="AF51" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG51" s="13"/>
       <c r="AH51" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI51" s="13"/>
       <c r="AJ51" s="13"/>
@@ -51134,7 +51131,7 @@
         <v>359</v>
       </c>
       <c r="W52" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X52" s="13"/>
       <c r="Y52" s="13"/>
@@ -51143,17 +51140,17 @@
       <c r="AB52" s="13"/>
       <c r="AC52" s="13"/>
       <c r="AD52" s="1" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="AE52" s="1" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="AF52" s="1" t="s">
         <v>254</v>
       </c>
       <c r="AG52" s="13"/>
       <c r="AH52" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI52" s="13"/>
       <c r="AJ52" s="13"/>
@@ -51180,7 +51177,7 @@
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
       <c r="N53" s="4" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="O53" s="6"/>
       <c r="P53" s="6"/>
@@ -51205,7 +51202,7 @@
         <v>359</v>
       </c>
       <c r="W53" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X53" s="13"/>
       <c r="Y53" s="13"/>
@@ -51219,14 +51216,14 @@
         <v>127</v>
       </c>
       <c r="AE53" s="1" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="AF53" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG53" s="13"/>
       <c r="AH53" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI53" s="13"/>
       <c r="AJ53" s="13"/>
@@ -51276,7 +51273,7 @@
         <v>359</v>
       </c>
       <c r="W54" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X54" s="13"/>
       <c r="Y54" s="13"/>
@@ -51288,14 +51285,14 @@
         <v>127</v>
       </c>
       <c r="AE54" s="1" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="AF54" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG54" s="13"/>
       <c r="AH54" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI54" s="13"/>
       <c r="AJ54" s="13"/>
@@ -51322,7 +51319,7 @@
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
       <c r="N55" s="4" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="O55" s="6"/>
       <c r="P55" s="6"/>
@@ -51347,7 +51344,7 @@
         <v>359</v>
       </c>
       <c r="W55" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X55" s="13"/>
       <c r="Y55" s="13"/>
@@ -51361,14 +51358,14 @@
         <v>127</v>
       </c>
       <c r="AE55" s="1" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="AF55" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG55" s="13"/>
       <c r="AH55" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI55" s="13"/>
       <c r="AJ55" s="13"/>
@@ -51442,7 +51439,7 @@
         <v>359</v>
       </c>
       <c r="W57" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X57" s="13"/>
       <c r="Y57" s="13"/>
@@ -51454,14 +51451,14 @@
         <v>127</v>
       </c>
       <c r="AE57" s="1" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="AF57" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG57" s="13"/>
       <c r="AH57" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI57" s="13"/>
       <c r="AJ57" s="13"/>
@@ -51511,7 +51508,7 @@
         <v>359</v>
       </c>
       <c r="W58" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X58" s="13"/>
       <c r="Y58" s="13"/>
@@ -51523,14 +51520,14 @@
         <v>127</v>
       </c>
       <c r="AE58" s="1" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="AF58" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG58" s="13"/>
       <c r="AH58" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI58" s="13"/>
       <c r="AJ58" s="13"/>
@@ -51557,7 +51554,7 @@
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
       <c r="N59" s="4" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="O59" s="6"/>
       <c r="P59" s="6"/>
@@ -51582,7 +51579,7 @@
         <v>359</v>
       </c>
       <c r="W59" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X59" s="13"/>
       <c r="Y59" s="13"/>
@@ -51590,20 +51587,20 @@
       <c r="AA59" s="13"/>
       <c r="AB59" s="13"/>
       <c r="AC59" s="1" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="AD59" s="1" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="AE59" s="1" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="AF59" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG59" s="13"/>
       <c r="AH59" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI59" s="13"/>
       <c r="AJ59" s="13"/>
@@ -51653,7 +51650,7 @@
         <v>359</v>
       </c>
       <c r="W60" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X60" s="13"/>
       <c r="Y60" s="13"/>
@@ -51662,17 +51659,17 @@
       <c r="AB60" s="13"/>
       <c r="AC60" s="13"/>
       <c r="AD60" s="1" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="AE60" s="1" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="AF60" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG60" s="13"/>
       <c r="AH60" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI60" s="13"/>
       <c r="AJ60" s="13"/>
@@ -51699,7 +51696,7 @@
       <c r="L61" s="4"/>
       <c r="M61" s="4"/>
       <c r="N61" s="4" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="O61" s="6"/>
       <c r="P61" s="6"/>
@@ -51724,7 +51721,7 @@
         <v>359</v>
       </c>
       <c r="W61" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X61" s="13"/>
       <c r="Y61" s="13"/>
@@ -51736,14 +51733,14 @@
       </c>
       <c r="AD61" s="13"/>
       <c r="AE61" s="1" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="AF61" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG61" s="13"/>
       <c r="AH61" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI61" s="13"/>
       <c r="AJ61" s="13"/>
@@ -51793,7 +51790,7 @@
         <v>359</v>
       </c>
       <c r="W62" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X62" s="13"/>
       <c r="Y62" s="13"/>
@@ -51803,14 +51800,14 @@
       <c r="AC62" s="13"/>
       <c r="AD62" s="13"/>
       <c r="AE62" s="1" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="AF62" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG62" s="13"/>
       <c r="AH62" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI62" s="13"/>
       <c r="AJ62" s="13"/>
@@ -51837,7 +51834,7 @@
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
       <c r="N63" s="4" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="O63" s="6"/>
       <c r="P63" s="6"/>
@@ -51862,7 +51859,7 @@
         <v>359</v>
       </c>
       <c r="W63" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X63" s="13"/>
       <c r="Y63" s="13"/>
@@ -51874,14 +51871,14 @@
       </c>
       <c r="AD63" s="13"/>
       <c r="AE63" s="1" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="AF63" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG63" s="13"/>
       <c r="AH63" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI63" s="13"/>
       <c r="AJ63" s="13"/>
@@ -51931,7 +51928,7 @@
         <v>359</v>
       </c>
       <c r="W64" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X64" s="13"/>
       <c r="Y64" s="13"/>
@@ -51941,14 +51938,14 @@
       <c r="AC64" s="13"/>
       <c r="AD64" s="13"/>
       <c r="AE64" s="1" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="AF64" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG64" s="13"/>
       <c r="AH64" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI64" s="13"/>
       <c r="AJ64" s="13"/>
@@ -51998,7 +51995,7 @@
         <v>359</v>
       </c>
       <c r="W65" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X65" s="13"/>
       <c r="Y65" s="13"/>
@@ -52007,17 +52004,17 @@
       <c r="AB65" s="13"/>
       <c r="AC65" s="13"/>
       <c r="AD65" s="1" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="AE65" s="1" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="AF65" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG65" s="13"/>
       <c r="AH65" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI65" s="13"/>
       <c r="AJ65" s="13"/>
@@ -52067,7 +52064,7 @@
         <v>359</v>
       </c>
       <c r="W66" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X66" s="13"/>
       <c r="Y66" s="13"/>
@@ -52077,14 +52074,14 @@
       <c r="AC66" s="13"/>
       <c r="AD66" s="13"/>
       <c r="AE66" s="1" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="AF66" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG66" s="13"/>
       <c r="AH66" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI66" s="13"/>
       <c r="AJ66" s="13"/>
@@ -52158,7 +52155,7 @@
         <v>359</v>
       </c>
       <c r="W68" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X68" s="13"/>
       <c r="Y68" s="13"/>
@@ -52175,7 +52172,7 @@
       </c>
       <c r="AG68" s="13"/>
       <c r="AH68" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI68" s="13"/>
       <c r="AJ68" s="13"/>
@@ -52202,7 +52199,7 @@
       <c r="L69" s="4"/>
       <c r="M69" s="4"/>
       <c r="N69" s="4" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="O69" s="6"/>
       <c r="P69" s="6"/>
@@ -52227,7 +52224,7 @@
         <v>359</v>
       </c>
       <c r="W69" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X69" s="13"/>
       <c r="Y69" s="13"/>
@@ -52239,14 +52236,14 @@
       </c>
       <c r="AD69" s="13"/>
       <c r="AE69" s="1" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="AF69" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG69" s="13"/>
       <c r="AH69" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI69" s="13"/>
       <c r="AJ69" s="13"/>
@@ -52273,7 +52270,7 @@
       <c r="L70" s="4"/>
       <c r="M70" s="4"/>
       <c r="N70" s="4" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="O70" s="6"/>
       <c r="P70" s="6"/>
@@ -52298,7 +52295,7 @@
         <v>359</v>
       </c>
       <c r="W70" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X70" s="13"/>
       <c r="Y70" s="13"/>
@@ -52312,14 +52309,14 @@
         <v>127</v>
       </c>
       <c r="AE70" s="1" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="AF70" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG70" s="13"/>
       <c r="AH70" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI70" s="13"/>
       <c r="AJ70" s="13"/>
@@ -52346,7 +52343,7 @@
       <c r="L71" s="4"/>
       <c r="M71" s="4"/>
       <c r="N71" s="4" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="O71" s="6"/>
       <c r="P71" s="6"/>
@@ -52371,7 +52368,7 @@
         <v>359</v>
       </c>
       <c r="W71" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X71" s="13"/>
       <c r="Y71" s="13"/>
@@ -52383,14 +52380,14 @@
       </c>
       <c r="AD71" s="13"/>
       <c r="AE71" s="1" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="AF71" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG71" s="13"/>
       <c r="AH71" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI71" s="13"/>
       <c r="AJ71" s="13"/>
@@ -52417,7 +52414,7 @@
       <c r="L72" s="4"/>
       <c r="M72" s="4"/>
       <c r="N72" s="4" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="O72" s="6"/>
       <c r="P72" s="6"/>
@@ -52442,7 +52439,7 @@
         <v>359</v>
       </c>
       <c r="W72" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X72" s="13"/>
       <c r="Y72" s="13"/>
@@ -52454,14 +52451,14 @@
       </c>
       <c r="AD72" s="13"/>
       <c r="AE72" s="1" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="AF72" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG72" s="13"/>
       <c r="AH72" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI72" s="13"/>
       <c r="AJ72" s="13"/>
@@ -52511,7 +52508,7 @@
         <v>359</v>
       </c>
       <c r="W73" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X73" s="13"/>
       <c r="Y73" s="13"/>
@@ -52520,17 +52517,17 @@
       <c r="AB73" s="13"/>
       <c r="AC73" s="13"/>
       <c r="AD73" s="1" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="AE73" s="1" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="AF73" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG73" s="13"/>
       <c r="AH73" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI73" s="13"/>
       <c r="AJ73" s="13"/>
@@ -52557,7 +52554,7 @@
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
       <c r="N74" s="4" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="O74" s="6"/>
       <c r="P74" s="6"/>
@@ -52582,7 +52579,7 @@
         <v>359</v>
       </c>
       <c r="W74" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X74" s="13"/>
       <c r="Y74" s="13"/>
@@ -52593,17 +52590,17 @@
         <v>712</v>
       </c>
       <c r="AD74" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="AE74" s="1" t="s">
         <v>1716</v>
-      </c>
-      <c r="AE74" s="1" t="s">
-        <v>1717</v>
       </c>
       <c r="AF74" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG74" s="13"/>
       <c r="AH74" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI74" s="13"/>
       <c r="AJ74" s="13"/>
@@ -52653,7 +52650,7 @@
         <v>359</v>
       </c>
       <c r="W75" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X75" s="13"/>
       <c r="Y75" s="13"/>
@@ -52663,14 +52660,14 @@
       <c r="AC75" s="13"/>
       <c r="AD75" s="13"/>
       <c r="AE75" s="1" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="AF75" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG75" s="13"/>
       <c r="AH75" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI75" s="13"/>
       <c r="AJ75" s="13"/>
@@ -52720,7 +52717,7 @@
         <v>359</v>
       </c>
       <c r="W76" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X76" s="13"/>
       <c r="Y76" s="13"/>
@@ -52730,14 +52727,14 @@
       <c r="AC76" s="13"/>
       <c r="AD76" s="13"/>
       <c r="AE76" s="1" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="AF76" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG76" s="13"/>
       <c r="AH76" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI76" s="13"/>
       <c r="AJ76" s="13"/>
@@ -52787,7 +52784,7 @@
         <v>359</v>
       </c>
       <c r="W77" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X77" s="13"/>
       <c r="Y77" s="13"/>
@@ -52796,17 +52793,17 @@
       <c r="AB77" s="13"/>
       <c r="AC77" s="13"/>
       <c r="AD77" s="1" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="AE77" s="1" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="AF77" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG77" s="13"/>
       <c r="AH77" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI77" s="13"/>
       <c r="AJ77" s="13"/>
@@ -52856,7 +52853,7 @@
         <v>359</v>
       </c>
       <c r="W78" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X78" s="13"/>
       <c r="Y78" s="13"/>
@@ -52865,17 +52862,17 @@
       <c r="AB78" s="13"/>
       <c r="AC78" s="13"/>
       <c r="AD78" s="1" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="AE78" s="1" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="AF78" s="1" t="s">
         <v>254</v>
       </c>
       <c r="AG78" s="13"/>
       <c r="AH78" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI78" s="13"/>
       <c r="AJ78" s="13"/>
@@ -52902,7 +52899,7 @@
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
       <c r="N79" s="4" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="O79" s="6"/>
       <c r="P79" s="6"/>
@@ -52927,7 +52924,7 @@
         <v>359</v>
       </c>
       <c r="W79" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X79" s="13"/>
       <c r="Y79" s="13"/>
@@ -52939,14 +52936,14 @@
       </c>
       <c r="AD79" s="13"/>
       <c r="AE79" s="1" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="AF79" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG79" s="13"/>
       <c r="AH79" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI79" s="13"/>
       <c r="AJ79" s="13"/>
@@ -52973,7 +52970,7 @@
       <c r="L80" s="4"/>
       <c r="M80" s="4"/>
       <c r="N80" s="4" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="O80" s="6"/>
       <c r="P80" s="6"/>
@@ -52998,7 +52995,7 @@
         <v>359</v>
       </c>
       <c r="W80" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X80" s="13"/>
       <c r="Y80" s="13"/>
@@ -53010,14 +53007,14 @@
       </c>
       <c r="AD80" s="13"/>
       <c r="AE80" s="1" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="AF80" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG80" s="13"/>
       <c r="AH80" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI80" s="13"/>
       <c r="AJ80" s="13"/>
@@ -53067,7 +53064,7 @@
         <v>359</v>
       </c>
       <c r="W81" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X81" s="13"/>
       <c r="Y81" s="13"/>
@@ -53076,17 +53073,17 @@
       <c r="AB81" s="13"/>
       <c r="AC81" s="13"/>
       <c r="AD81" s="1" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="AE81" s="1" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="AF81" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG81" s="13"/>
       <c r="AH81" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI81" s="13"/>
       <c r="AJ81" s="13"/>
@@ -53113,7 +53110,7 @@
       <c r="L82" s="4"/>
       <c r="M82" s="4"/>
       <c r="N82" s="4" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="O82" s="6"/>
       <c r="P82" s="6"/>
@@ -53138,7 +53135,7 @@
         <v>359</v>
       </c>
       <c r="W82" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X82" s="13"/>
       <c r="Y82" s="13"/>
@@ -53150,14 +53147,14 @@
       </c>
       <c r="AD82" s="13"/>
       <c r="AE82" s="1" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="AF82" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG82" s="13"/>
       <c r="AH82" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI82" s="13"/>
       <c r="AJ82" s="13"/>
@@ -53207,7 +53204,7 @@
         <v>359</v>
       </c>
       <c r="W83" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X83" s="13"/>
       <c r="Y83" s="13"/>
@@ -53217,14 +53214,14 @@
       <c r="AC83" s="13"/>
       <c r="AD83" s="13"/>
       <c r="AE83" s="1" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="AF83" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG83" s="13"/>
       <c r="AH83" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI83" s="13"/>
       <c r="AJ83" s="13"/>
@@ -53296,7 +53293,7 @@
       <c r="L85" s="4"/>
       <c r="M85" s="4"/>
       <c r="N85" s="4" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="O85" s="6"/>
       <c r="P85" s="6"/>
@@ -53321,7 +53318,7 @@
         <v>359</v>
       </c>
       <c r="W85" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X85" s="13"/>
       <c r="Y85" s="13"/>
@@ -53335,14 +53332,14 @@
         <v>222</v>
       </c>
       <c r="AE85" s="1" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="AF85" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG85" s="13"/>
       <c r="AH85" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI85" s="13"/>
       <c r="AJ85" s="13"/>
@@ -53392,7 +53389,7 @@
         <v>359</v>
       </c>
       <c r="W86" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X86" s="13"/>
       <c r="Y86" s="13"/>
@@ -53401,17 +53398,17 @@
       <c r="AB86" s="13"/>
       <c r="AC86" s="13"/>
       <c r="AD86" s="1" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="AE86" s="1" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="AF86" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG86" s="13"/>
       <c r="AH86" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI86" s="13"/>
       <c r="AJ86" s="13"/>
@@ -53461,7 +53458,7 @@
         <v>359</v>
       </c>
       <c r="W87" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X87" s="13"/>
       <c r="Y87" s="13"/>
@@ -53470,17 +53467,17 @@
       <c r="AB87" s="13"/>
       <c r="AC87" s="13"/>
       <c r="AD87" s="1" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="AE87" s="1" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="AF87" s="1" t="s">
         <v>254</v>
       </c>
       <c r="AG87" s="13"/>
       <c r="AH87" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI87" s="13"/>
       <c r="AJ87" s="13"/>
@@ -53507,7 +53504,7 @@
       <c r="L88" s="4"/>
       <c r="M88" s="4"/>
       <c r="N88" s="4" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="O88" s="6"/>
       <c r="P88" s="6"/>
@@ -53532,7 +53529,7 @@
         <v>359</v>
       </c>
       <c r="W88" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X88" s="13"/>
       <c r="Y88" s="13"/>
@@ -53543,7 +53540,7 @@
         <v>712</v>
       </c>
       <c r="AD88" s="1" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="AE88" s="1" t="s">
         <v>64</v>
@@ -53553,7 +53550,7 @@
       </c>
       <c r="AG88" s="13"/>
       <c r="AH88" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI88" s="13"/>
       <c r="AJ88" s="13"/>
@@ -53603,7 +53600,7 @@
         <v>359</v>
       </c>
       <c r="W89" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X89" s="13"/>
       <c r="Y89" s="13"/>
@@ -53620,7 +53617,7 @@
       </c>
       <c r="AG89" s="13"/>
       <c r="AH89" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI89" s="13"/>
       <c r="AJ89" s="13"/>
@@ -53670,7 +53667,7 @@
         <v>359</v>
       </c>
       <c r="W90" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X90" s="13"/>
       <c r="Y90" s="13"/>
@@ -53680,14 +53677,14 @@
       <c r="AC90" s="13"/>
       <c r="AD90" s="13"/>
       <c r="AE90" s="1" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="AF90" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG90" s="13"/>
       <c r="AH90" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI90" s="13"/>
       <c r="AJ90" s="13"/>
@@ -53737,7 +53734,7 @@
         <v>359</v>
       </c>
       <c r="W91" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X91" s="13"/>
       <c r="Y91" s="13"/>
@@ -53746,17 +53743,17 @@
       <c r="AB91" s="13"/>
       <c r="AC91" s="13"/>
       <c r="AD91" s="1" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="AE91" s="1" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="AF91" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG91" s="13"/>
       <c r="AH91" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI91" s="13"/>
       <c r="AJ91" s="13"/>
@@ -53806,7 +53803,7 @@
         <v>359</v>
       </c>
       <c r="W92" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X92" s="13"/>
       <c r="Y92" s="13"/>
@@ -53816,14 +53813,14 @@
       <c r="AC92" s="13"/>
       <c r="AD92" s="13"/>
       <c r="AE92" s="1" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="AF92" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG92" s="13"/>
       <c r="AH92" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI92" s="13"/>
       <c r="AJ92" s="13"/>
@@ -53850,7 +53847,7 @@
       <c r="L93" s="4"/>
       <c r="M93" s="4"/>
       <c r="N93" s="4" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="O93" s="6"/>
       <c r="P93" s="6"/>
@@ -53875,7 +53872,7 @@
         <v>359</v>
       </c>
       <c r="W93" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X93" s="13"/>
       <c r="Y93" s="13"/>
@@ -53883,20 +53880,20 @@
       <c r="AA93" s="13"/>
       <c r="AB93" s="13"/>
       <c r="AC93" s="1" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="AD93" s="1" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="AE93" s="1" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="AF93" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG93" s="13"/>
       <c r="AH93" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI93" s="13"/>
       <c r="AJ93" s="13"/>
@@ -53946,7 +53943,7 @@
         <v>359</v>
       </c>
       <c r="W94" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X94" s="13"/>
       <c r="Y94" s="13"/>
@@ -53956,14 +53953,14 @@
       <c r="AC94" s="13"/>
       <c r="AD94" s="13"/>
       <c r="AE94" s="1" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="AF94" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG94" s="13"/>
       <c r="AH94" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI94" s="13"/>
       <c r="AJ94" s="13"/>
@@ -53990,7 +53987,7 @@
       <c r="L95" s="4"/>
       <c r="M95" s="4"/>
       <c r="N95" s="4" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="O95" s="6"/>
       <c r="P95" s="6"/>
@@ -54015,7 +54012,7 @@
         <v>359</v>
       </c>
       <c r="W95" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X95" s="13"/>
       <c r="Y95" s="13"/>
@@ -54029,14 +54026,14 @@
         <v>127</v>
       </c>
       <c r="AE95" s="1" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AF95" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG95" s="13"/>
       <c r="AH95" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI95" s="13"/>
       <c r="AJ95" s="13"/>
@@ -54088,7 +54085,7 @@
         <v>359</v>
       </c>
       <c r="W96" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X96" s="13"/>
       <c r="Y96" s="13"/>
@@ -54100,14 +54097,14 @@
       </c>
       <c r="AD96" s="13"/>
       <c r="AE96" s="1" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="AF96" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG96" s="13"/>
       <c r="AH96" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI96" s="13"/>
       <c r="AJ96" s="13"/>
@@ -54157,7 +54154,7 @@
         <v>359</v>
       </c>
       <c r="W97" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X97" s="13"/>
       <c r="Y97" s="13"/>
@@ -54169,14 +54166,14 @@
         <v>222</v>
       </c>
       <c r="AE97" s="1" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="AF97" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG97" s="13"/>
       <c r="AH97" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI97" s="13"/>
       <c r="AJ97" s="13"/>
@@ -54203,7 +54200,7 @@
       <c r="L98" s="4"/>
       <c r="M98" s="4"/>
       <c r="N98" s="4" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="O98" s="6"/>
       <c r="P98" s="6"/>
@@ -54228,7 +54225,7 @@
         <v>359</v>
       </c>
       <c r="W98" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X98" s="13"/>
       <c r="Y98" s="13"/>
@@ -54240,14 +54237,14 @@
       </c>
       <c r="AD98" s="13"/>
       <c r="AE98" s="1" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="AF98" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG98" s="13"/>
       <c r="AH98" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI98" s="13"/>
       <c r="AJ98" s="13"/>
@@ -54274,7 +54271,7 @@
       <c r="L99" s="4"/>
       <c r="M99" s="4"/>
       <c r="N99" s="4" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="O99" s="6"/>
       <c r="P99" s="6"/>
@@ -54299,7 +54296,7 @@
         <v>359</v>
       </c>
       <c r="W99" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X99" s="13"/>
       <c r="Y99" s="13"/>
@@ -54311,14 +54308,14 @@
       </c>
       <c r="AD99" s="13"/>
       <c r="AE99" s="1" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="AF99" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG99" s="13"/>
       <c r="AH99" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI99" s="13"/>
       <c r="AJ99" s="13"/>
@@ -54368,7 +54365,7 @@
         <v>359</v>
       </c>
       <c r="W100" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X100" s="13"/>
       <c r="Y100" s="13"/>
@@ -54378,14 +54375,14 @@
       <c r="AC100" s="13"/>
       <c r="AD100" s="13"/>
       <c r="AE100" s="1" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="AF100" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG100" s="13"/>
       <c r="AH100" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI100" s="13"/>
       <c r="AJ100" s="13"/>
@@ -54412,7 +54409,7 @@
       <c r="L101" s="4"/>
       <c r="M101" s="4"/>
       <c r="N101" s="4" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="O101" s="6"/>
       <c r="P101" s="6"/>
@@ -54437,7 +54434,7 @@
         <v>359</v>
       </c>
       <c r="W101" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X101" s="13"/>
       <c r="Y101" s="13"/>
@@ -54451,14 +54448,14 @@
         <v>127</v>
       </c>
       <c r="AE101" s="1" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="AF101" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG101" s="13"/>
       <c r="AH101" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI101" s="13"/>
       <c r="AJ101" s="13"/>
@@ -54510,7 +54507,7 @@
         <v>359</v>
       </c>
       <c r="W102" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X102" s="13"/>
       <c r="Y102" s="13"/>
@@ -54529,7 +54526,7 @@
       </c>
       <c r="AG102" s="13"/>
       <c r="AH102" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI102" s="13"/>
       <c r="AJ102" s="13"/>
@@ -54556,7 +54553,7 @@
       <c r="L103" s="4"/>
       <c r="M103" s="4"/>
       <c r="N103" s="4" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="O103" s="6"/>
       <c r="P103" s="6"/>
@@ -54581,7 +54578,7 @@
         <v>359</v>
       </c>
       <c r="W103" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X103" s="13"/>
       <c r="Y103" s="13"/>
@@ -54593,14 +54590,14 @@
       </c>
       <c r="AD103" s="13"/>
       <c r="AE103" s="1" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="AF103" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG103" s="13"/>
       <c r="AH103" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI103" s="13"/>
       <c r="AJ103" s="13"/>
@@ -54627,7 +54624,7 @@
       <c r="L104" s="4"/>
       <c r="M104" s="4"/>
       <c r="N104" s="4" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="O104" s="6"/>
       <c r="P104" s="6"/>
@@ -54652,7 +54649,7 @@
         <v>359</v>
       </c>
       <c r="W104" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X104" s="13"/>
       <c r="Y104" s="13"/>
@@ -54664,14 +54661,14 @@
       </c>
       <c r="AD104" s="13"/>
       <c r="AE104" s="1" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="AF104" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG104" s="13"/>
       <c r="AH104" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI104" s="13"/>
       <c r="AJ104" s="13"/>
@@ -54698,7 +54695,7 @@
       <c r="L105" s="4"/>
       <c r="M105" s="4"/>
       <c r="N105" s="4" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="O105" s="6"/>
       <c r="P105" s="6"/>
@@ -54723,7 +54720,7 @@
         <v>359</v>
       </c>
       <c r="W105" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X105" s="13"/>
       <c r="Y105" s="13"/>
@@ -54737,14 +54734,14 @@
         <v>621</v>
       </c>
       <c r="AE105" s="1" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="AF105" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG105" s="13"/>
       <c r="AH105" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI105" s="13"/>
       <c r="AJ105" s="13"/>
@@ -54772,7 +54769,7 @@
       <c r="M106" s="4"/>
       <c r="AG106" s="13"/>
       <c r="AH106" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI106" s="13"/>
       <c r="AJ106" s="13"/>
@@ -54822,7 +54819,7 @@
         <v>359</v>
       </c>
       <c r="W107" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X107" s="13"/>
       <c r="Y107" s="13"/>
@@ -54832,14 +54829,14 @@
       <c r="AC107" s="13"/>
       <c r="AD107" s="13"/>
       <c r="AE107" s="1" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="AF107" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG107" s="13"/>
       <c r="AH107" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI107" s="13"/>
       <c r="AJ107" s="13"/>
@@ -54889,7 +54886,7 @@
         <v>359</v>
       </c>
       <c r="W108" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X108" s="13"/>
       <c r="Y108" s="13"/>
@@ -54902,11 +54899,11 @@
         <v>76</v>
       </c>
       <c r="AF108" s="1" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="AG108" s="13"/>
       <c r="AH108" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI108" s="13"/>
       <c r="AJ108" s="13"/>
@@ -54933,7 +54930,7 @@
       <c r="L109" s="4"/>
       <c r="M109" s="4"/>
       <c r="N109" s="4" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="O109" s="6"/>
       <c r="P109" s="6"/>
@@ -54958,7 +54955,7 @@
         <v>359</v>
       </c>
       <c r="W109" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X109" s="13"/>
       <c r="Y109" s="13"/>
@@ -54966,20 +54963,20 @@
       <c r="AA109" s="13"/>
       <c r="AB109" s="13"/>
       <c r="AC109" s="1" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="AD109" s="1" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="AE109" s="1" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="AF109" s="1" t="s">
         <v>224</v>
       </c>
       <c r="AG109" s="13"/>
       <c r="AH109" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI109" s="13"/>
       <c r="AJ109" s="13"/>
@@ -55006,7 +55003,7 @@
       <c r="L110" s="4"/>
       <c r="M110" s="4"/>
       <c r="N110" s="4" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="O110" s="6"/>
       <c r="P110" s="6"/>
@@ -55031,7 +55028,7 @@
         <v>359</v>
       </c>
       <c r="W110" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X110" s="13"/>
       <c r="Y110" s="13"/>
@@ -55043,14 +55040,14 @@
       </c>
       <c r="AD110" s="13"/>
       <c r="AE110" s="1" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="AF110" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG110" s="13"/>
       <c r="AH110" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI110" s="13"/>
       <c r="AJ110" s="13"/>
@@ -55100,7 +55097,7 @@
         <v>359</v>
       </c>
       <c r="W111" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X111" s="13"/>
       <c r="Y111" s="13"/>
@@ -55110,14 +55107,14 @@
       <c r="AC111" s="13"/>
       <c r="AD111" s="13"/>
       <c r="AE111" s="1" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="AF111" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AG111" s="13"/>
       <c r="AH111" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI111" s="13"/>
       <c r="AJ111" s="13"/>
@@ -55167,7 +55164,7 @@
         <v>359</v>
       </c>
       <c r="W112" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X112" s="13"/>
       <c r="Y112" s="13"/>
@@ -55176,17 +55173,17 @@
       <c r="AB112" s="13"/>
       <c r="AC112" s="13"/>
       <c r="AD112" s="1" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="AE112" s="1" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="AF112" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG112" s="13"/>
       <c r="AH112" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI112" s="13"/>
       <c r="AJ112" s="13"/>
@@ -55236,7 +55233,7 @@
         <v>359</v>
       </c>
       <c r="W113" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X113" s="13"/>
       <c r="Y113" s="13"/>
@@ -55245,17 +55242,17 @@
       <c r="AB113" s="13"/>
       <c r="AC113" s="13"/>
       <c r="AD113" s="1" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="AE113" s="1" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="AF113" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AG113" s="13"/>
       <c r="AH113" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI113" s="13"/>
       <c r="AJ113" s="13"/>
@@ -55282,7 +55279,7 @@
       <c r="L114" s="4"/>
       <c r="M114" s="4"/>
       <c r="N114" s="4" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="O114" s="6"/>
       <c r="P114" s="6"/>
@@ -55307,7 +55304,7 @@
         <v>359</v>
       </c>
       <c r="W114" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="X114" s="13"/>
       <c r="Y114" s="13"/>
@@ -55322,7 +55319,7 @@
       <c r="AF114" s="13"/>
       <c r="AG114" s="13"/>
       <c r="AH114" s="14" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AI114" s="13"/>
       <c r="AJ114" s="13"/>
@@ -55375,14 +55372,14 @@
       <c r="X115" s="34"/>
       <c r="Y115" s="34"/>
       <c r="Z115" s="36" t="s">
+        <v>1766</v>
+      </c>
+      <c r="AA115" s="36" t="s">
         <v>1767</v>
-      </c>
-      <c r="AA115" s="36" t="s">
-        <v>1768</v>
       </c>
       <c r="AB115" s="34"/>
       <c r="AC115" s="34" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AD115" s="34"/>
       <c r="AE115" s="34"/>
@@ -55545,7 +55542,7 @@
       <c r="K116" s="34"/>
       <c r="L116" s="34"/>
       <c r="M116" s="36" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="N116" s="34"/>
       <c r="O116" s="34"/>
@@ -55576,14 +55573,14 @@
       <c r="X116" s="34"/>
       <c r="Y116" s="34"/>
       <c r="Z116" s="36" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AA116" s="36" t="s">
         <v>1769</v>
-      </c>
-      <c r="AA116" s="36" t="s">
-        <v>1770</v>
       </c>
       <c r="AB116" s="34"/>
       <c r="AC116" s="34" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="AD116" s="34"/>
       <c r="AE116" s="34"/>
@@ -55605,7 +55602,7 @@
       <c r="AU116" s="34"/>
       <c r="AV116" s="37"/>
       <c r="AW116" s="37" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="AX116" s="37"/>
       <c r="AY116" s="37"/>
@@ -55777,14 +55774,14 @@
       <c r="X117" s="34"/>
       <c r="Y117" s="34"/>
       <c r="Z117" s="36" t="s">
+        <v>1772</v>
+      </c>
+      <c r="AA117" s="36" t="s">
         <v>1773</v>
-      </c>
-      <c r="AA117" s="36" t="s">
-        <v>1774</v>
       </c>
       <c r="AB117" s="34"/>
       <c r="AC117" s="34" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AD117" s="34"/>
       <c r="AE117" s="34"/>
@@ -55806,7 +55803,7 @@
       <c r="AU117" s="34"/>
       <c r="AV117" s="37"/>
       <c r="AW117" s="37" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="AX117" s="37"/>
       <c r="AY117" s="37"/>
@@ -55935,13 +55932,13 @@
     </row>
     <row r="118" spans="1:173" s="10" customFormat="1" ht="23.25" customHeight="1">
       <c r="A118" s="38" t="s">
+        <v>1774</v>
+      </c>
+      <c r="B118" s="39" t="s">
         <v>1775</v>
       </c>
-      <c r="B118" s="39" t="s">
+      <c r="C118" s="38" t="s">
         <v>1776</v>
-      </c>
-      <c r="C118" s="38" t="s">
-        <v>1777</v>
       </c>
       <c r="D118" s="38"/>
       <c r="E118" s="38" t="s">
@@ -55957,10 +55954,10 @@
       <c r="M118" s="39"/>
       <c r="N118" s="39"/>
       <c r="O118" s="38" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="P118" s="38" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="Q118" s="40" t="s">
         <v>99</v>
@@ -55998,12 +55995,12 @@
       <c r="AH118" s="39"/>
       <c r="AI118" s="39"/>
       <c r="AJ118" s="38" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="AK118" s="38"/>
       <c r="AL118" s="38"/>
       <c r="AM118" s="38" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="AN118" s="38"/>
       <c r="AO118" s="38" t="s">
@@ -56022,14 +56019,14 @@
         <v>132</v>
       </c>
       <c r="AT118" s="38" t="s">
+        <v>1774</v>
+      </c>
+      <c r="AU118" s="39" t="s">
         <v>1775</v>
-      </c>
-      <c r="AU118" s="39" t="s">
-        <v>1776</v>
       </c>
       <c r="AV118" s="39"/>
       <c r="AW118" s="39" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="AX118" s="39"/>
       <c r="AY118" s="39"/>
@@ -56158,13 +56155,13 @@
     </row>
     <row r="119" spans="1:173" s="10" customFormat="1" ht="23.25" customHeight="1">
       <c r="A119" s="38" t="s">
+        <v>1780</v>
+      </c>
+      <c r="B119" s="39" t="s">
         <v>1781</v>
       </c>
-      <c r="B119" s="39" t="s">
+      <c r="C119" s="38" t="s">
         <v>1782</v>
-      </c>
-      <c r="C119" s="38" t="s">
-        <v>1783</v>
       </c>
       <c r="D119" s="38"/>
       <c r="E119" s="38" t="s">
@@ -56180,10 +56177,10 @@
       <c r="M119" s="39"/>
       <c r="N119" s="39"/>
       <c r="O119" s="38" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="P119" s="38" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="Q119" s="40" t="s">
         <v>731</v>
@@ -56221,12 +56218,12 @@
       <c r="AH119" s="39"/>
       <c r="AI119" s="39"/>
       <c r="AJ119" s="38" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="AK119" s="38"/>
       <c r="AL119" s="38"/>
       <c r="AM119" s="38" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="AN119" s="38"/>
       <c r="AO119" s="38" t="s">
@@ -56245,14 +56242,14 @@
         <v>132</v>
       </c>
       <c r="AT119" s="38" t="s">
+        <v>1780</v>
+      </c>
+      <c r="AU119" s="39" t="s">
         <v>1781</v>
-      </c>
-      <c r="AU119" s="39" t="s">
-        <v>1782</v>
       </c>
       <c r="AV119" s="39"/>
       <c r="AW119" s="39" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="AX119" s="39"/>
       <c r="AY119" s="39"/>
@@ -56381,13 +56378,13 @@
     </row>
     <row r="120" spans="1:173" s="10" customFormat="1" ht="23.25" customHeight="1">
       <c r="A120" s="38" t="s">
+        <v>1784</v>
+      </c>
+      <c r="B120" s="39" t="s">
         <v>1785</v>
       </c>
-      <c r="B120" s="39" t="s">
+      <c r="C120" s="38" t="s">
         <v>1786</v>
-      </c>
-      <c r="C120" s="38" t="s">
-        <v>1787</v>
       </c>
       <c r="D120" s="38"/>
       <c r="E120" s="38" t="s">
@@ -56403,10 +56400,10 @@
       <c r="M120" s="39"/>
       <c r="N120" s="39"/>
       <c r="O120" s="38" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="P120" s="38" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="Q120" s="40" t="s">
         <v>873</v>
@@ -56444,12 +56441,12 @@
       <c r="AH120" s="39"/>
       <c r="AI120" s="39"/>
       <c r="AJ120" s="38" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="AK120" s="38"/>
       <c r="AL120" s="38"/>
       <c r="AM120" s="38" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="AN120" s="38"/>
       <c r="AO120" s="38" t="s">
@@ -56468,14 +56465,14 @@
         <v>132</v>
       </c>
       <c r="AT120" s="38" t="s">
+        <v>1784</v>
+      </c>
+      <c r="AU120" s="39" t="s">
         <v>1785</v>
-      </c>
-      <c r="AU120" s="39" t="s">
-        <v>1786</v>
       </c>
       <c r="AV120" s="39"/>
       <c r="AW120" s="39" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="AX120" s="39"/>
       <c r="AY120" s="39"/>
@@ -56604,13 +56601,13 @@
     </row>
     <row r="121" spans="1:173" s="10" customFormat="1" ht="23.25" customHeight="1">
       <c r="A121" s="38" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B121" s="39" t="s">
         <v>1790</v>
       </c>
-      <c r="B121" s="39" t="s">
+      <c r="C121" s="38" t="s">
         <v>1791</v>
-      </c>
-      <c r="C121" s="38" t="s">
-        <v>1792</v>
       </c>
       <c r="D121" s="38"/>
       <c r="E121" s="38" t="s">
@@ -56626,10 +56623,10 @@
       <c r="M121" s="39"/>
       <c r="N121" s="39"/>
       <c r="O121" s="38" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="P121" s="38" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="Q121" s="40" t="s">
         <v>110</v>
@@ -56667,12 +56664,12 @@
       <c r="AH121" s="39"/>
       <c r="AI121" s="39"/>
       <c r="AJ121" s="38" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="AK121" s="38"/>
       <c r="AL121" s="38"/>
       <c r="AM121" s="38" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="AN121" s="38"/>
       <c r="AO121" s="38" t="s">
@@ -56691,14 +56688,14 @@
         <v>132</v>
       </c>
       <c r="AT121" s="38" t="s">
+        <v>1789</v>
+      </c>
+      <c r="AU121" s="39" t="s">
         <v>1790</v>
-      </c>
-      <c r="AU121" s="39" t="s">
-        <v>1791</v>
       </c>
       <c r="AV121" s="39"/>
       <c r="AW121" s="39" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="AX121" s="39"/>
       <c r="AY121" s="39"/>
@@ -56827,13 +56824,13 @@
     </row>
     <row r="122" spans="1:173" s="10" customFormat="1" ht="23.25" customHeight="1">
       <c r="A122" s="38" t="s">
+        <v>1780</v>
+      </c>
+      <c r="B122" s="39" t="s">
         <v>1781</v>
       </c>
-      <c r="B122" s="39" t="s">
-        <v>1782</v>
-      </c>
       <c r="C122" s="38" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="D122" s="38"/>
       <c r="E122" s="38" t="s">
@@ -56849,10 +56846,10 @@
       <c r="M122" s="39"/>
       <c r="N122" s="39"/>
       <c r="O122" s="38" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="P122" s="38" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="Q122" s="40" t="s">
         <v>873</v>
@@ -56890,12 +56887,12 @@
       <c r="AH122" s="39"/>
       <c r="AI122" s="39"/>
       <c r="AJ122" s="38" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="AK122" s="38"/>
       <c r="AL122" s="38"/>
       <c r="AM122" s="38" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="AN122" s="38"/>
       <c r="AO122" s="38" t="s">
@@ -56914,14 +56911,14 @@
         <v>132</v>
       </c>
       <c r="AT122" s="38" t="s">
+        <v>1780</v>
+      </c>
+      <c r="AU122" s="39" t="s">
         <v>1781</v>
-      </c>
-      <c r="AU122" s="39" t="s">
-        <v>1782</v>
       </c>
       <c r="AV122" s="39"/>
       <c r="AW122" s="39" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="AX122" s="39"/>
       <c r="AY122" s="39"/>
@@ -57050,13 +57047,13 @@
     </row>
     <row r="123" spans="1:173" s="10" customFormat="1" ht="23.25" customHeight="1">
       <c r="A123" s="32" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B123" s="42" t="s">
         <v>1795</v>
       </c>
-      <c r="B123" s="42" t="s">
+      <c r="C123" s="32" t="s">
         <v>1796</v>
-      </c>
-      <c r="C123" s="32" t="s">
-        <v>1797</v>
       </c>
       <c r="D123" s="32"/>
       <c r="E123" s="32" t="s">
@@ -57072,10 +57069,10 @@
       <c r="M123" s="42"/>
       <c r="N123" s="42"/>
       <c r="O123" s="32" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="P123" s="32" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="Q123" s="43" t="s">
         <v>99</v>
@@ -57113,12 +57110,12 @@
       <c r="AH123" s="42"/>
       <c r="AI123" s="42"/>
       <c r="AJ123" s="32" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="AK123" s="32"/>
       <c r="AL123" s="32"/>
       <c r="AM123" s="32" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="AN123" s="32"/>
       <c r="AO123" s="32" t="s">
@@ -57137,14 +57134,14 @@
         <v>132</v>
       </c>
       <c r="AT123" s="32" t="s">
+        <v>1794</v>
+      </c>
+      <c r="AU123" s="42" t="s">
         <v>1795</v>
-      </c>
-      <c r="AU123" s="42" t="s">
-        <v>1796</v>
       </c>
       <c r="AV123" s="42"/>
       <c r="AW123" s="42" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="AX123" s="42"/>
       <c r="AY123" s="42"/>
@@ -57273,13 +57270,13 @@
     </row>
     <row r="124" spans="1:173" s="10" customFormat="1" ht="23.25" customHeight="1">
       <c r="A124" s="32" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B124" s="42" t="s">
         <v>1800</v>
       </c>
-      <c r="B124" s="42" t="s">
+      <c r="C124" s="32" t="s">
         <v>1801</v>
-      </c>
-      <c r="C124" s="32" t="s">
-        <v>1802</v>
       </c>
       <c r="D124" s="32"/>
       <c r="E124" s="32" t="s">
@@ -57295,10 +57292,10 @@
       <c r="M124" s="42"/>
       <c r="N124" s="42"/>
       <c r="O124" s="32" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="P124" s="32" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="Q124" s="43" t="s">
         <v>99</v>
@@ -57336,12 +57333,12 @@
       <c r="AH124" s="42"/>
       <c r="AI124" s="42"/>
       <c r="AJ124" s="32" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="AK124" s="32"/>
       <c r="AL124" s="32"/>
       <c r="AM124" s="32" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="AN124" s="32"/>
       <c r="AO124" s="32" t="s">
@@ -57360,14 +57357,14 @@
         <v>149</v>
       </c>
       <c r="AT124" s="32" t="s">
+        <v>1799</v>
+      </c>
+      <c r="AU124" s="42" t="s">
         <v>1800</v>
-      </c>
-      <c r="AU124" s="42" t="s">
-        <v>1801</v>
       </c>
       <c r="AV124" s="42"/>
       <c r="AW124" s="42" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="AX124" s="42"/>
       <c r="AY124" s="42"/>
